--- a/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_12.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 2.253</t>
+          <t>X ≈ 2.252</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>174</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.052759585766154</v>
+        <v>6.085841642695264</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.720588217020236</v>
+        <v>5.75407446081595</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.430547012341322</v>
+        <v>9.46574255451538</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.295428081011302</v>
+        <v>9.331463707848826</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.07806798573041</v>
+        <v>10.14341618671276</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.696022664569952</v>
+        <v>9.76118750612531</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.5038825718196</v>
+        <v>13.57000161651273</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.51506208772457</v>
+        <v>11.5815269360546</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.70456014998885</v>
+        <v>12.77101878730355</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.36585675250061</v>
+        <v>11.43324010033248</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.925397700048947</v>
+        <v>9.992492871174584</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.078277132888772</v>
+        <v>9.145728265901127</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.960989695692739</v>
+        <v>8.029777396263647</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.732715724769598</v>
+        <v>3.801782169563211</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.503488739507461</v>
+        <v>2.5733578449776</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.377966244836372</v>
+        <v>1.447182101394624</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.475847360895834</v>
+        <v>-0.4064384501701355</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.154414913077837</v>
+        <v>-1.08484258945488</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.660521574375664</v>
+        <v>-2.591160487075861</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.326700044192023</v>
+        <v>-1.257510816145924</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-2.444122040968097</v>
+        <v>-2.374257306843134</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7978972573503</v>
+        <v>-0.7278982898879036</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.625423483086891</v>
+        <v>0.6951460326235761</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.5495059487799949</v>
+        <v>0.6193602964871374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 2.875</t>
+          <t>X ≈ 2.873</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.5748273921704552</v>
+        <v>0.7993848306487195</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.648939555425933</v>
+        <v>1.878997355694445</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.27505007080574</v>
+        <v>1.510612951574608</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.13734283472904</v>
+        <v>0.09660978990113023</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2044851692971719</v>
+        <v>0.4703013356992614</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.03863832414917567</v>
+        <v>0.3030931580384788</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3273433445876179</v>
+        <v>0.5965709709638176</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.519351342323901</v>
+        <v>2.797819413914148</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.4453954681913004</v>
+        <v>0.7163783125930507</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.088535950368431</v>
+        <v>-1.822845232483282</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.639919864337926</v>
+        <v>-4.384503928471389</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.331248259164028</v>
+        <v>-6.080438042118821</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-7.099463193108747</v>
+        <v>-6.845987761171642</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.321327228708164</v>
+        <v>-7.067486138255681</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-9.041275051655745</v>
+        <v>-8.790338073863197</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-8.450863216428729</v>
+        <v>-8.200500904906477</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-9.294920908140831</v>
+        <v>-9.046810799279669</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-11.17221121907041</v>
+        <v>-10.93016912075396</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-8.482360493147347</v>
+        <v>-8.231630950279133</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-8.652925056477066</v>
+        <v>-8.403559238019788</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-7.781727527844119</v>
+        <v>-7.526570273503708</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.278061445313277</v>
+        <v>-9.027745574793556</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.715820894893895</v>
+        <v>-9.468233763389073</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-8.731491850192938</v>
+        <v>-8.479915688296138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 3.497</t>
+          <t>X ≈ 3.494</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.151823520228227</v>
+        <v>0.9632555066238311</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.272123144337591</v>
+        <v>-2.421976262666206</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.167904799799139</v>
+        <v>-2.324458714727697</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2086095363840954</v>
+        <v>0.02232634216992579</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.476396321512709</v>
+        <v>-2.602235194908388</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.289729310090294</v>
+        <v>-2.41680650945726</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.130018514285645</v>
+        <v>-1.27484175225861</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.34414670027035</v>
+        <v>-3.464151485232449</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.852938896075209</v>
+        <v>-4.952060635173147</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.758498939540154</v>
+        <v>-1.895053541649638</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7097848310752255</v>
+        <v>-0.8560281447828331</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.109497296924047</v>
+        <v>1.930620098459656</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.9794636222676161</v>
+        <v>0.8140742942169368</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7963119509670946</v>
+        <v>-0.9372359899424509</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.64430515362168</v>
+        <v>1.473226729164182</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.077999067855053</v>
+        <v>0.915679397411175</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1651770111998871</v>
+        <v>0.01536162874891289</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.388292280362059</v>
+        <v>2.213358493865535</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.052419355125693</v>
+        <v>0.8932382776567493</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.629634071040783</v>
+        <v>1.463542254450445</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.471431378507425</v>
+        <v>1.305781241948154</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.616004425843542</v>
+        <v>0.4613446271873087</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.592022596738687</v>
+        <v>-1.956007175113427</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.040457824197148</v>
+        <v>-1.648544212796629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 4.119</t>
+          <t>X ≈ 4.114</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.645646454369633</v>
+        <v>-2.409837487879095</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.674731328933781</v>
+        <v>-3.783121151883876</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.351709396889682</v>
+        <v>-2.442901001766963</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.415110745718536</v>
+        <v>-3.500421480496193</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.398721350833306</v>
+        <v>-2.447183473568572</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.865243077021795</v>
+        <v>-2.261539147693959</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.681212131025028</v>
+        <v>-4.074530488773618</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.737085785754353</v>
+        <v>-6.785316949583844</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.271966955528612</v>
+        <v>-4.312415279255006</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.623221953876886</v>
+        <v>-2.999060097267112</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.738494257607918</v>
+        <v>-4.117739051335455</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.242753193408845</v>
+        <v>-1.613678039790472</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.0525499614376983</v>
+        <v>0.04896211928041794</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5195520520906669</v>
+        <v>0.5245827697326177</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4929922859151077</v>
+        <v>-0.4823297950359162</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.5899368765703912</v>
+        <v>-0.5855778994721845</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.077165996254273</v>
+        <v>-1.069418892709784</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.533680911970301</v>
+        <v>-1.524547956401619</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.316370701493376</v>
+        <v>-1.309557515524297</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.959549133162575</v>
+        <v>-2.170931161222043</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.8988237668113399</v>
+        <v>-1.319094726159953</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.109138043037774</v>
+        <v>-1.746415361004637</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4859308208065158</v>
+        <v>-1.123433204855218</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.5618721600750618</v>
+        <v>-0.9842085484608063</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 4.741</t>
+          <t>X ≈ 4.735</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.662258168028345</v>
+        <v>4.326860290305945</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.670248660583866</v>
+        <v>3.991600971890939</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9123830061453972</v>
+        <v>1.883832813687924</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.016505619807795</v>
+        <v>2.166628622378546</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7907584319318204</v>
+        <v>-1.170451203840685</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.588427860959499</v>
+        <v>-1.649817152095579</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.034656171265915</v>
+        <v>-2.427429314749872</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.329741030081216</v>
+        <v>-1.851693950817122</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.289307096065684</v>
+        <v>-1.618970234385408</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7502427976758455</v>
+        <v>-0.7247886237874965</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.49768128749173</v>
+        <v>1.552282986075888</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.523378662971396</v>
+        <v>3.61258685097291</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.711203001785321</v>
+        <v>3.489851992197018</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.134819574868906</v>
+        <v>4.939580438986525</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.133003225488018</v>
+        <v>4.949614070557494</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.413417117889175</v>
+        <v>4.208839351406226</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.607264152034801</v>
+        <v>4.408657064420709</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>3.384226203840882</v>
+        <v>2.963295422737836</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.804292838042933</v>
+        <v>3.181222120065122</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.67120462046212</v>
+        <v>2.028216852093237</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.778169227965812</v>
+        <v>3.160532052731313</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>5.022346185524448</v>
+        <v>4.632888535215294</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.986890328904344</v>
+        <v>2.766472346053988</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.240981992936135</v>
+        <v>3.026210562629295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 5.363</t>
+          <t>X ≈ 5.356</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.91456126629317</v>
+        <v>5.506412050388874</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.923528381705005</v>
+        <v>6.48434118052505</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.615467858316165</v>
+        <v>7.23527009640943</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.91518552936653</v>
+        <v>11.31790213204829</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.44697973399174</v>
+        <v>12.30167727576341</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>16.20642655398142</v>
+        <v>15.97875867897015</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15.00039225210283</v>
+        <v>15.22050914227815</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>15.62557920747092</v>
+        <v>15.81756375178695</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13.44399943389072</v>
+        <v>13.68142228622462</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13.5726917435099</v>
+        <v>13.79073319225967</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12.06603393448731</v>
+        <v>12.326524704721</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>10.89827212211731</v>
+        <v>11.18017041284151</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12.91530107559731</v>
+        <v>12.68981767091699</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>14.49291044395759</v>
+        <v>14.22598706995004</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>16.53006656538346</v>
+        <v>16.20070715883563</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>15.34088758850655</v>
+        <v>15.05301109075288</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>15.66313932749819</v>
+        <v>15.36569392903986</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>16.00658640467645</v>
+        <v>15.70724156488623</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>16.22270956760827</v>
+        <v>15.93041463507162</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>16.85818385650214</v>
+        <v>16.56341003588817</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.4181224609571</v>
+        <v>15.1517362124306</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>15.34216740531459</v>
+        <v>15.0758902510217</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>14.72008158524964</v>
+        <v>14.47317198104751</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>14.19570975270764</v>
+        <v>13.95874323659626</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 5.985</t>
+          <t>X ≈ 5.976</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2216524772930981</v>
+        <v>1.390473736801347</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.048598663843805</v>
+        <v>2.370701481468714</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.20905963931073</v>
+        <v>3.563625128808866</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5236653039577703</v>
+        <v>-0.1985579843536698</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.744949920918351</v>
+        <v>-0.9618744120219205</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.129620475311398</v>
+        <v>-0.77867000785659</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.127791138253606</v>
+        <v>1.517093999041812</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.719080552546686</v>
+        <v>1.680209569543244</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8998714696341779</v>
+        <v>0.8505235104446456</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.726587161739573</v>
+        <v>2.707084253933878</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.570533649495971</v>
+        <v>2.546171116194117</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.293166613949666</v>
+        <v>2.268679076076509</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.174387213464946</v>
+        <v>1.593022253429368</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.257643137234723</v>
+        <v>2.692152966776241</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.167231139789081</v>
+        <v>1.160585681566701</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.02562245617580317</v>
+        <v>-0.0007383474059707851</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.196381674934344</v>
+        <v>1.185552784187372</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>0.6429517550422332</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.4316090130117374</v>
+        <v>0.4187639696677152</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.114130434782609</v>
+        <v>-0.2746587520940906</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.657330843780564</v>
+        <v>-1.257955417525245</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.733285899423173</v>
+        <v>-1.333801378934446</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.023728124245487</v>
+        <v>-0.6187980320910569</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2301042461225506</v>
+        <v>0.1864269834080829</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 6.607</t>
+          <t>X ≈ 6.597</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7518603559164418</v>
+        <v>-1.376463826662999</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.087898543754463</v>
+        <v>-1.711549840076422</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.790109992861417</v>
+        <v>-3.97744527644717</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.574025818715789</v>
+        <v>-1.803090445343763</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6889469310533798</v>
+        <v>-1.316483212285647</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5675705896215106</v>
+        <v>0.1145854991198547</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.653348235291929</v>
+        <v>-2.314401294837197</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1667893928177975</v>
+        <v>-0.1124359309130796</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.469913860003956</v>
+        <v>1.167150666959373</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6982475856183186</v>
+        <v>0.6250961488210294</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.888977478457186</v>
+        <v>3.200711761623637</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.351305056380049</v>
+        <v>1.682554904418396</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1868868863281179</v>
+        <v>0.1492255105294404</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4360096921941405</v>
+        <v>0.7593814210028711</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.2204722444627905</v>
+        <v>0.7591741371785758</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.4676737287046961</v>
+        <v>0.5251137032661362</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.664369200159058</v>
+        <v>1.224508885221439</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.9813267123338321</v>
+        <v>1.122444013010529</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.7755089469955934</v>
+        <v>0.5065433149264038</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>2.228375527426167</v>
+        <v>1.942937167259053</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.263234190158158</v>
+        <v>1.401736212430649</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.187279134515549</v>
+        <v>1.325890251021605</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>1.883995229267732</v>
+        <v>2.017031630170322</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.5422311051891242</v>
+        <v>0.6911993769470968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 7.229</t>
+          <t>X ≈ 7.217</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.020530901151169</v>
+        <v>-4.808688320934763</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.557249210644123</v>
+        <v>-3.798821805172153</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.534375126196529</v>
+        <v>-1.489775385444069</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.260668939330785</v>
+        <v>-2.219666132204132</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.675940724119009</v>
+        <v>-3.162466187711786</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.528300205008655</v>
+        <v>-3.724933781459228</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.79859247753339</v>
+        <v>-3.697157401169513</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.551421875028197</v>
+        <v>-0.7089496512577398</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.713920458089227</v>
+        <v>2.040363783925294</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.611970435903082</v>
+        <v>-0.3767979556658076</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.974607329757632</v>
+        <v>0.4558546278926485</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9147808500140258</v>
+        <v>-1.158066350456536</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.21240441840844</v>
+        <v>-0.1632294658920088</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.455621002118072</v>
+        <v>2.09951380474692</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.477928055394834</v>
+        <v>0.3242773690217646</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.468614961178567</v>
+        <v>2.324137933564742</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.813302944029516</v>
+        <v>5.232269721612411</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>6.167778987393703</v>
+        <v>5.43567491434024</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.843361609784971</v>
+        <v>5.433235310888115</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>7.652027027027032</v>
+        <v>7.037937510937113</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>6.56828607748853</v>
+        <v>5.725506704233972</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.411249940764911</v>
+        <v>5.103212655393172</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>4.604944026165889</v>
+        <v>5.377687367875225</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.366840524735323</v>
+        <v>3.116062764925189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 7.851</t>
+          <t>X ≈ 7.838</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.974825884796658</v>
+        <v>-3.396158468743302</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.730607411529121</v>
+        <v>-3.167321103478905</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.176311958391487</v>
+        <v>-5.465702107824896</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.566525237161223</v>
+        <v>-3.594307352075433</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.195614419375353</v>
+        <v>-1.918624446314723</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.421550714986445</v>
+        <v>-1.726272044034395</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4557345430737527</v>
+        <v>-0.7893212298220362</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.383950958595896</v>
+        <v>-5.066063706525192</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.188009884567208</v>
+        <v>-5.596984408072387</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.054868551150534</v>
+        <v>-3.515205507049252</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.524695330546948</v>
+        <v>-4.952983299089809</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-6.385184582858926</v>
+        <v>-5.232712014571199</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.928280452508993</v>
+        <v>-5.47057600332716</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-8.312427961217772</v>
+        <v>-6.834512022630832</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-5.482987107231757</v>
+        <v>-4.635512463068466</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-6.050717755284793</v>
+        <v>-5.183982683982684</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-6.766206798270858</v>
+        <v>-5.889328392388727</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-5.708399516691784</v>
+        <v>-5.422740524781339</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-4.329485656085481</v>
+        <v>-4.063992000999939</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-4.142441860465119</v>
+        <v>-3.877146191031841</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.941456222951373</v>
+        <v>-2.133978073283458</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.854620580919629</v>
+        <v>-1.638395463264118</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-4.486822158623553</v>
+        <v>-5.363920750782</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.399972800217668</v>
+        <v>-3.725467289719617</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 8.473</t>
+          <t>X ≈ 8.459</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.025472757102108</v>
+        <v>-4.325778620281163</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.360648271746435</v>
+        <v>-5.345486925480408</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.746294681778565</v>
+        <v>-3.358848440264829</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.460087994971722</v>
+        <v>-4.07180245970757</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.798330752968738</v>
+        <v>-2.352798411706971</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9354904642863033</v>
+        <v>-0.7959692119108865</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3186704306867298</v>
+        <v>0.4868766247467065</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.04011578516809067</v>
+        <v>0.2086651799936732</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5940438254849099</v>
+        <v>-0.4347791449409755</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.043554911930052</v>
+        <v>-1.892626327826783</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9335070578880575</v>
+        <v>1.121159341732401</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6544131544130778</v>
+        <v>0.8424099382844048</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8812732872774376</v>
+        <v>0.404179378277604</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.6599164762430831</v>
+        <v>0.1831005018310137</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6746904384699306</v>
+        <v>-1.159974302598982</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.43098174019994</v>
+        <v>-1.935450394354504</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-3.592102461375958</v>
+        <v>-4.124162051879878</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.670058850444143</v>
+        <v>-2.174208235153159</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-6.183665417242132</v>
+        <v>-6.067905895324643</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-7.347972972972968</v>
+        <v>-6.565991592206011</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-6.539822030619654</v>
+        <v>-5.738674746473485</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-6.61577708626222</v>
+        <v>-6.499452214731825</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.638299217077346</v>
+        <v>-3.485251474852511</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.362889204994509</v>
+        <v>-2.876152221226548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 9.095</t>
+          <t>X ≈ 9.079</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.468735737106385</v>
+        <v>2.359152886567941</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.133560222462016</v>
+        <v>2.824376088218216</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.487510552026684</v>
+        <v>1.386357039187224</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>-0.1265969802555063</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.40844745380948</v>
+        <v>0.3376125471971605</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.166292695088501</v>
+        <v>-4.275421266705408</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.113762001745705</v>
+        <v>-7.447369950595757</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.598665853613475</v>
+        <v>-6.925581395348878</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.557149788590884</v>
+        <v>-6.884094213434132</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-7.330985199360271</v>
+        <v>-6.857009889470618</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-7.056625932244891</v>
+        <v>-7.382950247308699</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.780164280164279</v>
+        <v>-2.861699650756691</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.063598469602546</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.04859086491740072</v>
+        <v>-0.2059405940594061</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.770612006832437</v>
+        <v>1.535916108360126</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.746624437406247</v>
+        <v>4.530303030303031</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.612530743257324</v>
+        <v>4.396385893325473</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.094848914463626</v>
+        <v>6.691545189504382</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>8.507436570428645</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>6.498015873015873</v>
+        <v>8.694282380396729</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>8.335767844970256</v>
+        <v>10.55173621243069</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>5.878860408375267</v>
+        <v>8.075890251021598</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>8.534587955809819</v>
+        <v>10.75036496350356</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>6.077694235589014</v>
+        <v>8.274532710280475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 9.718</t>
+          <t>X ≈ 9.7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-13.32324421276834</v>
+        <v>-12.11542338461836</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-7.518068850219635</v>
+        <v>-6.517996793137712</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.571804402025116</v>
+        <v>-2.023812452338191</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.285597715218231</v>
+        <v>-3.584224098899575</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4894833769507159</v>
+        <v>2.012188818383699</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.463702887235435</v>
+        <v>-2.885590758230826</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.780974840359562</v>
+        <v>1.427206320590685</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.129158752527374</v>
+        <v>-2.240835632636973</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.964835669960927</v>
+        <v>-3.046806077840913</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.984285115818025</v>
+        <v>-2.972264126758759</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-5.218697778527307</v>
+        <v>-4.393119738834116</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-9.00656361182677</v>
+        <v>-7.21424202363805</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.622282900489353</v>
+        <v>-5.795031209138187</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-9.475218658892125</v>
+        <v>-8.558482966940758</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-11.01134288038557</v>
+        <v>-10.06408389164005</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-7.784703883395757</v>
+        <v>-6.927324088341031</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-7.91879757754468</v>
+        <v>-7.061241225318462</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-6.269395028727686</v>
+        <v>-6.318624302021043</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-6.053271865795871</v>
+        <v>-7.797648175333961</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.866228070175438</v>
+        <v>-8.458259992484628</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-5.532235496717206</v>
+        <v>-8.153348533332014</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.97661160499144</v>
+        <v>-4.839363986266541</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.824643456053167</v>
+        <v>-3.717431646665844</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1461988304093609</v>
+        <v>-2.098348645651825</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 10.34</t>
+          <t>X ≈ 10.32</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.193135231417401</v>
+        <v>-0.4298379391200342</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.33673054871371</v>
+        <v>-6.269201893433156</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.776431012799847</v>
+        <v>-5.872358557143045</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.950401317143438</v>
+        <v>-1.998156613283037</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.315671102167542</v>
+        <v>-3.251378278490854</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.128506489160756</v>
+        <v>-3.981843285054033</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-7.556239877851901</v>
+        <v>-6.588654354265529</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.525060010096169</v>
+        <v>-0.4448474503947608</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1713233115637252</v>
+        <v>1.431502116841102</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.142335108055356</v>
+        <v>-2.093707137177049</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.522843097577194</v>
+        <v>-5.489372265657323</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-11.22671576211399</v>
+        <v>-10.35527763240802</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-14.12111848502597</v>
+        <v>-13.31330208458539</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-17.88229830490982</v>
+        <v>-15.36924334635303</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-13.23149503067279</v>
+        <v>-12.35766187329128</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-9.981567724414241</v>
+        <v>-9.010981373366697</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-9.230705666350829</v>
+        <v>-7.31003612502311</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-8.45073333023366</v>
+        <v>-7.414876828844193</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-6.464698662877119</v>
+        <v>-5.364123062598871</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.622787610619469</v>
+        <v>-2.424983674649141</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-3.281032267405031</v>
+        <v>-2.967529842615171</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-4.241943075260032</v>
+        <v>-3.043375804024272</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.967167908777853</v>
+        <v>-3.68633228420282</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.388241991409153</v>
+        <v>-1.009870959444392</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 10.96</t>
+          <t>X ≈ 10.94</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>73</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-11.20836798109338</v>
+        <v>-11.17509368877443</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.433954454641743</v>
+        <v>-6.030418432329732</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-12.98324395982377</v>
+        <v>-12.94788953615524</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.587448231921073</v>
+        <v>-10.92111752820076</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-19.54175911283545</v>
+        <v>-19.47608608293977</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-17.98473148613004</v>
+        <v>-17.91925688314377</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-22.86718665927999</v>
+        <v>-22.80079460812997</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-23.14574130479851</v>
+        <v>-24.44886906658164</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-24.47408825347459</v>
+        <v>-24.40738188466701</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-23.87806065054531</v>
+        <v>-25.1802975607035</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-24.97356439712856</v>
+        <v>-26.2761009322402</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-25.25265830060358</v>
+        <v>-26.55485033568828</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-20.89769746429605</v>
+        <v>-20.82869733405109</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-21.11905427533048</v>
+        <v>-23.78950223789502</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-19.03825948697045</v>
+        <v>-18.96819348068106</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-17.07333642365044</v>
+        <v>-17.00394354503943</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-15.83756710410073</v>
+        <v>-17.13786068201676</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-15.94255052019601</v>
+        <v>-15.87283837213962</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-15.72642735726419</v>
+        <v>-15.65694699121498</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-15.53938356164384</v>
+        <v>-15.47010118124711</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-16.08258397064187</v>
+        <v>-14.64278433551451</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-14.78867601258577</v>
+        <v>-14.71863029692361</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-14.51390084610365</v>
+        <v>-13.07429257074285</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-15.95970519907082</v>
+        <v>-15.88985085136346</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 11.58</t>
+          <t>X ≈ 11.56</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.465413477970174</v>
+        <v>5.450061977477127</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5209248273718359</v>
+        <v>-1.702896639054543</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.448997384481196</v>
+        <v>-7.686370233540046</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.999999999999993</v>
+        <v>-7.262960616619146</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.774265098696887</v>
+        <v>0.3557943653790332</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>7.612592502401348</v>
+        <v>5.088215096930959</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10.3280984633706</v>
+        <v>8.861720958495148</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>6.561171724828725</v>
+        <v>5.174418604651201</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5.43989709217697</v>
+        <v>4.079542150202236</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>6.991643076756382</v>
+        <v>5.579353746893013</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>7.266002343871691</v>
+        <v>5.853413389054936</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>6.986908440396888</v>
+        <v>5.574663985606939</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.187998617258508</v>
+        <v>6.724229191478067</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>9.129432503898535</v>
+        <v>6.503150315031533</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8.470501264861205</v>
+        <v>5.845007017450975</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>6.739979919133738</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.280304829636059</v>
+        <v>1.760022256961889</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>5.338112111215139</v>
+        <v>2.791545189504475</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>5.554235274147011</v>
+        <v>3.007436570428602</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.090116279069761</v>
+        <v>-1.351172165057783</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5469158700718779</v>
+        <v>-1.893718333023841</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.633751512103622</v>
+        <v>-0.833200658069309</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.90852667858568</v>
+        <v>-0.55872594558722</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.832585339317284</v>
+        <v>0.5018054375531378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 12.21</t>
+          <t>X ≈ 12.18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.294132562503215</v>
+        <v>1.046652886568076</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.628344539442693</v>
+        <v>-0.8506239117817387</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-7.829949765433689</v>
+        <v>-6.976142960812815</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-6.956441491325258</v>
+        <v>-3.001596980255471</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-8.909012863650851</v>
+        <v>-4.899887452802787</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-11.89645142524728</v>
+        <v>-9.400421266705365</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-14.25661914460289</v>
+        <v>-13.29736995059567</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-16.12247537742295</v>
+        <v>-15.13808139534888</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-14.49365772509878</v>
+        <v>-13.53409421343413</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.330985199360271</v>
+        <v>-6.494509889470663</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-3.09545024730874</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.2491996507566938</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.238201644205716</v>
+        <v>4.877638282387231</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>10.36605118237775</v>
+        <v>12.46905940594064</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>12.88172311794359</v>
+        <v>13.37341610836</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>13.47678316756497</v>
+        <v>13.96780303030303</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>13.34268947341604</v>
+        <v>13.83388589332552</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>13.23770605732076</v>
+        <v>13.72904518950433</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>13.45382922025258</v>
+        <v>13.94493657042874</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>15.22817460317461</v>
+        <v>15.69428238039669</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>13.09767260687506</v>
+        <v>13.5892362124307</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>13.02171755123245</v>
+        <v>13.5133902510216</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>13.29649271771458</v>
+        <v>13.78786496350361</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>11.63324979114453</v>
+        <v>12.14953271028033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 12.83</t>
+          <t>X ≈ 12.8</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.67412140575086</v>
+        <v>-4.803637811106455</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.514512603414332</v>
+        <v>4.163910971939153</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>8.836716901233032</v>
+        <v>7.377054713605901</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>-2.638224887232262</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.5280604826984</v>
+        <v>-9.950759545826045</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.721848250643987</v>
+        <v>-9.76379335972873</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-9.494714382698014</v>
+        <v>-10.53574204361908</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-7.392316647264202</v>
+        <v>-8.488372093023258</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.350800582241632</v>
+        <v>-8.446884911108484</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-10.50558837396345</v>
+        <v>-11.54538198249381</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-6.620159549634273</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-5.74841824841824</v>
+        <v>-6.89890895308227</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-9.253861847857706</v>
+        <v>-10.34765241528724</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-7.094266277939738</v>
+        <v>-8.243149896385049</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.6103403741199003</v>
+        <v>0.401032387429801</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.777185086403279</v>
+        <v>-3.655743481324876</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.1493740186474426</v>
+        <v>0.8615021723953191</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.126594946209657</v>
+        <v>3.082242863922914</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.03823427181090722</v>
+        <v>0.972552849498399</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-1.166182735882337</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.775343266140816</v>
+        <v>-1.708728903848368</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-2.851298321783425</v>
+        <v>-1.784574865257532</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-2.576523155301295</v>
+        <v>-1.510100152775415</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-5.033416875522136</v>
+        <v>-3.911513801347532</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 13.45</t>
+          <t>X ≈ 13.42</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>12.99254526091586</v>
+        <v>15.58992211733726</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>16.36107344997524</v>
+        <v>15.25514531898745</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>7.513965578481702</v>
+        <v>6.124818577648824</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.5038759689923</v>
+        <v>9.258018404359817</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.434902480264391</v>
+        <v>8.922227931812657</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.622067093271284</v>
+        <v>12.95534796406382</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.145497257513547</v>
+        <v>8.337245434019628</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.836761091708823</v>
+        <v>4.212880143112763</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>11.94667501733498</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.8383269699519</v>
+        <v>7.327605495144766</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>12.5200936444747</v>
+        <v>15.29397282961448</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.129888629888583</v>
+        <v>3.476761887704846</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.698306292302327</v>
+        <v>-5.338707871459079</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.2159593996328724</v>
+        <v>-1.713632901751602</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-11.98600174978128</v>
+        <v>-10.06408389163996</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-7.687237996456197</v>
+        <v>-1.777389277389325</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-7.82133169060512</v>
+        <v>-5.757460260520546</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.222611402996691</v>
+        <v>-5.862300964341671</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-4.006488240064876</v>
+        <v>-5.646409583417345</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-3.819444444444443</v>
+        <v>-5.459563773449482</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-4.362644853442397</v>
+        <v>-2.155956095261615</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-8.142303612788758</v>
+        <v>-2.231802056670602</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4601210388992243</v>
+        <v>1.888826501965191</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.5360623781676495</v>
+        <v>5.659148094895706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 14.07</t>
+          <t>X ≈ 14.04</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>37</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.322770054399449</v>
+        <v>-2.28949576208062</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.85556794446975</v>
+        <v>13.59194365578578</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.11857018308628</v>
+        <v>12.15392460675472</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.81143934632307</v>
+        <v>-2.072542926201422</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.931398976761031</v>
+        <v>0.2943693039539355</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.118563589767781</v>
+        <v>0.4813354900513929</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.762410650394358</v>
+        <v>-8.398721301947106</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6355598905075084</v>
+        <v>-3.271527341294778</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.108658877217827</v>
+        <v>2.175365246025287</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.367879236254304</v>
+        <v>-1.300253132713863</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.093519969139003</v>
+        <v>-1.02619349055194</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.075316575316535</v>
+        <v>-4.00764559670268</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.497105091101012</v>
+        <v>0.2745977418467618</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.123867307540777</v>
+        <v>-5.351886540005346</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-3.377393141172668</v>
+        <v>-3.30732713488316</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-8.187738496956698</v>
+        <v>-10.82104832104832</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2137240829975084</v>
+        <v>-2.846857349917762</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-5.724112904498192</v>
+        <v>-2.951698053738866</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-5.507989741566377</v>
+        <v>-2.73580667281454</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-5.320945945945944</v>
+        <v>-2.548960862846471</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-5.864146354943898</v>
+        <v>-5.794209733515245</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-3.237398707883763</v>
+        <v>-8.572758397627091</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.44278186400377</v>
+        <v>-0.1901755770368894</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.366840524735302</v>
+        <v>-2.968710532962824</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 14.69</t>
+          <t>X ≈ 14.66</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>38</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>22.64166806793342</v>
+        <v>20.04336341288381</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22.3064925532891</v>
+        <v>22.34016556190244</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>12.97205524709773</v>
+        <v>15.63898861813463</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.626682986536174</v>
+        <v>9.66287670395505</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.89299214888044</v>
+        <v>14.59024412614454</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.448577814518856</v>
+        <v>9.514052417505042</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13.93886957720166</v>
+        <v>11.37368268098319</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>13.66031493168313</v>
+        <v>11.09547123623007</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>13.7018309967057</v>
+        <v>11.1369584181449</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.66483769119943</v>
+        <v>7.732463794739914</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.307618010946378</v>
+        <v>5.374944489533405</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.660103054839936</v>
+        <v>7.727774033453869</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.272453941615915</v>
+        <v>1.341454071860838</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.94583397268682</v>
+        <v>9.015112037519543</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.655323786281109</v>
+        <v>5.725389792570532</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.618804888534058</v>
+        <v>3.688197767145176</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>11.37944803649036</v>
+        <v>14.08059641964138</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>8.642885673026655</v>
+        <v>8.712597821083321</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>8.85900883595847</v>
+        <v>8.928489202007647</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.782894736842067</v>
+        <v>3.852177117238831</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.6081153804757591</v>
+        <v>0.6780520019044118</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-4.730997569903714</v>
+        <v>-2.029372906873107</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-9.719380298158434</v>
+        <v>-7.018056089127931</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-15.05847953216378</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 15.32</t>
+          <t>X ≈ 15.29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.468735737106343</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-7.821777757935678</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.836716901232975</v>
+        <v>6.124818577648767</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.9800664451826222</v>
+        <v>-2.280443134101724</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-20.81377476841275</v>
+        <v>-25.6931566835718</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-13.48375301254877</v>
+        <v>-17.81388280516684</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.171952283968587</v>
+        <v>12.18339928017347</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.893397638449812</v>
+        <v>11.90518783542028</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.350800582241433</v>
+        <v>-3.437940367280284</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-8.124635993010862</v>
+        <v>-11.90316373562436</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-11.62910409346254</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.129370629370726</v>
+        <v>-11.90785349691054</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.253861847857671</v>
+        <v>-13.03101556376666</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-23.76093294460641</v>
+        <v>-28.63670982482863</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-24.41986418364361</v>
+        <v>-29.29485312240919</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-23.82480413402223</v>
+        <v>-28.7004662004662</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-23.95889782817115</v>
+        <v>-28.83438333744367</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-24.06388124426643</v>
+        <v>-28.93922404126485</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-23.84775808133462</v>
+        <v>-28.72333266034053</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-16.51785714285704</v>
+        <v>-20.8441791580648</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-17.0610575518552</v>
+        <v>-21.38672532603095</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-17.1370126074976</v>
+        <v>-21.46257128743994</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-16.86223744101547</v>
+        <v>-21.18809657495788</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-16.93817878028405</v>
+        <v>-28.95623652048875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 15.94</t>
+          <t>X ≈ 15.91</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.65921192758254</v>
+        <v>7.897614425029573</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-7.821777757935578</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-13.78233071781454</v>
+        <v>-9.25979680696657</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.170542635658919</v>
+        <v>-2.280443134101667</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-2.616233606649054</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-23.0075625363584</v>
+        <v>-10.12157511285925</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-23.78042866841231</v>
+        <v>-18.58583148905729</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-24.0589833139307</v>
+        <v>-18.86404293381027</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-24.01746724890853</v>
+        <v>-18.82255575189589</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-24.79130265967796</v>
+        <v>-19.59547142793238</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-24.51694339256251</v>
+        <v>-19.32141178577013</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-24.79603729603717</v>
+        <v>-19.60016118921823</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-25.92052851452444</v>
+        <v>-20.72332325607434</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-17.80855199222558</v>
+        <v>-13.25209444021314</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-18.46748323126288</v>
+        <v>-13.91023773779381</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-26.20575651497472</v>
+        <v>-21.0081585081585</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-34.67318354245685</v>
+        <v>-28.83438333744367</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-34.77816695855237</v>
+        <v>-21.24691634895716</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-42.89537712895377</v>
+        <v>-28.72333266034064</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-51.04166666666667</v>
+        <v>-36.2287945426803</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-34.91820040899808</v>
+        <v>-21.38672532603083</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-26.66082213130746</v>
+        <v>-13.77026359513225</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-26.38604696482533</v>
+        <v>-13.4957888826502</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-18.12865497076036</v>
+        <v>-13.57162113587347</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 16.56</t>
+          <t>X ≈ 16.53</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-30.59719832882772</v>
+        <v>-20.30751378009864</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-23.24006615116435</v>
+        <v>-13.97562391178178</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-9.295151230635156</v>
+        <v>-8.746976294146201</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-10.00894454382831</v>
+        <v>-2.79326364692227</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.681906636544568</v>
+        <v>-3.129054119469409</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.88987336107755</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.11700722902341</v>
+        <v>9.619296716070856</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>11.83845258350485</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.87996864852771</v>
+        <v>9.382572453232626</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.413825545450592</v>
+        <v>1.942990110529479</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.688184812565972</v>
+        <v>2.217049752691253</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.10139860139849</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.976907382911243</v>
+        <v>7.48180494905376</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.44785826418491</v>
+        <v>13.92739273927384</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>16.78892702514755</v>
+        <v>13.26924944169343</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>25.07629476707651</v>
+        <v>20.53030303030307</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>17.24989338061985</v>
+        <v>13.72971922665889</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>17.14490996452479</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.976417742841001</v>
+        <v>-6.159230096237962</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-12.63905095293651</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-13.76435425515169</v>
+        <v>-19.8482637875693</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-13.8403093107943</v>
+        <v>-19.9241097489784</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-5.873226452004481</v>
+        <v>-12.98296836982968</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-5.949167791272949</v>
+        <v>-6.392133956386381</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 17.18</t>
+          <t>X ≈ 17.15</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.99254526091599</v>
+        <v>13.02581955323482</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.009296920395002</v>
+        <v>-3.975623911781661</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>27.88433594885218</v>
+        <v>27.91969037252067</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.162790697674296</v>
+        <v>-6.126596980255393</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>43.47193951730141</v>
+        <v>43.53761254719709</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>43.65910413030832</v>
+        <v>43.72457873329459</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>42.88623799825441</v>
+        <v>42.95263004940436</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>42.64919941775824</v>
+        <v>42.71590578656574</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>41.87536400698894</v>
+        <v>41.94299011052938</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>25.48305660743749</v>
+        <v>25.55038308602452</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>25.20396270396259</v>
+        <v>25.27163368257652</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>24.0794714854758</v>
+        <v>24.14847161572076</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>23.85811467444122</v>
+        <v>23.92739273927394</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>23.19918343540379</v>
+        <v>23.26924944169325</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>23.79424348502517</v>
+        <v>23.86363636363625</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>40.32681645754303</v>
+        <v>40.39638589332556</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>40.43795620437981</v>
+        <v>40.50743657042894</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>40.625</v>
+        <v>40.69428238039673</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>40.08179959100205</v>
+        <v>40.1517362124307</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>40.00584453535944</v>
+        <v>40.0758902510216</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.35036496350365</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 17.8</t>
+          <t>X ≈ 17.77</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46.32587859424849</v>
+        <v>46.35915288656732</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>45.99070307960417</v>
+        <v>46.02437608821751</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>44.55100261551874</v>
+        <v>44.58635703918723</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>43.83720930232558</v>
+        <v>43.87340301974449</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>43.47193951730154</v>
+        <v>43.53761254719721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>43.65910413030832</v>
+        <v>43.72457873329459</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>42.88623799825429</v>
+        <v>42.95263004940424</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>42.64919941775908</v>
+        <v>42.71590578656658</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>41.87536400698965</v>
+        <v>41.94299011053009</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>42.14972327410428</v>
+        <v>42.2170497526913</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>41.87062937063008</v>
+        <v>41.93830034924402</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>40.74613815214152</v>
+        <v>40.81513828238648</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>40.52478134110716</v>
+        <v>40.59405940593989</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>39.86585010207128</v>
+        <v>39.93591610836075</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>40.46091015169267</v>
+        <v>40.53030303030374</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>40.32681645754374</v>
+        <v>40.39638589332627</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>40.43795620437957</v>
+        <v>40.5074365704287</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>40.62499999999929</v>
+        <v>40.69428238039602</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>40.08179959100134</v>
+        <v>40.15173621242999</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>40.00584453535873</v>
+        <v>40.07589025102089</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.35036496350365</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 18.42</t>
+          <t>X ≈ 18.39</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-33.67412140575065</v>
+        <v>-33.64084711343182</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-34.00929692039498</v>
+        <v>-33.97562391178164</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-15.44899738448126</v>
+        <v>-15.41364296081277</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-16.16279069767442</v>
+        <v>-16.12659698025551</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-16.34089586969168</v>
+        <v>-16.27542126670541</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>2.952630049404242</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>22.60768335273573</v>
+        <v>22.67441860465117</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>22.64919941775837</v>
+        <v>22.71590578656587</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.875364006988789</v>
+        <v>1.94299011052923</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.14972327410428</v>
+        <v>22.2170497526913</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>41.87062937062937</v>
+        <v>41.93830034924331</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>40.74613815214236</v>
+        <v>40.81513828238732</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>40.524781341108</v>
+        <v>40.59405940594073</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>39.86585010207043</v>
+        <v>39.9359161083599</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>40.46091015169181</v>
+        <v>40.53030303030289</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>40.32681645754289</v>
+        <v>40.39638589332542</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>40.22183304144775</v>
+        <v>40.29154518950438</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>40.43795620437943</v>
+        <v>40.50743657042856</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>40.62500000000013</v>
+        <v>40.69428238039686</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>40.08179959100217</v>
+        <v>40.15173621243083</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>40.00584453535956</v>
+        <v>40.07589025102173</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>40.28061970184157</v>
+        <v>40.35036496350365</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>40.2046783625731</v>
+        <v>40.27453271028038</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 19.05</t>
+          <t>X ≈ 19.01</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>46.3258785942492</v>
+        <v>46.35915288656803</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>45.99070307960488</v>
+        <v>46.02437608821822</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44.55100261551874</v>
+        <v>44.58635703918723</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>43.83720930232629</v>
+        <v>43.8734030197452</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>43.47193951730154</v>
+        <v>43.53761254719721</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>43.65910413030832</v>
+        <v>43.72457873329459</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>42.88623799825429</v>
+        <v>42.95263004940424</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>42.64919941775837</v>
+        <v>42.71590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41.87536400698894</v>
+        <v>41.94299011052938</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>42.14972327410428</v>
+        <v>42.2170497526913</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>41.87062937062937</v>
+        <v>41.93830034924331</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>40.74613815214223</v>
+        <v>40.81513828238719</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>40.52478134110788</v>
+        <v>40.5940594059406</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-60.13414989792872</v>
+        <v>-60.06408389163925</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-59.53908984830733</v>
+        <v>-59.46969696969626</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-59.67318354245697</v>
+        <v>-59.60361410667444</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-59.77816695855225</v>
+        <v>-59.70845481049562</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-59.56204379561972</v>
+        <v>-59.49256342957059</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-59.375</v>
+        <v>-59.30571761960327</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-59.91820040899795</v>
+        <v>-59.8482637875693</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-59.99415546464056</v>
+        <v>-59.9241097489784</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-59.71938029815843</v>
+        <v>-59.64963503649635</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-59.7953216374269</v>
+        <v>-59.72546728971962</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 19.67</t>
+          <t>X ≈ 19.63</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>46.32587859424849</v>
+        <v>46.35915288656732</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>45.99070307960417</v>
+        <v>46.02437608821751</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>44.55100261551803</v>
+        <v>44.58635703918652</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>43.83720930232487</v>
+        <v>43.87340301974378</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>43.47193951730154</v>
+        <v>43.53761254719721</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>43.65910413030832</v>
+        <v>43.72457873329459</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>42.88623799825429</v>
+        <v>42.95263004940424</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>42.60768335273573</v>
+        <v>42.67441860465117</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>42.64919941775908</v>
+        <v>42.71590578656658</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>41.87536400698894</v>
+        <v>41.94299011052938</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>42.14972327410428</v>
+        <v>42.2170497526913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>41.87062937062937</v>
+        <v>41.93830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>40.74613815214294</v>
+        <v>40.8151382823879</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>40.52478134110788</v>
+        <v>40.5940594059406</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>39.86585010206986</v>
+        <v>39.93591610835933</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-59.53908984830804</v>
+        <v>-59.46969696969697</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-59.67318354245697</v>
+        <v>-59.60361410667444</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-59.77816695855225</v>
+        <v>-59.70845481049562</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-59.56204379562114</v>
+        <v>-59.49256342957201</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-59.375</v>
+        <v>-59.30571761960327</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-59.91820040899795</v>
+        <v>-59.8482637875693</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-59.99415546464056</v>
+        <v>-59.9241097489784</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-59.71938029815843</v>
+        <v>-59.64963503649635</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-59.7953216374269</v>
+        <v>-59.72546728971962</v>
       </c>
     </row>
   </sheetData>
@@ -3184,2457 +3184,2457 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1033919791391469</v>
+        <v>0.1024683945894296</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.06701783678905571</v>
+        <v>-0.06774872604626836</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.06209262257649328</v>
+        <v>-0.0628700713954089</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.04489846784411355</v>
+        <v>-0.04571681373752767</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.006321352263682911</v>
+        <v>-0.007896078620753144</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01894923009980687</v>
+        <v>0.01734874222051275</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.09720343329600922</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01453879237805467</v>
+        <v>0.01291220393666492</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1328010874065413</v>
+        <v>0.1310338389780128</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1217105623125292</v>
+        <v>0.119933810261287</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.08528413329281648</v>
+        <v>0.08355750000954032</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1815813252697822</v>
+        <v>0.1797310496904032</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3282277043810353</v>
+        <v>0.3261698864420524</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4232584984682859</v>
+        <v>0.4210799845269406</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.3795896480681904</v>
+        <v>0.3774435546607506</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.3951796467621662</v>
+        <v>0.3930305743197451</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.3985438932872043</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.4609959711936469</v>
+        <v>0.45875928326371</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.4858030943317146</v>
+        <v>0.4835417078241662</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.5113296440323083</v>
+        <v>0.5090418665036864</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.5246481846585382</v>
+        <v>0.522327963775588</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.5565778487386623</v>
+        <v>0.5542161105133729</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.550080779685878</v>
+        <v>0.5477333845562811</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.5221386800334145</v>
+        <v>0.5198213731580239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 2.564</t>
+          <t>X &gt; 2.563</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3165</v>
+        <v>3169</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2236822589502978</v>
+        <v>-0.2260601460134168</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3851990226856756</v>
+        <v>-0.3874070518632564</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5839628584297856</v>
+        <v>-0.5860567539162247</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5583950932788113</v>
+        <v>-0.5605888272294877</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5607237992813765</v>
+        <v>-0.5652732746346558</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5130604942596975</v>
+        <v>-0.5176553426388892</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6398462255043498</v>
+        <v>-0.6443567679215576</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6177174646173</v>
+        <v>-0.6222846920521334</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5583477520529527</v>
+        <v>-0.5629886857959363</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.4964510291859625</v>
+        <v>-0.5012448878997731</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.4556889348321604</v>
+        <v>-0.4605115295211348</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3075261219737158</v>
+        <v>-0.3125641587730428</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09139333400386818</v>
+        <v>-0.09681140314739878</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2413167741787348</v>
+        <v>0.2354560715587155</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.2628255274013895</v>
+        <v>0.2568726848232217</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.3411496726500332</v>
+        <v>0.3351503705611378</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.4466146920953662</v>
+        <v>0.4404664978595605</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.549805289949802</v>
+        <v>0.5435136934413762</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.6587763936540156</v>
+        <v>0.6523641066605848</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6123777216787616</v>
+        <v>0.6060378168921545</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.6878601970626548</v>
+        <v>0.6813705125567964</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.6310418830070574</v>
+        <v>0.6246130514000257</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.5459387163709408</v>
+        <v>0.5396394114531802</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.5206341287658276</v>
+        <v>0.514355998383877</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 3.186</t>
+          <t>X &gt; 3.184</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2883</v>
+        <v>2888</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3017883018278766</v>
+        <v>-0.325835090072303</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5841678326154351</v>
+        <v>-0.6079263172800609</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7658017921947575</v>
+        <v>-0.7900609738756899</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5995802257488236</v>
+        <v>-0.6245337065278633</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.6355725433462851</v>
+        <v>-0.6660338236318211</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5670247907533792</v>
+        <v>-0.5975134896923251</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7344516569181252</v>
+        <v>-0.7650980056732095</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9245691481266363</v>
+        <v>-0.9550579793708778</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6565286705784104</v>
+        <v>-0.6874700315533104</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3407215988101626</v>
+        <v>-0.3726542726546356</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04640932258081421</v>
+        <v>-0.07871033003878836</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2816829112165919</v>
+        <v>0.2486451768295055</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.5940994513820357</v>
+        <v>0.5598778477545565</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.9810551053664227</v>
+        <v>0.9460262796466097</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.172904043979294</v>
+        <v>1.137158773185725</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.201138446399668</v>
+        <v>1.165662146325133</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.39948081740463</v>
+        <v>1.363570694707249</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.69639171226811</v>
+        <v>1.659893496346122</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.55291465313303</v>
+        <v>1.516769442879443</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.518661240041567</v>
+        <v>1.482664123135315</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.516311025513474</v>
+        <v>1.479996330037061</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.600298608149728</v>
+        <v>1.563779524377999</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.549690436931712</v>
+        <v>1.513397154573227</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.425628761463152</v>
+        <v>1.389491159033838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 3.808</t>
+          <t>X &gt; 3.804</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2626</v>
+        <v>2628</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4440496263779181</v>
+        <v>-0.453370689441023</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4189719014986792</v>
+        <v>-0.4284541004610318</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.628581505464247</v>
+        <v>-0.6382560223454306</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.6786757203673091</v>
+        <v>-0.6885305149987175</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4554157607915386</v>
+        <v>-0.4744766103396216</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3984280422881952</v>
+        <v>-0.4175225516638292</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.695738525789622</v>
+        <v>-0.7146667369851656</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.687771192718813</v>
+        <v>-0.7068219399781839</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2458365807259071</v>
+        <v>-0.2655546750307991</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2019673046107613</v>
+        <v>-0.2220363845501012</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.01851356610276156</v>
+        <v>-0.00180674106106693</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.102799325105849</v>
+        <v>0.08223974318269711</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5563848314591198</v>
+        <v>0.5347290364607034</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.15500153852625</v>
+        <v>1.132345986683582</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.126769205754584</v>
+        <v>1.103910040859091</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.213189786950309</v>
+        <v>1.19039407734401</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.520279019306621</v>
+        <v>1.496955153287601</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.628677147911631</v>
+        <v>1.605136685328212</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.601896866228181</v>
+        <v>1.578458218738611</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.507800608828006</v>
+        <v>1.484555936627729</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.520703283426862</v>
+        <v>1.4972322215527</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.696628998421126</v>
+        <v>1.672848425926546</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.857161971453145</v>
+        <v>1.856641114131264</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.666978438734553</v>
+        <v>1.690057824435634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 4.43</t>
+          <t>X &gt; 4.425</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1739092716820565</v>
+        <v>-0.2144511743456761</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01948367761074365</v>
+        <v>-0.01878937940768566</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4171502507232958</v>
+        <v>-0.4178766610667992</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3429096441485058</v>
+        <v>-0.3451484415007471</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2169682600040304</v>
+        <v>-0.2335738934807523</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2184468900998482</v>
+        <v>-0.1923352132929423</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3294149153994752</v>
+        <v>-0.3043674060664969</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.05449186337403944</v>
+        <v>0.03547078963207184</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2481777063918287</v>
+        <v>0.2286392330853957</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.09512550613715121</v>
+        <v>0.1170877750729034</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4795059754251056</v>
+        <v>0.5008220551551901</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.267901322888541</v>
+        <v>0.2893415732127096</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.6182063824194159</v>
+        <v>0.5940498470130322</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.232972467387739</v>
+        <v>1.206564722827032</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.325517195540478</v>
+        <v>1.297618236019616</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.434437051777351</v>
+        <v>1.407271953248973</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.838990742036835</v>
+        <v>1.810355228930327</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.016704836319548</v>
+        <v>1.987327038673527</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.959974160771182</v>
+        <v>1.931136485177213</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.933251389482685</v>
+        <v>1.930956154383935</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.817584114302598</v>
+        <v>1.841156007652543</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.040902252332501</v>
+        <v>2.090401561307559</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.144664165287487</v>
+        <v>2.220561376825593</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.94046288587365</v>
+        <v>2.016633478854246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 5.052</t>
+          <t>X &gt; 5.045</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8936336008727466</v>
+        <v>-0.8765406148868706</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.568594138550317</v>
+        <v>-0.6034744697633485</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.6150130094812596</v>
+        <v>-0.7534487860554933</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6940406976744171</v>
+        <v>-0.7113468588373451</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1315761076984643</v>
+        <v>-0.09698414862396731</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.01456465327741796</v>
+        <v>0.02015481496692928</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.0756388345902721</v>
+        <v>0.005159232283617143</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2604950886770538</v>
+        <v>0.3106053750791773</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4769880674648235</v>
+        <v>0.4980069538810383</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2209342468323072</v>
+        <v>0.2398270934977518</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3279798852697979</v>
+        <v>0.3475268705101939</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2165827802770437</v>
+        <v>-0.1951628753061314</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1579028580245847</v>
+        <v>0.1718634285860148</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6522948281113088</v>
+        <v>0.6623187916061326</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.7588824867614434</v>
+        <v>0.7651844010429656</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.9911016097184628</v>
+        <v>0.9988242601712614</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.427012921197253</v>
+        <v>1.431542143325558</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.813188640661899</v>
+        <v>1.84503810596749</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.68550040870177</v>
+        <v>1.748883295746396</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.823428290766202</v>
+        <v>1.91677626792729</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.525807449548211</v>
+        <v>1.648800791687052</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.597200134573583</v>
+        <v>1.719725867459957</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.01932304172368</v>
+        <v>2.140971617124002</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.746918048231251</v>
+        <v>1.869444647658071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 5.674</t>
+          <t>X &gt; 5.666</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.731045324743683</v>
+        <v>-1.677924539822371</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.490129340986577</v>
+        <v>-1.493354408235682</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.750367247494957</v>
+        <v>-1.756437720638097</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.244982478496333</v>
+        <v>-2.221627018485989</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.678745414205309</v>
+        <v>-1.653644283403878</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.009755518814487</v>
+        <v>-1.983458445491628</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.929998973769841</v>
+        <v>-1.905138003112171</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.62941873288446</v>
+        <v>-1.636303496005283</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.117961482845693</v>
+        <v>-1.157179552602628</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.421339289714361</v>
+        <v>-1.461498121545056</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.115807237165662</v>
+        <v>-1.156444223212304</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.583716063914075</v>
+        <v>-1.62334348637313</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.41126415936025</v>
+        <v>-1.399773998314565</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.050108526733538</v>
+        <v>-1.040608723516343</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.180981853852295</v>
+        <v>-1.172755680882553</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7739299806123441</v>
+        <v>-0.7656881833158593</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3240384790261928</v>
+        <v>-0.3178998209601573</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.06739288700759971</v>
+        <v>0.1046293016539011</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1025843361609731</v>
+        <v>-0.03161733496184382</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.02585493656922466</v>
+        <v>0.07788171996745064</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.182954959466791</v>
+        <v>-0.04650167303185526</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.09343842106638078</v>
+        <v>0.04285060344449931</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.4571227354874523</v>
+        <v>0.5926557124023262</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.2157098021759651</v>
+        <v>0.3516252212935953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 6.296</t>
+          <t>X &gt; 6.287</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.014760103308724</v>
+        <v>-2.116267150768614</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.004284389066804</v>
+        <v>-2.04536239247917</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.470940958148972</v>
+        <v>-2.516446699130526</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.495079098928336</v>
+        <v>-2.51063688050489</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.669126313419468</v>
+        <v>-1.752468550744148</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.137633636316515</v>
+        <v>-2.15557107943949</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.374276753785878</v>
+        <v>-2.394028289134177</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.115934737716529</v>
+        <v>-2.110091076797929</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.411139991418253</v>
+        <v>-1.443994275895093</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.024007062193455</v>
+        <v>-2.057009889470613</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.651409513812652</v>
+        <v>-1.685389271698938</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.147002871184228</v>
+        <v>-2.179346709580223</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.786943133302003</v>
+        <v>-1.827316319992278</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.530704157000571</v>
+        <v>-1.573860393558142</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.522162516225961</v>
+        <v>-1.506090161232443</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.8900999493181416</v>
+        <v>-0.8749667313029903</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5449460187677673</v>
+        <v>-0.5326787645526636</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.04495369842817354</v>
+        <v>0.02772609402699544</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.05477910831784527</v>
+        <v>-0.09595752133748903</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1322646873025874</v>
+        <v>0.1282446445476708</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.03126263585359368</v>
+        <v>0.1265631476100566</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.1448211620176849</v>
+        <v>0.239515172355766</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.6722811042420744</v>
+        <v>0.7657205330442451</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.2804837952957726</v>
+        <v>0.3752249695629502</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 6.918</t>
+          <t>X &gt; 6.907</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.237128038027876</v>
+        <v>-2.247885236599124</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.165639103285976</v>
+        <v>-2.104750837680541</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.238665281160223</v>
+        <v>-2.25652108122393</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.657255642323868</v>
+        <v>-2.636516157331187</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.841713619229829</v>
+        <v>-1.830034511626323</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.613958600318981</v>
+        <v>-2.559453643453018</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.501215876284448</v>
+        <v>-2.408194692863802</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.51787056159219</v>
+        <v>-2.465493030105826</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.918428076698397</v>
+        <v>-1.908541930665351</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.503334217863134</v>
+        <v>-2.534182201694477</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.450868441872061</v>
+        <v>-2.554673369547281</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.762975366602305</v>
+        <v>-2.866415936681534</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.068676662672587</v>
+        <v>-2.178962012598063</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.876997754518513</v>
+        <v>-1.988966424317702</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.751360580422002</v>
+        <v>-1.909102341824465</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.9644796033191767</v>
+        <v>-1.124054429076587</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.757878936216251</v>
+        <v>-0.8452992507986181</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1199203017914741</v>
+        <v>-0.1670346921524342</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.2009739590676816</v>
+        <v>-0.2031481816068279</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2368127786032659</v>
+        <v>-0.1946065084921571</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1856595471851747</v>
+        <v>-0.1003023346411993</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.03873198767176689</v>
+        <v>0.04623865724843057</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.4589257939663796</v>
+        <v>0.543100323029222</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.2343960445939004</v>
+        <v>0.3190101009401189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 7.54</t>
+          <t>X &gt; 7.528</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.952951009881609</v>
+        <v>-1.845975318560164</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.943892445352091</v>
+        <v>-1.838871775029638</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.350890671916716</v>
+        <v>-2.376859385107046</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.720449905936029</v>
+        <v>-2.701939446008936</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.708783374264726</v>
+        <v>-1.620913588192671</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.468262478985999</v>
+        <v>-2.37653523414329</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.294484893311967</v>
+        <v>-2.205896085985643</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.831215098210905</v>
+        <v>-2.741176939479082</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.656571469407872</v>
+        <v>-2.528310151737472</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.999743658816399</v>
+        <v>-2.872776813206698</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.156047613061965</v>
+        <v>-3.027166185612039</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.349008872264683</v>
+        <v>-3.134535983233135</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.75084720530824</v>
+        <v>-2.495324839396694</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.886071372070418</v>
+        <v>-2.630640422532814</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.425278235569387</v>
+        <v>-2.259624200387819</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.830218185948006</v>
+        <v>-1.665237278444827</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.964311880096929</v>
+        <v>-1.799154415422301</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.121836209198243</v>
+        <v>-1.04636218613885</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.164110979082963</v>
+        <v>-1.087760685145909</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.493863049095609</v>
+        <v>-1.329731341730202</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.261869659643949</v>
+        <v>-1.014644576591593</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.9071614939256705</v>
+        <v>-0.7474373647588521</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2017231060826319</v>
+        <v>-0.2156727723454068</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1053991568067545</v>
+        <v>-0.1199784389477543</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 8.162</t>
+          <t>X &gt; 8.148</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.601320596852915</v>
+        <v>-1.572229555409763</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.633159407756089</v>
+        <v>-1.604281833073408</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.859513056877617</v>
+        <v>-1.831402799359694</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.573306370070775</v>
+        <v>-2.544356818802434</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.624117105549828</v>
+        <v>-1.568341035042955</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.650299307507652</v>
+        <v>-2.491364758128213</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.614267562918606</v>
+        <v>-2.456048053522096</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.387261035535253</v>
+        <v>-2.330626804026934</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.042408266771467</v>
+        <v>-1.986415101426061</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.816243677540896</v>
+        <v>-2.759330777462552</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.744108879586321</v>
+        <v>-2.687087482424744</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.820978313900461</v>
+        <v>-2.764020538748625</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.024337075360293</v>
+        <v>-1.96992730792563</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.942357182653495</v>
+        <v>-1.888281663686044</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.893502779628115</v>
+        <v>-1.840067746332195</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.096218260845959</v>
+        <v>-1.043864477265082</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.129199720414505</v>
+        <v>-1.076873440680494</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.3241730252863206</v>
+        <v>-0.2735405824431538</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.613611035256433</v>
+        <v>-0.5621900693291124</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.033240647118305</v>
+        <v>-0.8798851271713843</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.9697676486339546</v>
+        <v>-0.8169822537650688</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7423860005354115</v>
+        <v>-0.5901036944879863</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.543511511750566</v>
+        <v>0.6934527536146433</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.4675701724820982</v>
+        <v>0.5167123268293139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 8.784</t>
+          <t>X &gt; 8.769</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.9987349610421106</v>
+        <v>-1.09646841520712</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9771922830586135</v>
+        <v>-0.9578724324918397</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.70345636188911</v>
+        <v>-1.567489114658926</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.417249675082267</v>
+        <v>-2.280443134101667</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.593458818013566</v>
+        <v>-1.432801653986218</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.952073039727345</v>
+        <v>-2.784297006350378</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.130408850735002</v>
+        <v>-2.964529713909364</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.814433175207192</v>
+        <v>-2.76936837759736</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.297292853347464</v>
+        <v>-2.254508414617561</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.952222199907617</v>
+        <v>-2.909080895387781</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.391299318047928</v>
+        <v>-3.345080424823493</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.432581093104275</v>
+        <v>-3.387143437738942</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.535669220033753</v>
+        <v>-2.380127989802162</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.400307838440284</v>
+        <v>-2.246177280449935</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.107990563803391</v>
+        <v>-1.957575015900311</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.037306257344902</v>
+        <v>-0.8898153128922388</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.6957756946567315</v>
+        <v>-0.5503596688046244</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.08732272549636377</v>
+        <v>0.05485879897183565</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.3666125658539983</v>
+        <v>0.3890933751624317</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.07803210463733734</v>
+        <v>0.1025664040653638</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.01045595247647668</v>
+        <v>0.03339301716442833</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2912190894616913</v>
+        <v>0.430919836820415</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.279430641199475</v>
+        <v>1.415453720900096</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.9656771735124607</v>
+        <v>1.102935077144288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 9.406</t>
+          <t>X &gt; 9.39</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.786009517638909</v>
+        <v>-1.696402668987517</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.701604612702809</v>
+        <v>-1.614512800670667</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.442004377488253</v>
+        <v>-2.080309627479437</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.01593755082127</v>
+        <v>-2.654374758033292</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.122466077104058</v>
+        <v>-1.740165230580558</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.914322443118245</v>
+        <v>-2.525421266705408</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.428447316431019</v>
+        <v>-2.186258839484644</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.147561402509027</v>
+        <v>-2.047803617571056</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.546604778045833</v>
+        <v>-1.450760880100795</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.180580048955115</v>
+        <v>-2.223676556137285</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.745381621000625</v>
+        <v>-2.644061358419805</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.72377622377622</v>
+        <v>-3.478366317423365</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.169945763941683</v>
+        <v>-2.934861717612812</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.831862015535478</v>
+        <v>-2.600385038503845</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.791492555272079</v>
+        <v>-2.564083891639967</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.056572365790565</v>
+        <v>-1.830808080808083</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.631225500498928</v>
+        <v>-1.409169662229992</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.176768357153648</v>
+        <v>-1.09734369938451</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8207850543616928</v>
+        <v>-1.02034120734907</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.05332167832168</v>
+        <v>-1.3890509529366</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.456661947459487</v>
+        <v>-1.792708232013744</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6934561639412635</v>
+        <v>-0.8963319712006239</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.0008994221212859088</v>
+        <v>-0.2051905920519062</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.06481822271295812</v>
+        <v>-0.1421339563862887</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 10.03</t>
+          <t>X &gt; 10.01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4024176957467063</v>
+        <v>0.3458638500231856</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.598315223223743</v>
+        <v>-0.653364775569159</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.03801568730988</v>
+        <v>-2.09138382460015</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.58541964942151</v>
+        <v>-2.472111930421626</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.617910732282496</v>
+        <v>-2.475676489347634</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.43074611927571</v>
+        <v>-2.454823260060891</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.037222900248203</v>
+        <v>-2.894546030329977</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.151052088196053</v>
+        <v>-2.009966777408636</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.277589267765762</v>
+        <v>-1.137914811440773</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.217814029616726</v>
+        <v>-2.076943444287899</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.27623346466445</v>
+        <v>-2.30122267255787</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.721716719220879</v>
+        <v>-2.746085032816495</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.515093129055771</v>
+        <v>-2.374230488376938</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.571724482519407</v>
+        <v>-1.432518667149104</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.232319615067524</v>
+        <v>-1.093984223865867</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.9700382676092048</v>
+        <v>-0.8318232155441407</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.4385745574320055</v>
+        <v>-0.3012885252790909</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.210779271364224</v>
+        <v>-0.07390331547901496</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1717332426491183</v>
+        <v>0.308101022255947</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1403910149750374</v>
+        <v>-0.003392038207920223</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6835914239729917</v>
+        <v>-0.5459382061739504</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.2603784263710125</v>
+        <v>-0.1234452971511573</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.3471754422741782</v>
+        <v>0.4832553289521613</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.1048447519241833</v>
+        <v>0.2413101189182498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 10.65</t>
+          <t>X &gt; 10.63</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2193212172000187</v>
+        <v>0.5173678967100201</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4988998009163552</v>
+        <v>0.5882706115447931</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9408006631697816</v>
+        <v>-1.255427950670786</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.269348074723602</v>
+        <v>-2.576901239890404</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.224781794173872</v>
+        <v>-2.3041724426608</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.037617181167086</v>
+        <v>-2.117206256563421</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.990811182073571</v>
+        <v>-2.077795914084597</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.064447794805247</v>
+        <v>-2.356007358837672</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.613095664208849</v>
+        <v>-1.706000907146098</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.772176976617622</v>
+        <v>-2.073237069998001</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.2928996767154</v>
+        <v>-1.596337671243788</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7523214490427605</v>
+        <v>-1.063728048322623</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1723676603389563</v>
+        <v>0.04434720733648589</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.205109209960334</v>
+        <v>1.648826140220521</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.546177970923033</v>
+        <v>1.396362355824543</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.116647856609987</v>
+        <v>0.9765504948060766</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.597308260821727</v>
+        <v>1.248312871013191</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.697242877513325</v>
+        <v>1.549151680376582</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.708448007658262</v>
+        <v>1.562203304708625</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.6659836065573757</v>
+        <v>0.5320105751228965</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.08213483522746401</v>
+        <v>-0.01053559284313366</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.6615822402774683</v>
+        <v>0.5221377155246429</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.346193472333361</v>
+        <v>1.405131697783574</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.450580001917352</v>
+        <v>0.5179404181911238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 11.27</t>
+          <t>X &gt; 11.25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.229493052080535</v>
+        <v>2.549629077044223</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.894317537436208</v>
+        <v>1.738661802503934</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.177508639615134</v>
+        <v>0.7768332296634171</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.982067806108148</v>
+        <v>-1.126596980255506</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8213371076629841</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7675378652480802</v>
+        <v>0.6293406380564974</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.681418721145867</v>
+        <v>1.524058620832818</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.643827931048989</v>
+        <v>1.483942414174976</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.408235562336685</v>
+        <v>2.239715310375395</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.116327862410628</v>
+        <v>1.942990110529379</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.87261484036933</v>
+        <v>2.693240228881777</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.557376358581188</v>
+        <v>3.366871777814737</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.878668272624154</v>
+        <v>3.672281139530043</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.307913871228358</v>
+        <v>6.07024988213108</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>5.167054921347678</v>
+        <v>4.93591610836004</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>4.316331838438934</v>
+        <v>4.101731601731601</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.66416585513339</v>
+        <v>4.444004940944595</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>4.800146294459793</v>
+        <v>4.577259475218668</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.775305601969926</v>
+        <v>4.555055618047739</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>3.516566265060241</v>
+        <v>3.313329999444349</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.732402000640604</v>
+        <v>2.532688593383078</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.37933851126305</v>
+        <v>3.171128346259692</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>4.136041388588545</v>
+        <v>3.92179353493222</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.337208483055022</v>
+        <v>3.369770805518471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 11.89</t>
+          <t>X &gt; 11.87</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.645027530419419</v>
+        <v>1.780839633555985</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.525657486899711</v>
+        <v>2.650882112314612</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.909665229500497</v>
+        <v>3.020091978946269</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.0682123418392635</v>
+        <v>0.49990904384088</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3108452923775218</v>
+        <v>0.7665282098478201</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.021746933521463</v>
+        <v>-0.5525297004403456</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5788075944508719</v>
+        <v>-0.420863926499365</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3584432311551922</v>
+        <v>0.5057439058559794</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.615764767302444</v>
+        <v>1.752050364879125</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.841929356533015</v>
+        <v>0.9791346888426347</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.724191359210657</v>
+        <v>1.855603969558771</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.660902926860373</v>
+        <v>2.78167384321921</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.752217179497848</v>
+        <v>2.863331053471533</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.570374046275056</v>
+        <v>5.955505189073136</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>4.303540071675435</v>
+        <v>4.694952252938343</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.682794650172198</v>
+        <v>4.084519897772914</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.764506427147893</v>
+        <v>5.155422037903861</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>4.659523011052613</v>
+        <v>5.050581334082679</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.571694806203276</v>
+        <v>4.965267895729916</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>4.150835866261396</v>
+        <v>4.549704067143708</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.303684089482289</v>
+        <v>3.705953079900581</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.835631769401992</v>
+        <v>4.232516757045694</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>4.718309671446427</v>
+        <v>5.109401108081954</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>3.730514228834494</v>
+        <v>4.129954397027355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 12.52</t>
+          <t>X &gt; 12.49</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.9649763386101</v>
+        <v>1.956167811941164</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.509500072086077</v>
+        <v>3.487062655382395</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.453258254616486</v>
+        <v>5.407252561575291</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.73194614443085</v>
+        <v>1.336089586908663</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.494495908278978</v>
+        <v>2.119702099436019</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.553840972413589</v>
+        <v>1.560399628816974</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.660674088479865</v>
+        <v>2.654122586717669</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.261818691081594</v>
+        <v>4.241582783755639</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.431154304976417</v>
+        <v>5.402472950744979</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.777619646086684</v>
+        <v>2.763885632917443</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.67603906357796</v>
+        <v>3.037945275079366</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.524764708975233</v>
+        <v>3.50546452834778</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.40027349048809</v>
+        <v>2.382302461491662</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.434555777198106</v>
+        <v>4.40002955519433</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.271865139664563</v>
+        <v>2.622483272539149</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.363165790789701</v>
+        <v>1.7243328810493</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>2.73283149513702</v>
+        <v>3.082953057504668</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.62784807904174</v>
+        <v>2.978112353683485</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.468031392349495</v>
+        <v>2.820869406249592</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.527255639097746</v>
+        <v>1.888312231142997</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.9840552300997913</v>
+        <v>1.345766063176967</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.659979873705296</v>
+        <v>2.016188758484283</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.686634739435554</v>
+        <v>3.036932127682761</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.858813700918958</v>
+        <v>2.214831217743061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 13.14</t>
+          <t>X &gt; 13.11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.022307165677773</v>
+        <v>3.248041775456919</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.133560222462016</v>
+        <v>3.357709421551554</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.818859758375879</v>
+        <v>5.03080148363167</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.872923588039875</v>
+        <v>2.095625241966708</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.186225231587244</v>
+        <v>4.426501436086106</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.480532701736891</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.939809426825725</v>
+        <v>5.174852271626463</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.446969067021442</v>
+        <v>6.674418604651166</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7.827770846329798</v>
+        <v>8.049239119899198</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.268221149846077</v>
+        <v>5.498545666084937</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.649723274104275</v>
+        <v>4.883716419357974</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.263486513486512</v>
+        <v>5.493855904798863</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.585423866427938</v>
+        <v>4.815138282387188</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.596209912536445</v>
+        <v>6.816281628162827</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.812278673499144</v>
+        <v>3.047027219471147</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.514481580263386</v>
+        <v>2.752525252525253</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.273245028971601</v>
+        <v>3.507497004436665</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>2.958211856171047</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.174103237095373</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.232142857142861</v>
+        <v>2.472060158174507</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.688942448144907</v>
+        <v>1.929513990208477</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.505844535359437</v>
+        <v>2.742556917688269</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.673476844698705</v>
+        <v>3.905920519059208</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.151106934001668</v>
+        <v>3.385643821391483</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 13.76</t>
+          <t>X &gt; 13.73</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.655827832827882</v>
+        <v>1.63553479611577</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.320652318183555</v>
+        <v>1.803270560580025</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.449479772879151</v>
+        <v>4.887864576875664</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6900011804981787</v>
+        <v>1.159835180548512</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.878030887859914</v>
+        <v>3.83912008488565</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.049967074470757</v>
+        <v>2.518548582540824</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.322786221604545</v>
+        <v>4.761675275534898</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.582302642075831</v>
+        <v>6.996026644852165</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.623818707098465</v>
+        <v>7.540026389580945</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.327140656735132</v>
+        <v>5.259573025102242</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.571043071058583</v>
+        <v>3.523582416007883</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.830020233573542</v>
+        <v>5.757395826630237</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.720757441482327</v>
+        <v>6.141771448216339</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.529857483239859</v>
+        <v>7.930742823026023</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.840469391410672</v>
+        <v>4.760036711375115</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.912686801438149</v>
+        <v>3.344373382061832</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.793821533685161</v>
+        <v>4.717993933526557</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.673609691193946</v>
+        <v>4.110640666891307</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.889732854125761</v>
+        <v>4.326532047815633</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.06154822335025</v>
+        <v>3.508352732155529</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.518347814352296</v>
+        <v>2.463294001375424</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.965235398303605</v>
+        <v>3.39247316559446</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.240010564785734</v>
+        <v>4.169460440890582</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.656455012319292</v>
+        <v>3.088603062039176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 14.38</t>
+          <t>X &gt; 14.35</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.575878594249204</v>
+        <v>2.531992392740875</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8842969203951228</v>
+        <v>-0.8892041586953567</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.676002615518748</v>
+        <v>3.228332347829209</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.96220930232559</v>
+        <v>1.898094377769183</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.096939517301529</v>
+        <v>4.648723658308327</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.034104130308322</v>
+        <v>2.983837992553845</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.886237998254295</v>
+        <v>7.767444864219051</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.482683352735734</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.899199417758368</v>
+        <v>8.765288502615263</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.875364006988939</v>
+        <v>6.757804925344189</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.649723274104275</v>
+        <v>4.562728765036979</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.120629370629374</v>
+        <v>7.9876830652927</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.62113815214223</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>11.14978134110788</v>
+        <v>10.96442977631096</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.740850102070574</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.710910151691955</v>
+        <v>6.579685746352425</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.951816457543032</v>
+        <v>6.445768609374952</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.846833041447752</v>
+        <v>5.723643954936477</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.062956204379567</v>
+        <v>5.939535335860803</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5</v>
+        <v>4.89181324459426</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.456799591002046</v>
+        <v>4.34926707662823</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>5.630844535359437</v>
+        <v>6.125272967070991</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.655619701841566</v>
+        <v>5.165179778318461</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.954678362573091</v>
+        <v>4.472063574477907</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 15</t>
+          <t>X &gt; 14.98</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-2.834395500528743</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.10765757613283</v>
+        <v>-8.007881976297909</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5309645975960109</v>
+        <v>-0.5749332833934204</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4250857796416341</v>
+        <v>-0.4814356899329368</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.668660828776943</v>
+        <v>1.602128676229476</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.036153310636188</v>
+        <v>0.9826432494236315</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.000992096614951</v>
+        <v>6.662307468759082</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.181453844539007</v>
+        <v>8.803450862715678</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.403297778414114</v>
+        <v>8.038486431727151</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.629462367644685</v>
+        <v>6.459119142787443</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.44480524131739</v>
+        <v>4.313823946239687</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.264071993580188</v>
+        <v>8.067332607307819</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.598597168535669</v>
+        <v>9.363525379161381</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.83625675094394</v>
+        <v>11.56180134142447</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.07896485616893</v>
+        <v>6.871399979327784</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.674024905790311</v>
+        <v>7.465786901270775</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.261242687051237</v>
+        <v>4.106063312680398</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.975931402103498</v>
+        <v>4.80767422176244</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.192054565035313</v>
+        <v>5.023565602686766</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.379098360655746</v>
+        <v>5.210411412654793</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.655570082805319</v>
+        <v>5.47431685759198</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.858303551752876</v>
+        <v>8.62427734779579</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>9.133078718235005</v>
+        <v>8.898752060277843</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>9.876809510114079</v>
+        <v>8.822919807054568</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 15.63</t>
+          <t>X &gt; 15.6</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.60004733167672</v>
+        <v>-3.19039666298152</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-8.638926550024749</v>
+        <v>-8.02967796583583</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.74529368077755</v>
+        <v>-1.359588906758717</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-0.2707411243996631</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.58305062841265</v>
+        <v>4.798873808458467</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.918363389567574</v>
+        <v>3.184038192754052</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.849200961217257</v>
+        <v>6.015693112467304</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.348424093476481</v>
+        <v>8.440184370416944</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.038612162993161</v>
+        <v>6.181013716655265</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.38914788914789</v>
+        <v>10.40676881771178</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>12.04243444843852</v>
+        <v>11.98630945355836</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>16.4507072670338</v>
+        <v>16.26973508161628</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>11.16214639836686</v>
+        <v>11.10708727953121</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.75720644798825</v>
+        <v>11.7014742014742</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.919409050135627</v>
+        <v>7.963953460893123</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>8.740351559966271</v>
+        <v>8.760013657972848</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>8.956474722898086</v>
+        <v>8.975905038897174</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.217592592592595</v>
+        <v>8.261849947964294</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.600318109520565</v>
+        <v>8.620204680899171</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>12.22806675758165</v>
+        <v>12.14796232309367</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>12.50284192406378</v>
+        <v>12.42243703557573</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>13.35282651072125</v>
+        <v>13.24750568325334</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 16.25</t>
+          <t>X &gt; 16.22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.757454739084125</v>
+        <v>-4.661255276697275</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.217630253728451</v>
+        <v>-8.057256564843001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2406640511479239</v>
+        <v>-0.3116021444862511</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.9544573643410814</v>
+        <v>-0.004148000663683149</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.971939517301536</v>
+        <v>5.782510506380888</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.159104130308322</v>
+        <v>4.949068529212958</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.279160661649136</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.39935001940239</v>
+        <v>12.06217370669198</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>13.48253275109171</v>
+        <v>13.124069051872</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.70869734032228</v>
+        <v>12.35115337583551</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.858056607437618</v>
+        <v>9.563988528201499</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.78729603729603</v>
+        <v>14.38727994108004</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.78780481880889</v>
+        <v>16.32534236401984</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>20.73311467444122</v>
+        <v>20.18589614063447</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>14.86585010207057</v>
+        <v>14.42571202672739</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>16.50257681835861</v>
+        <v>16.04050711193568</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>13.24348312420969</v>
+        <v>12.84536548516229</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>14.18016637478109</v>
+        <v>12.74052478134111</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>13.97682432553075</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>15.625</v>
+        <v>14.16367013549878</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>14.04013292433539</v>
+        <v>12.60071580426743</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>17.08917786869278</v>
+        <v>15.58609433265425</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>17.36395303517491</v>
+        <v>15.8605690451363</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>17.28801169590644</v>
+        <v>16.80514495517833</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 16.87</t>
+          <t>X &gt; 16.84</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>83</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.866892490088148</v>
+        <v>-1.833618197769319</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.021345113166205</v>
+        <v>-6.987672104552864</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.177508639615134</v>
+        <v>1.212863063283621</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.4637153264219762</v>
+        <v>0.49990904384088</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.327361204048515</v>
+        <v>7.393034233944192</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.104887262838439</v>
+        <v>5.170361865824709</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.151298239218157</v>
+        <v>9.217690290368104</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12.48720142502489</v>
+        <v>12.55393667694032</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.73353676715595</v>
+        <v>13.80024313596346</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>14.16452063349497</v>
+        <v>14.23214673703541</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.82442206928499</v>
+        <v>10.89174854787202</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>15.36460527424383</v>
+        <v>15.43227625285776</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>17.854571887082</v>
+        <v>17.92357201732695</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>21.24767290737294</v>
+        <v>21.31695097220566</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>14.56464528279346</v>
+        <v>14.63471128908292</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>15.15970533241484</v>
+        <v>15.22909821102591</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>12.61597308404906</v>
+        <v>12.68554251983159</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>13.71580894506221</v>
+        <v>13.78552109311883</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>17.54638993931933</v>
+        <v>17.61587030536847</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>18.93825301204819</v>
+        <v>19.00753539244492</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>18.39505260305024</v>
+        <v>18.46498922447889</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>21.93355537873293</v>
+        <v>22.00360109439509</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>21.00351126810663</v>
+        <v>21.07325652976871</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>20.92756992883816</v>
+        <v>20.99742427654544</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 17.49</t>
+          <t>X &gt; 17.46</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>77</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.024770756400152</v>
+        <v>-2.991496464081322</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-7.256050167148373</v>
+        <v>-7.222377158535032</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.9035428390267199</v>
+        <v>-0.8681884153582331</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>1.016260162601625</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.51090055626257</v>
+        <v>4.576573586158247</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.100662571866764</v>
+        <v>2.166137174853034</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.522601634617928</v>
+        <v>6.588993685767875</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.14015088520327</v>
+        <v>10.2068861371187</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.48036824892721</v>
+        <v>11.54707461773471</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.00523413685907</v>
+        <v>12.07286024039951</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.682190806571811</v>
+        <v>9.749517285158838</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.59790209790211</v>
+        <v>14.66557307651604</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.36951477551886</v>
+        <v>17.43851490576382</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>21.0442618605884</v>
+        <v>21.11353992542112</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.8918241280446</v>
+        <v>13.96189013433406</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>14.48688417766598</v>
+        <v>14.55627705627705</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.45668658741316</v>
+        <v>10.52625602319569</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>11.65040447001918</v>
+        <v>11.72011661807581</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>15.76263152905489</v>
+        <v>15.83211189510403</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>17.24837662337663</v>
+        <v>17.31765900377336</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>16.70517621437867</v>
+        <v>16.77511283580733</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>20.52532505483996</v>
+        <v>20.59537077050212</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>19.50139892262079</v>
+        <v>19.57114418428287</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>19.42545758335232</v>
+        <v>19.4953119310596</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 18.11</t>
+          <t>X &gt; 18.08</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>76</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.956665341447753</v>
+        <v>-7.922992332834411</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.50162896342863</v>
+        <v>-1.466274539760143</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4161566707466307</v>
+        <v>0.4523503881655344</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.998255306775221</v>
+        <v>4.063928336670898</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.553840972413589</v>
+        <v>1.61931557539986</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.044132735096397</v>
+        <v>6.110524786246344</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.712946510630474</v>
+        <v>9.779681762545906</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.07025204933731</v>
+        <v>11.13695841814481</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.61220611225209</v>
+        <v>11.67983221579253</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.254986431999015</v>
+        <v>9.322312910586042</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.23905042326095</v>
+        <v>14.30672140187488</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>17.06192762582645</v>
+        <v>17.13092775607141</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>20.78793923584472</v>
+        <v>20.85721730067745</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>13.55006062838635</v>
+        <v>13.62012663467582</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>14.14512067800774</v>
+        <v>14.21451355661881</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>10.06365856280618</v>
+        <v>10.13322799858871</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>11.27446462039512</v>
+        <v>11.34417676845175</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>15.5074365704287</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>16.94078947368422</v>
+        <v>17.01007185408095</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>16.39758906468627</v>
+        <v>16.46752568611492</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>20.26900243009629</v>
+        <v>20.33904814575845</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>19.2279881228942</v>
+        <v>19.29773338455628</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>19.15204678362573</v>
+        <v>19.22190113133301</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 18.74</t>
+          <t>X &gt; 18.7</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>71</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.561445349412772</v>
+        <v>-1.528171057093942</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.121972976733154</v>
+        <v>-6.088299968119813</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.519419919692524</v>
+        <v>-0.4840654960240371</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.583688175565023</v>
+        <v>1.619881892983926</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.035319798991672</v>
+        <v>4.10099282888735</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.814033707773106</v>
+        <v>2.879508310759377</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.266519688395142</v>
+        <v>6.332911739545089</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.804866451327285</v>
+        <v>8.871601703242717</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.25483322057526</v>
+        <v>10.32153958938277</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.29789921825654</v>
+        <v>12.36552532179698</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.346906372695827</v>
+        <v>8.414232851282854</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.29316458189697</v>
+        <v>12.36083556051091</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.39402547608589</v>
+        <v>15.46302560633085</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>19.39802077772759</v>
+        <v>19.46729884256031</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.69683601756353</v>
+        <v>11.766902023853</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>12.29189606718491</v>
+        <v>12.36128894579599</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.932450260359929</v>
+        <v>8.002019696142455</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.235917548490008</v>
+        <v>9.305629696546632</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13.67739282409789</v>
+        <v>13.74687319014702</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>15.27288732394366</v>
+        <v>15.34216970434039</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>14.72968691494571</v>
+        <v>14.79962353637436</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>18.87908397197915</v>
+        <v>18.94912968764131</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.74540843423593</v>
+        <v>17.81515369589802</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>17.66946709496747</v>
+        <v>17.73932144267474</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 19.36</t>
+          <t>X &gt; 19.32</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>70</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.245549977179373</v>
+        <v>-2.212275684860543</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.866439777537984</v>
+        <v>-6.832766768924643</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.163283098766975</v>
+        <v>-1.127928675098488</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>1.016260162601625</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.230532701736898</v>
+        <v>2.296007304723169</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.743380855397149</v>
+        <v>5.809772906547096</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.321969067021442</v>
+        <v>8.388704318936874</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.792056560615507</v>
+        <v>9.858762929423008</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.87536400698894</v>
+        <v>11.94299011052938</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.864008988389983</v>
+        <v>7.931335466977011</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.87062937062937</v>
+        <v>11.93830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.03185243785652</v>
+        <v>15.10085256810148</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.09620991253644</v>
+        <v>19.16548797736917</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>12.72299295921342</v>
+        <v>12.79305896550289</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.3180530088348</v>
+        <v>13.38744588744588</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.898245028971601</v>
+        <v>8.967814464754127</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10.22183304144775</v>
+        <v>10.29154518950438</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.72367049009386</v>
+        <v>14.79315085614299</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.33928571428571</v>
+        <v>16.40856809468244</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.79608530528775</v>
+        <v>15.86602192671641</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>20.00584453535944</v>
+        <v>20.0758902510216</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>18.85204827327014</v>
+        <v>18.92179353493222</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>18.77610693400167</v>
+        <v>18.84596128170895</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 19.98</t>
+          <t>X &gt; 19.94</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.949483724591374</v>
+        <v>-2.916209432272545</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-7.632485326192224</v>
+        <v>-7.598812317578883</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.790454555015664</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3589484327603643</v>
+        <v>0.395142150179268</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.892229372373997</v>
+        <v>2.957902402269674</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.630118623061946</v>
+        <v>1.695593226048217</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.205078577964436</v>
+        <v>5.271470629114383</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.825074657083562</v>
+        <v>7.891809908998994</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>11.44058139829328</v>
+        <v>11.50820750183372</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>7.367114578452103</v>
+        <v>7.43444105703913</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.43584676193372</v>
+        <v>11.50351774054765</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.65918163040309</v>
+        <v>14.72818176064805</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.78565090632527</v>
+        <v>18.85492897115799</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.32961821801261</v>
+        <v>12.39968422430207</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>14.37395362995282</v>
+        <v>14.44334650856389</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.892033848847376</v>
+        <v>9.961603284629902</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>11.23632579507094</v>
+        <v>11.30603794312756</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.80027504495929</v>
+        <v>15.86975541100842</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>17.43659420289855</v>
+        <v>17.50587658329528</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>16.89339379390059</v>
+        <v>16.96333041532925</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>21.16526482521451</v>
+        <v>21.23531054087668</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>19.9907646293778</v>
+        <v>20.06050989103989</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>19.91482329010933</v>
+        <v>19.98467763781661</v>
       </c>
     </row>
   </sheetData>
@@ -5831,2454 +5831,2454 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.297309811547898</v>
+        <v>-7.264035519229068</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.835383876916865</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.275084341003001</v>
+        <v>-3.239729917334515</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.438153016514995</v>
+        <v>-5.401959299096092</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.252698163857879</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.514808913169936</v>
+        <v>-8.449334310183666</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.18622576986165</v>
+        <v>-12.1198337187117</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.116954328423681</v>
+        <v>-8.050219076508249</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.87253971267641</v>
+        <v>-13.80583334386891</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.19709976112701</v>
+        <v>-13.12947365758657</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.47346513169283</v>
+        <v>-11.4061386531058</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-16.10038512212425</v>
+        <v>-16.03271414351032</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-23.02197778988675</v>
+        <v>-22.9529776596418</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-27.59116068787764</v>
+        <v>-27.52188262304491</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-25.35154120227725</v>
+        <v>-25.28147519598779</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-26.20575651497472</v>
+        <v>-26.13636363636364</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-26.33985020912364</v>
+        <v>-26.27028077334111</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-29.34338434985659</v>
+        <v>-29.27367220179997</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-30.57653654924362</v>
+        <v>-30.50705618319449</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-31.83876811594203</v>
+        <v>-31.7694857355453</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-32.38196852493998</v>
+        <v>-32.31203190351133</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-33.90719894290143</v>
+        <v>-33.83715322723927</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-33.6324237764193</v>
+        <v>-33.56267851475722</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-32.25908975336893</v>
+        <v>-32.18923540566165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 2.564</t>
+          <t>X &lt; 2.563</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>243</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.292956783549613</v>
+        <v>2.326231075868442</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.603871803884715</v>
+        <v>3.637544812498057</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.867875043502281</v>
+        <v>5.903229467170767</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.154081730309123</v>
+        <v>5.190275447728027</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.200334579029928</v>
+        <v>5.266007608925605</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.564453924547003</v>
+        <v>4.629928527533274</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.260723594962116</v>
+        <v>6.327115646112063</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.982168949443555</v>
+        <v>6.048904201358987</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.200639746976478</v>
+        <v>5.26734611578398</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.426804336207049</v>
+        <v>4.494430439747489</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.878118335832667</v>
+        <v>3.945444814419695</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.952933897378351</v>
+        <v>2.020604875992284</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.8176478560882217</v>
+        <v>-0.7486477258432629</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.154231004571137</v>
+        <v>-5.084952939738415</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.401639609863587</v>
+        <v>-5.331573603574121</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.45267009522162</v>
+        <v>-6.383277216610544</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-7.82133169060512</v>
+        <v>-7.751762254822594</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.160883007934963</v>
+        <v>-9.091170859878339</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-10.59085037998258</v>
+        <v>-10.52137001393344</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.992283950617285</v>
+        <v>-9.923001570220556</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-10.9470069933601</v>
+        <v>-10.87707037193145</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-10.19991678151299</v>
+        <v>-10.12987106585083</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.102096347541149</v>
+        <v>-9.032351085879064</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-8.766515053064758</v>
+        <v>-8.69666070535748</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 3.186</t>
+          <t>X &lt; 3.184</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.373497641868248</v>
+        <v>1.511824642293227</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.562131651033447</v>
+        <v>2.703765401195319</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.408145472661595</v>
+        <v>3.555822688042184</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.313399778516064</v>
+        <v>2.461189279286472</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.519558564920587</v>
+        <v>2.697917890708666</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.135294606498803</v>
+        <v>2.312364992836578</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.076714188730492</v>
+        <v>3.257973560854623</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.131492876545259</v>
+        <v>4.315639978696971</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.830409603359769</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.9229830546079896</v>
+        <v>1.103295454040833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.7074195830385861</v>
+        <v>-0.5310418503621364</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.510323010323006</v>
+        <v>-2.336508811062032</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.206242800238726</v>
+        <v>-4.032189961887617</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.332361516034979</v>
+        <v>-6.161665784899093</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-7.372245136024659</v>
+        <v>-7.201488471792636</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-7.539089848308045</v>
+        <v>-7.370460328475602</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-8.625564494837917</v>
+        <v>-8.458575938735514</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-10.25435743474272</v>
+        <v>-10.0901341998086</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.466805700382338</v>
+        <v>-9.301723734914809</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.279761904761905</v>
+        <v>-9.114877924946782</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-9.251533742331283</v>
+        <v>-9.084905008943345</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-9.708441178926272</v>
+        <v>-9.542430359665431</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-9.433666012444142</v>
+        <v>-9.267955647183378</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-8.747702589807851</v>
+        <v>-8.580429121780696</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 3.808</t>
+          <t>X &lt; 3.804</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.30036839016757</v>
+        <v>1.333642682486399</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9651928755232433</v>
+        <v>0.9988658841365847</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.566308737967724</v>
+        <v>1.60166316163621</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.617821547223535</v>
+        <v>1.654015264642439</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8698987009750141</v>
+        <v>0.9355717308706915</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6744102527573048</v>
+        <v>0.7398848557435755</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.687258406417556</v>
+        <v>1.753650457567502</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.66380580171532</v>
+        <v>1.730541053630752</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1747096218400017</v>
+        <v>0.2414159906475035</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.03862931311138595</v>
+        <v>0.1062554166518268</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.7074195830385861</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.49365776622512</v>
+        <v>-2.424657635980161</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.500728862973759</v>
+        <v>-4.431450798141036</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.394353979562077</v>
+        <v>-4.324287973272611</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-4.692151072797841</v>
+        <v>-4.622758194186765</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.719101909803904</v>
+        <v>-5.649532474021377</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.079187366715509</v>
+        <v>-6.009475218658885</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.990615224191863</v>
+        <v>-5.921134858142729</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.676020408163261</v>
+        <v>-5.606738027766532</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-5.709016735528571</v>
+        <v>-5.639080114099919</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.295175872803824</v>
+        <v>-6.225130157141663</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-6.845817079767627</v>
+        <v>-6.843512587516763</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-6.21475897758036</v>
+        <v>-6.281589738699211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 4.43</t>
+          <t>X &lt; 4.425</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.236493119388868</v>
+        <v>0.3274068548220015</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2849021345478278</v>
+        <v>-0.2874819883457391</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.510034272874428</v>
+        <v>0.515395321166686</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2617903079121788</v>
+        <v>0.2692947097538223</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.01036960746569093</v>
+        <v>0.02687491881252413</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.009424733751266956</v>
+        <v>-0.0662709399080228</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2419177003027073</v>
+        <v>0.1888578738673559</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5952961630929394</v>
+        <v>-0.556206978915597</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.019329446301221</v>
+        <v>-0.9815732050307702</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6758464213164572</v>
+        <v>-0.727411383401531</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.518805589955313</v>
+        <v>-1.573799920511313</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.053020536260753</v>
+        <v>-1.105583871111506</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.805072276163166</v>
+        <v>-1.761892529937747</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.143747522951713</v>
+        <v>-3.103419585656042</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.337129413758099</v>
+        <v>-3.294709475206723</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.580058190952357</v>
+        <v>-3.54065868771751</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.459030842270757</v>
+        <v>-4.421541277542786</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.843343867304576</v>
+        <v>-4.806494026181895</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.720330574018945</v>
+        <v>-4.683973326863544</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.668569431500472</v>
+        <v>-4.683868880107475</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.414469065714371</v>
+        <v>-4.479449595225695</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-4.905453317114883</v>
+        <v>-5.022148964664673</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.139941045821985</v>
+        <v>-5.307898341818479</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.697098999447483</v>
+        <v>-4.86565420560747</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 5.052</t>
+          <t>X &lt; 5.045</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.213641085197793</v>
+        <v>1.202561480887042</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5888203859046612</v>
+        <v>0.6492850467032909</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5973458450625486</v>
+        <v>0.8135966604545288</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6488035052241372</v>
+        <v>0.6833083365689561</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1828828177238435</v>
+        <v>-0.2351478315354854</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.358299785572747</v>
+        <v>-0.4123477051613449</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2609701235731094</v>
+        <v>-0.3831310576605773</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7570737176050955</v>
+        <v>-0.8387009288765341</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.078139233438158</v>
+        <v>-1.120709822478624</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.6917135854693655</v>
+        <v>-0.7265941345472058</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8524522153808647</v>
+        <v>-0.8901712538732554</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.04380137628867686</v>
+        <v>-0.07482875360133079</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.5881620654067206</v>
+        <v>-0.6144751384735017</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.317133089639043</v>
+        <v>-1.346130236656052</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.468450115478376</v>
+        <v>-1.49369731250065</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.816102176081792</v>
+        <v>-1.847523373781577</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.457810083428683</v>
+        <v>-2.49201673249501</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.029255492659658</v>
+        <v>-3.107433658052145</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.844541980079406</v>
+        <v>-2.96448173737582</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.052325581395351</v>
+        <v>-3.215272688895752</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.609109499907042</v>
+        <v>-2.809605873637871</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-2.716135086183499</v>
+        <v>-2.916810478905404</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.346474253001844</v>
+        <v>-3.550292450667278</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-2.944009684074132</v>
+        <v>-3.146519921298577</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 5.674</t>
+          <t>X &lt; 5.666</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.874507023176889</v>
+        <v>1.824487052714197</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.476987368881687</v>
+        <v>1.489710254364383</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.720578675369111</v>
+        <v>1.738137176601349</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.227727081489647</v>
+        <v>2.211941433236056</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.586795946764703</v>
+        <v>1.563846151194717</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.961226477374488</v>
+        <v>1.938195222988533</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.875002043198116</v>
+        <v>1.853317119985121</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.534025425145224</v>
+        <v>1.549418604651166</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.9513217648245345</v>
+        <v>1.002334804702201</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.301081859673083</v>
+        <v>1.355122693393668</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9512214014450961</v>
+        <v>1.003791466262278</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.483613140916518</v>
+        <v>1.538050192895589</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.295451510444359</v>
+        <v>1.290435343050099</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8868287818070044</v>
+        <v>0.8817392058155278</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.039383185716019</v>
+        <v>1.036604038316263</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.5732697022537536</v>
+        <v>0.5678264824606316</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.06464417289883784</v>
+        <v>0.05867482390716816</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.3777921927808592</v>
+        <v>-0.421400401489997</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1870437956204327</v>
+        <v>-0.2680481074949981</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.275562851782361</v>
+        <v>-0.3938977321736346</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.0934194327776865</v>
+        <v>-0.2485139439170183</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.194531169086396</v>
+        <v>-0.3496416638720206</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8221371903890073</v>
+        <v>-0.9771240784500037</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.5476727346055839</v>
+        <v>-0.7029108987421822</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 6.296</t>
+          <t>X &lt; 6.287</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.66939004463088</v>
+        <v>1.774907809981599</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.552317038165398</v>
+        <v>1.604244797189779</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.911962266554731</v>
+        <v>1.971477389296638</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.884126923711293</v>
+        <v>1.914978512085845</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.168446067519874</v>
+        <v>1.250960468422591</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.57395129188037</v>
+        <v>1.602040440077964</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.783617910918053</v>
+        <v>1.814774469535529</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.55964841823792</v>
+        <v>1.568780947289369</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.946142649199416</v>
+        <v>0.9853471885373892</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.482350906552256</v>
+        <v>1.52677981480101</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.156273492444889</v>
+        <v>1.198429818408719</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.586786575869546</v>
+        <v>1.631619078706613</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.281072649958823</v>
+        <v>1.329924700788069</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.059715838924468</v>
+        <v>1.108845824341479</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.055806433948298</v>
+        <v>1.053112165315135</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.5045782739627001</v>
+        <v>0.4974443227455225</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.2067291212984941</v>
+        <v>0.1992336479805417</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.3024706177548708</v>
+        <v>-0.2889586440115011</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.2177815005384716</v>
+        <v>-0.1825962882788588</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.3810142154182614</v>
+        <v>-0.3791020664816926</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.2901916562627278</v>
+        <v>-0.3740031084893403</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3882441345912966</v>
+        <v>-0.4720549544578532</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.8475292576327007</v>
+        <v>-0.9325297733384517</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5076504045501835</v>
+        <v>-0.5921705261431001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 6.918</t>
+          <t>X &lt; 6.907</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.388559404278134</v>
+        <v>1.405024446201061</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.246247920492046</v>
+        <v>1.215105204587125</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.253027687842753</v>
+        <v>1.273947575160193</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.483133084284098</v>
+        <v>1.478424748377996</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.9526344979965131</v>
+        <v>0.9494908668495583</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.457269267922996</v>
+        <v>1.426172166418688</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.388653457191488</v>
+        <v>1.330225413962431</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.399953884136707</v>
+        <v>1.370070778564212</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.006687340463678</v>
+        <v>1.00493430275727</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.392272219549319</v>
+        <v>1.420746396796304</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.357069818328533</v>
+        <v>1.433305195361839</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.561301192765669</v>
+        <v>1.638348728536961</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.113465363355381</v>
+        <v>1.192496772953227</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.9887736079034255</v>
+        <v>1.068176483831266</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.9098327023605677</v>
+        <v>1.020136824720154</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.3932446127842724</v>
+        <v>0.5012614039719594</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.2591509186353491</v>
+        <v>0.3189415564426952</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1553429740261407</v>
+        <v>-0.1247181212410311</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1038918846383297</v>
+        <v>-0.1024375825238621</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.08167957405614601</v>
+        <v>-0.1092026147630065</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1119050094822143</v>
+        <v>-0.1677216772111194</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2073337592142153</v>
+        <v>-0.2630927998258556</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5337283349979884</v>
+        <v>-0.5895575171164964</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.3869802213260272</v>
+        <v>-0.4428691316973286</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 7.54</t>
+          <t>X &lt; 7.528</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9314317013448417</v>
+        <v>0.8845392000338208</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8407912630263965</v>
+        <v>0.7946941094196305</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.013287573613141</v>
+        <v>1.035120290070623</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.162893327038738</v>
+        <v>1.161388885468867</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6463324532838755</v>
+        <v>0.6047503563844856</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.035429218647543</v>
+        <v>0.9936905317921685</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9507541272865581</v>
+        <v>0.9101897311018519</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.228373007908139</v>
+        <v>1.188350493196054</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.137263078235819</v>
+        <v>1.078737644972954</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.31808846519327</v>
+        <v>1.261272536381519</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.397510884723751</v>
+        <v>1.340167556057111</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.498783421094181</v>
+        <v>1.397759808702766</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.197865344347726</v>
+        <v>1.07211657215236</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.269132249393216</v>
+        <v>1.143704796011527</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.036062868028019</v>
+        <v>0.9558717624620385</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.7269855397185623</v>
+        <v>0.6456535183243233</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.7970915240913925</v>
+        <v>0.7159597947902796</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3638658865431807</v>
+        <v>0.3270691681899862</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.3846702363511483</v>
+        <v>0.3475076499489234</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.5539204797867612</v>
+        <v>0.4720601581745001</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.4373551465576</v>
+        <v>0.3118073551607949</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.254844090717377</v>
+        <v>0.1737550197048705</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.110839372891526</v>
+        <v>-0.1035736212760554</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1602526565635287</v>
+        <v>-0.1528938257837424</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 8.162</t>
+          <t>X &lt; 8.148</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5846828530534651</v>
+        <v>0.5735555052259755</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5175363446601864</v>
+        <v>0.506570111959519</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5755927794531672</v>
+        <v>0.5650630178932019</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8277792080246442</v>
+        <v>0.8172784806211766</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4448681473261473</v>
+        <v>0.4228584488365641</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8605813564059872</v>
+        <v>0.7971494590018509</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8501132035088048</v>
+        <v>0.7869204513730637</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7596340714215657</v>
+        <v>0.7376110543844447</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6196184810287093</v>
+        <v>0.5976791855806525</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9382493337460218</v>
+        <v>0.9162960653548424</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9079469583148096</v>
+        <v>0.8859075998564592</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9409707939119727</v>
+        <v>0.9189826344878611</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6226813620187741</v>
+        <v>0.6013224929135035</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5906520698028146</v>
+        <v>0.569378204788805</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.574252079006321</v>
+        <v>0.5532000589773247</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.246653868214409</v>
+        <v>0.2256509100889517</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2608642728769084</v>
+        <v>0.2398784798165039</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.0668267523666799</v>
+        <v>-0.08752361972512546</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.05016742550168374</v>
+        <v>0.02928323159935076</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2205427156417699</v>
+        <v>0.1581999061699193</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.1974065274182308</v>
+        <v>0.135234562265687</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.1049771251983458</v>
+        <v>0.04287332984949188</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.4218596370014112</v>
+        <v>-0.4836565063559632</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3906089462321987</v>
+        <v>-0.4111343694387486</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 8.784</t>
+          <t>X &lt; 8.769</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2567</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2641025324731459</v>
+        <v>0.297376824791975</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1815103410958017</v>
+        <v>0.176558397990334</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.385623944730483</v>
+        <v>0.343698615694187</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5824740877913683</v>
+        <v>0.5413581801619571</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3164870811066365</v>
+        <v>0.2661508302598605</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7577501651245697</v>
+        <v>0.7071706095034926</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.8196745307620361</v>
+        <v>0.7699675107045536</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7184073171182348</v>
+        <v>0.7077132233116359</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5500514704307164</v>
+        <v>0.5392985053884871</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7672663704139708</v>
+        <v>0.7574031287393765</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.9094131965848931</v>
+        <v>0.8992202953269626</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.924526229877138</v>
+        <v>0.9146477707244998</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6375268255324542</v>
+        <v>0.5901576772669372</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5946300023418658</v>
+        <v>0.5474936317846044</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5024960648034877</v>
+        <v>0.4561024437637613</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1502305400414627</v>
+        <v>0.1031185642836121</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.03932617005273897</v>
+        <v>-0.00765451071485046</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1590453106704004</v>
+        <v>-0.2059285765274907</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3085445732254115</v>
+        <v>-0.3168247048434623</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2151400233372271</v>
+        <v>-0.2236483858420897</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1905739498539845</v>
+        <v>-0.1984583400984832</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.2822052894751366</v>
+        <v>-0.3289365298269828</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.6072307654481577</v>
+        <v>-0.654307933692607</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.5043204687475082</v>
+        <v>-0.551334060268907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 9.406</t>
+          <t>X &lt; 9.39</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4127710832035447</v>
+        <v>0.392302057838755</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3185115510597498</v>
+        <v>0.2985102075992074</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4832060053492455</v>
+        <v>0.3917385356855689</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.600939490309365</v>
+        <v>0.5105711613374098</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3672197532897314</v>
+        <v>0.2694458190526134</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5753711904337351</v>
+        <v>0.4773462609698669</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4508136440107506</v>
+        <v>0.3907991154802843</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3780783324330343</v>
+        <v>0.355363951770812</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2193618992945616</v>
+        <v>0.1965116232854811</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3903252186623831</v>
+        <v>0.4056656463756454</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5384889799431463</v>
+        <v>0.5164952240406535</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7985406460452751</v>
+        <v>0.7400754971722989</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6573807556925289</v>
+        <v>0.6005618857908104</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5691764576450637</v>
+        <v>0.5126382364365227</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5616310051053617</v>
+        <v>0.5060753086562286</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.3646495074861065</v>
+        <v>0.3080808080808026</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2527423834689557</v>
+        <v>0.1963117918064796</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1329112185503831</v>
+        <v>0.1136356268653813</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.03765968844184187</v>
+        <v>0.09216033757738273</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.09848906192064533</v>
+        <v>0.1898313418210549</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.2079123506459553</v>
+        <v>0.3001592179965655</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.06104244107356749</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1796624065474433</v>
+        <v>-0.1249413862921216</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1963613700670805</v>
+        <v>-0.1415148380108562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 10.03</t>
+          <t>X &lt; 10.01</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2807</v>
+        <v>2810</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1405525011571527</v>
+        <v>-0.1286692101492264</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.002721460658250408</v>
+        <v>0.01448908256850245</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2794326013744737</v>
+        <v>0.2910550257644076</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3635623267330743</v>
+        <v>0.3398341151508433</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3721518315265868</v>
+        <v>0.342137114182016</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3316705019897412</v>
+        <v>0.3370256922761996</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4641416809738388</v>
+        <v>0.4340591261640583</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2768296509999928</v>
+        <v>0.2469592982109674</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.09073024695751997</v>
+        <v>0.06103852992870884</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2943643614731712</v>
+        <v>0.2645198555718693</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3057516428985991</v>
+        <v>0.3112757533997765</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4020234820163893</v>
+        <v>0.4074711500937624</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.362887619849829</v>
+        <v>0.3330397357725161</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1626940141643232</v>
+        <v>0.1330664981391791</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.09312282934330085</v>
+        <v>0.06362096823943375</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.0346224074646031</v>
+        <v>0.005107856420842438</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.07830081324588178</v>
+        <v>-0.1076964637919389</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.1265494683282853</v>
+        <v>-0.155897992313804</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.209269969162392</v>
+        <v>-0.2385669819691643</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1434098185699071</v>
+        <v>-0.1728107255023517</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.02496197483425533</v>
+        <v>-0.05444935457961009</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1151949804824994</v>
+        <v>-0.1445933905146788</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2464458252239652</v>
+        <v>-0.2757467405162686</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.194324131192495</v>
+        <v>-0.2236879302890173</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 10.65</t>
+          <t>X &lt; 10.63</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.08934396776234621</v>
+        <v>-0.139827398952022</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2023628619314906</v>
+        <v>-0.2183984782557715</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.008330055165117756</v>
+        <v>0.06254751537770886</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1977535200126539</v>
+        <v>0.2531240132797095</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1919122971586305</v>
+        <v>0.2088174484906062</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1601252330993361</v>
+        <v>0.1767408034341926</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1555604361160547</v>
+        <v>0.1733384962707305</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.168991254643089</v>
+        <v>0.2212669862525303</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.09383314859312009</v>
+        <v>0.1119521396674372</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1234894330284675</v>
+        <v>0.1768803253265148</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0426656539201673</v>
+        <v>0.09563092595187328</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.04615098407730756</v>
+        <v>0.007218807107513214</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.195519985012325</v>
+        <v>-0.1746228097629796</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5332391367078273</v>
+        <v>-0.4438374871969941</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.4209371973490263</v>
+        <v>-0.3987833451918732</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.3519313783626856</v>
+        <v>-0.330646747626588</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4316392992044911</v>
+        <v>-0.3759996159020602</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.4480234178823963</v>
+        <v>-0.4264035284443395</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.4509326845093184</v>
+        <v>-0.4296359329912676</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.2778727770177838</v>
+        <v>-0.2567952795416915</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1508381099900902</v>
+        <v>-0.1631166280894902</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.2747851703216</v>
+        <v>-0.2527643193310212</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.3903833792950238</v>
+        <v>-0.4030596940305884</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.2405271168789511</v>
+        <v>-0.2530452273695047</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 11.27</t>
+          <t>X &lt; 11.25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.35847153837679</v>
+        <v>-0.407016267660822</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3774561243752217</v>
+        <v>-0.3591673756172113</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.3063298330545905</v>
+        <v>-0.2526738270590414</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.03932571260969553</v>
+        <v>-0.01769923789164096</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2863606155005982</v>
+        <v>-0.2684319562900015</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2797866036670982</v>
+        <v>-0.2621322301605531</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.402798546596209</v>
+        <v>-0.3840266471726963</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3966370194809556</v>
+        <v>-0.377443097476494</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5023963269224794</v>
+        <v>-0.4832960757553764</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4591887033535968</v>
+        <v>-0.4389127504153976</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.5648475841791551</v>
+        <v>-0.5450134752621025</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6584887658098992</v>
+        <v>-0.6382642313159437</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6986021940628291</v>
+        <v>-0.6767032094543097</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.033660217333683</v>
+        <v>-1.011536863213301</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.873656893265867</v>
+        <v>-0.8504884234626857</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.758683317151764</v>
+        <v>-0.7363636363636346</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.806516875790301</v>
+        <v>-0.7840075711626042</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.8251826304428747</v>
+        <v>-0.8025175189679388</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8228843559940131</v>
+        <v>-0.8005380708792771</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6496079412746099</v>
+        <v>-0.627479969402998</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.5390281793584322</v>
+        <v>-0.5160434202905009</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6285461157257046</v>
+        <v>-0.6054724744292983</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7347443596146874</v>
+        <v>-0.7121141544382112</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.62392170424949</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 11.89</t>
+          <t>X &lt; 11.87</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2247339138101125</v>
+        <v>-0.2409115671863944</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3814349403886723</v>
+        <v>-0.3972873547218256</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4489973844812525</v>
+        <v>-0.4636268369817458</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1769888261029422</v>
+        <v>-0.2233711738038977</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2013981198837484</v>
+        <v>-0.2507062653229539</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.06062463946887675</v>
+        <v>-0.1101533519216744</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1047180740971214</v>
+        <v>-0.1213124756199804</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2033021076843013</v>
+        <v>-0.2196382428940495</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3372259216081517</v>
+        <v>-0.3535610955019806</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.2520204094352465</v>
+        <v>-0.2677403354951906</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3470425732437192</v>
+        <v>-0.3629696459507983</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4457730881218396</v>
+        <v>-0.4614409185445325</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4512728510940178</v>
+        <v>-0.4660005076483955</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7507123461695571</v>
+        <v>-0.7975263545772009</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6134245093283894</v>
+        <v>-0.6597459181857701</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.5497798385898705</v>
+        <v>-0.5966399748783147</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.66475839663714</v>
+        <v>-0.711485826791062</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.6533695517451221</v>
+        <v>-0.700029664675796</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.645052874738461</v>
+        <v>-0.691915131354115</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6010784949724268</v>
+        <v>-0.6481300709651379</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.5087260417039872</v>
+        <v>-0.5553672582147797</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5653985675292432</v>
+        <v>-0.6119747716909245</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.660938739716876</v>
+        <v>-0.7077330566196807</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.5553086461959822</v>
+        <v>-0.6020906663430026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 12.52</t>
+          <t>X &lt; 12.49</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3142</v>
+        <v>3144</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.21440576594037</v>
+        <v>-0.2148919508175098</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4062627863875363</v>
+        <v>-0.4064514544223314</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5960097145476553</v>
+        <v>-0.5953175263735986</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3120633099451382</v>
+        <v>-0.279567903137945</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3749443801992527</v>
+        <v>-0.3447775887496647</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2965920722233264</v>
+        <v>-0.2981916651873746</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3869497193778741</v>
+        <v>-0.3880849142148648</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5208790285182232</v>
+        <v>-0.5217839269944022</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6197267779970943</v>
+        <v>-0.6205931054885738</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3933305430744269</v>
+        <v>-0.3939319920671949</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3859344121080852</v>
+        <v>-0.4183636144293885</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.456574180416915</v>
+        <v>-0.4571369131141125</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3575725995228467</v>
+        <v>-0.3576033974860238</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5285181512779147</v>
+        <v>-0.528324867997263</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.3436072130674788</v>
+        <v>-0.374898988373225</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.2692485784667724</v>
+        <v>-0.300915243808646</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.3845204748164477</v>
+        <v>-0.4160546017553699</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.3753715328851612</v>
+        <v>-0.4068675089083271</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.3628064266976452</v>
+        <v>-0.3944370402413568</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.2840909090909065</v>
+        <v>-0.3158828038472308</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2361654328453326</v>
+        <v>-0.2677108800383223</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2931376529357266</v>
+        <v>-0.3246183313051674</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3811683986993231</v>
+        <v>-0.4127510937300514</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3109167997439002</v>
+        <v>-0.3425156357756052</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 13.14</t>
+          <t>X &lt; 13.11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2597154188471507</v>
+        <v>-0.2763611321235615</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3286980432896982</v>
+        <v>-0.3452094524486498</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4723983205186997</v>
+        <v>-0.4884559283938188</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2951252794471984</v>
+        <v>-0.3111931760771469</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4556283877874492</v>
+        <v>-0.4736163985295505</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4071044893044231</v>
+        <v>-0.4251872573450299</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.506451786188066</v>
+        <v>-0.5242738207580544</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6110666472642592</v>
+        <v>-0.6287346891359107</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7080997382278866</v>
+        <v>-0.7256932140587367</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.526136931097362</v>
+        <v>-0.5437327885646539</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4839958375629152</v>
+        <v>-0.5017002473087047</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5261165617861536</v>
+        <v>-0.543725283767003</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4745191248530816</v>
+        <v>-0.4919286344358227</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6148554779278186</v>
+        <v>-0.6320901092298783</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.3471157607543631</v>
+        <v>-0.3644593609766318</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.3285635325185794</v>
+        <v>-0.3460662967705161</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.3814254728862991</v>
+        <v>-0.398855183693847</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3424302814362576</v>
+        <v>-0.3598798026659935</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3585317228703602</v>
+        <v>-0.3760220761878443</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.3097553324968629</v>
+        <v>-0.3273409351783201</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2696280839273513</v>
+        <v>-0.2871352609235345</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.3268610515834354</v>
+        <v>-0.3443041672913481</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4101181317534142</v>
+        <v>-0.4275522259568234</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.3732110846630832</v>
+        <v>-0.3906696744074196</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 13.76</t>
+          <t>X &lt; 13.73</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3211</v>
+        <v>3213</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.149075023561565</v>
+        <v>-0.1488817240623774</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1893154790094087</v>
+        <v>-0.2198279303289254</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4056805527980956</v>
+        <v>-0.435287982457794</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2048829291816858</v>
+        <v>-0.2342369431382849</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3980295229461461</v>
+        <v>-0.3980310171592194</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3483285113764083</v>
+        <v>-0.3175134982126764</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4842700562686346</v>
+        <v>-0.4529427060137152</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6213219153150931</v>
+        <v>-0.5897498685603537</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6242041780258845</v>
+        <v>-0.6236233336323949</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4812251402978873</v>
+        <v>-0.4803132672208505</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3750906216773586</v>
+        <v>-0.3743947606378981</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5122437289672774</v>
+        <v>-0.5113120538574734</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5015341011166186</v>
+        <v>-0.5310155637666583</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6115117355763857</v>
+        <v>-0.6408149347357863</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.4447089041406045</v>
+        <v>-0.4427306948677767</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.390285871917861</v>
+        <v>-0.3576199749748312</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4438485517795243</v>
+        <v>-0.4421234234446274</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.3749963026616712</v>
+        <v>-0.4043230925707988</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3891582234811324</v>
+        <v>-0.4186044488379181</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3392301710730905</v>
+        <v>-0.3688198887981784</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.3040124811821485</v>
+        <v>-0.3022438870717892</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.3925370394927228</v>
+        <v>-0.3595685359146401</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4105384550700109</v>
+        <v>-0.408813630149119</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.3745804353091771</v>
+        <v>-0.341713788319062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 14.38</t>
+          <t>X &lt; 14.35</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3248</v>
+        <v>3250</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1736628303915708</v>
+        <v>-0.1730805384243297</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.06434279195475057</v>
+        <v>-0.06364347168398865</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2639254970539113</v>
+        <v>-0.2928847828855297</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2570379436964529</v>
+        <v>-0.2550373472279901</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3603224967786574</v>
+        <v>-0.3901941215088129</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3090526363787589</v>
+        <v>-0.3084690023235197</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5440835943950191</v>
+        <v>-0.5429316279756122</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6214833139309306</v>
+        <v>-0.620131303493352</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5932155378039994</v>
+        <v>-0.5919043206316843</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4912822223182332</v>
+        <v>-0.4896079286863042</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.3832420739484661</v>
+        <v>-0.3817856748293877</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5526835128062118</v>
+        <v>-0.5509700370227932</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.524190169428806</v>
+        <v>-0.5218749037520354</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6968270075722955</v>
+        <v>-0.6942841523416021</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.4780246292772858</v>
+        <v>-0.4752529619069108</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.4788932881114789</v>
+        <v>-0.4764495786595191</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4412326976028922</v>
+        <v>-0.4694415552467461</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.4358190790193603</v>
+        <v>-0.433270535311344</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4473804079782582</v>
+        <v>-0.4449443819522472</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.395910209102091</v>
+        <v>-0.393609445048881</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.3672929958942959</v>
+        <v>-0.3647101447780372</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4249246954097927</v>
+        <v>-0.453015038031289</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3780445025290078</v>
+        <v>-0.4063252856504533</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.3433511940771439</v>
+        <v>-0.3716211358734682</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 15</t>
+          <t>X &lt; 14.98</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3286</v>
+        <v>3288</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.08834459606244138</v>
+        <v>0.05894147007754214</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1926377833533692</v>
+        <v>0.193560378248435</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1118337921014572</v>
+        <v>-0.1099258257266413</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1434319559926251</v>
+        <v>-0.1411072583691748</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.219437184665189</v>
+        <v>-0.2180572441544655</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1968280730815124</v>
+        <v>-0.1955664572680149</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.377461668715128</v>
+        <v>-0.4059176056638378</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4571258538057563</v>
+        <v>-0.4853876907483539</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4286557776369619</v>
+        <v>-0.4569673590593197</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3973632657383348</v>
+        <v>-0.394986873116892</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3176910938860189</v>
+        <v>-0.3155161364332031</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.458054680310596</v>
+        <v>-0.4556390446960918</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5034827153130337</v>
+        <v>-0.5004118843299992</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5856555520960072</v>
+        <v>-0.5824111822946918</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.4072910208429263</v>
+        <v>-0.4037866517248858</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.4316217244464795</v>
+        <v>-0.4284348337746309</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3048264212908549</v>
+        <v>-0.3016414207867371</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3310223655996296</v>
+        <v>-0.3277626429182163</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3399228597346848</v>
+        <v>-0.3367784310896695</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3476443768996944</v>
+        <v>-0.3445997581208928</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3560234555166488</v>
+        <v>-0.3526697432058796</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.4746907444459154</v>
+        <v>-0.4712222109844788</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4860368238657671</v>
+        <v>-0.4827150000110976</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.513520054955805</v>
+        <v>-0.479725197262205</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 15.63</t>
+          <t>X &lt; 15.6</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3300</v>
+        <v>3301</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1025863884111118</v>
+        <v>0.05951389739835378</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.174929449261704</v>
+        <v>0.1622033527382314</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.07411030227709858</v>
+        <v>-0.08552736779651582</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1386943121322517</v>
+        <v>-0.1494816535466867</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3063069424755014</v>
+        <v>-0.3178091395497731</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2528910475096424</v>
+        <v>-0.2645746261510311</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3455979981279782</v>
+        <v>-0.3565923737422381</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4260922805573912</v>
+        <v>-0.4368264963437127</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.457889571683566</v>
+        <v>-0.4686539239287058</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4300071456966421</v>
+        <v>-0.4401169784600683</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3495221228169427</v>
+        <v>-0.35989653578185</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4904817404817408</v>
+        <v>-0.5005768013754661</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.5404822042455635</v>
+        <v>-0.5495960171297156</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.6836778733936413</v>
+        <v>-0.692560950447195</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.5088854675879304</v>
+        <v>-0.5172560970780324</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5306255194084102</v>
+        <v>-0.5395065798510998</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4049646129135738</v>
+        <v>-0.4137713013540036</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4315244903126825</v>
+        <v>-0.4402358809522298</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4395021919895683</v>
+        <v>-0.4484013001097154</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.4161622276029036</v>
+        <v>-0.4252335046259645</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.4268289285256586</v>
+        <v>-0.4354308577872246</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.5453365670027637</v>
+        <v>-0.5538402969650775</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.5554905677737025</v>
+        <v>-0.5642322503061621</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.5832004253056837</v>
+        <v>-0.5918714096832716</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 16.25</t>
+          <t>X &lt; 16.22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3312</v>
+        <v>3314</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1189820425250616</v>
+        <v>0.09004890095221185</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.159869246371521</v>
+        <v>0.1310907165155797</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.123464831225931</v>
+        <v>-0.121289137724311</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1303777324883413</v>
+        <v>-0.1577907415032698</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3287209450220914</v>
+        <v>-0.3267738914466491</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3348898636856745</v>
+        <v>-0.3030323111231752</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4300732063116399</v>
+        <v>-0.4277362069752257</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5113070318796531</v>
+        <v>-0.5087645785320163</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5428655055960121</v>
+        <v>-0.5403273164680797</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5179011764145471</v>
+        <v>-0.5149425817783069</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4367428913092652</v>
+        <v>-0.4339872175521577</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5782274284079278</v>
+        <v>-0.5752294162407665</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6321344930578903</v>
+        <v>-0.628470740169206</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7455377437807442</v>
+        <v>-0.7416806662615656</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.573776516417837</v>
+        <v>-0.5696511501413113</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.623427197705638</v>
+        <v>-0.6196066626530268</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5288629639694733</v>
+        <v>-0.5250233207665858</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5557438120784681</v>
+        <v>-0.5217078225438172</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5930959511826828</v>
+        <v>-0.5591497507523755</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.599366706875756</v>
+        <v>-0.5655126768666889</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5516845718938796</v>
+        <v>-0.5175432569693541</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.639900787513227</v>
+        <v>-0.6056537779289499</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6490512912160895</v>
+        <v>-0.6149442370996638</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6467709127892221</v>
+        <v>-0.6427877483798596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 16.87</t>
+          <t>X &lt; 16.84</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3325</v>
+        <v>3329</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0002862803027596783</v>
+        <v>-0.001228975007151689</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.06898213547579957</v>
+        <v>0.06794517207379158</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1590989983485613</v>
+        <v>-0.1599116175291897</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1687697709180682</v>
+        <v>-0.1695948900793454</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3378690951386574</v>
+        <v>-0.3393289103894048</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2834624266764223</v>
+        <v>-0.2849820674224688</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.381266490076051</v>
+        <v>-0.3826957126997641</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.463253492520181</v>
+        <v>-0.46459484826363</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4945131570919301</v>
+        <v>-0.4958167014724069</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.5025934653081521</v>
+        <v>-0.503913867933079</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4206781638825419</v>
+        <v>-0.422088487883201</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5327269374317609</v>
+        <v>-0.5340133292960587</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5907923034932594</v>
+        <v>-0.5920473463553293</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6746189587422009</v>
+        <v>-0.6757818639006672</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5060755128064471</v>
+        <v>-0.5074631606633346</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.5231882581490268</v>
+        <v>-0.5245366460529723</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4594980682672869</v>
+        <v>-0.4609282553554976</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4866629057152636</v>
+        <v>-0.4880650053981697</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5830648166414534</v>
+        <v>-0.5843450732425666</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6186167017122273</v>
+        <v>-0.6198490327445896</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6032965628441076</v>
+        <v>-0.6045663085777022</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.69148038198351</v>
+        <v>-0.6926477255620114</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6694704965949967</v>
+        <v>-0.6706560575173697</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6675020885547198</v>
+        <v>-0.6686934837718965</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 17.49</t>
+          <t>X &lt; 17.46</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3331</v>
+        <v>3335</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02295670993196808</v>
+        <v>0.0220474666752466</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.0616842904608248</v>
+        <v>0.06071806021703452</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1089019190874723</v>
+        <v>-0.109709706939114</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1795021270984662</v>
+        <v>-0.1802482470215381</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2594037662805562</v>
+        <v>-0.2608370652058909</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2047358219162234</v>
+        <v>-0.2062294981399475</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3037261594517986</v>
+        <v>-0.3051265138415786</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3860423717936996</v>
+        <v>-0.3873540005413147</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4171484603049933</v>
+        <v>-0.4184225716430845</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4265791918152431</v>
+        <v>-0.4278668617011405</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3742001708718021</v>
+        <v>-0.3755428399012928</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4865348531217464</v>
+        <v>-0.4877528327106901</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5465009860983443</v>
+        <v>-0.5476829967520871</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6305613706550659</v>
+        <v>-0.6316506090070817</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4634912152947024</v>
+        <v>-0.4648015949892468</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4794911660678594</v>
+        <v>-0.4807648727780389</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3861853399404964</v>
+        <v>-0.3875758062555263</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4134681272666612</v>
+        <v>-0.4148301472211529</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5092860018554433</v>
+        <v>-0.5105275014275819</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.5444152923538255</v>
+        <v>-0.5456098028916756</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5300780334730533</v>
+        <v>-0.5313075263350271</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.618217870881189</v>
+        <v>-0.6193449902130439</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.5957308383745215</v>
+        <v>-0.5968772427313596</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5938806287208109</v>
+        <v>-0.595032507110929</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 18.11</t>
+          <t>X &lt; 18.08</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.03675787889898885</v>
+        <v>0.0358423774879455</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.0753780945124447</v>
+        <v>0.07440586784895231</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.09558253211024947</v>
+        <v>-0.09639541836416043</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1663706499417188</v>
+        <v>-0.1671214141053383</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2463535295501487</v>
+        <v>-0.2477823857387023</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1916421383483922</v>
+        <v>-0.1931314634853791</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2908297831729953</v>
+        <v>-0.2922253040106142</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3732007571806406</v>
+        <v>-0.3745074096686452</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4042813112526815</v>
+        <v>-0.4055504951410782</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4139366505125537</v>
+        <v>-0.4152188446945075</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3614874882275672</v>
+        <v>-0.3628248367383762</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4738682370261316</v>
+        <v>-0.4750807738152432</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.534149015072849</v>
+        <v>-0.5353248188975428</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6182467857622669</v>
+        <v>-0.6193297153983224</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4514201762891972</v>
+        <v>-0.4527236524770331</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4672335608828959</v>
+        <v>-0.468500797448165</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3739921677938938</v>
+        <v>-0.3753759971919379</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4012945798823822</v>
+        <v>-0.4026499032544493</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4970153269359869</v>
+        <v>-0.4982503496551018</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5320743405275792</v>
+        <v>-0.5332625297829097</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5179005589229888</v>
+        <v>-0.5191233263533661</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.6060330891156624</v>
+        <v>-0.607153487744128</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.5834667067992996</v>
+        <v>-0.5846065678119032</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5816361632372207</v>
+        <v>-0.58278143840068</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 18.74</t>
+          <t>X &lt; 18.7</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3337</v>
+        <v>3341</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01340712003651134</v>
+        <v>-0.01421215504908702</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.02464175182876005</v>
+        <v>0.02378138111147621</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1184434833496297</v>
+        <v>-0.1191753819906438</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1901961191817136</v>
+        <v>-0.1908635675807062</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2408137604100204</v>
+        <v>-0.242149357564692</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2157095805709659</v>
+        <v>-0.2170705670924278</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2860935461702709</v>
+        <v>-0.2873937743003481</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3389316189314258</v>
+        <v>-0.3401777611516366</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3698936610005816</v>
+        <v>-0.3711025566999311</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4105208035153893</v>
+        <v>-0.4117043753126453</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.3278886661942337</v>
+        <v>-0.329163723754732</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4106486228015029</v>
+        <v>-0.4118338589284818</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4724998406893093</v>
+        <v>-0.4736445338419273</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5567842400095415</v>
+        <v>-0.5578355507887309</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3911732093460429</v>
+        <v>-0.3924421005951899</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4060554686369002</v>
+        <v>-0.4072902811332142</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3131356955670128</v>
+        <v>-0.3144862691595094</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3405360880766253</v>
+        <v>-0.34185785800085</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.4357721020237904</v>
+        <v>-0.4369746668695598</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4704803950912861</v>
+        <v>-0.4716369021144828</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4571225646865855</v>
+        <v>-0.4583116344592568</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5452186572131836</v>
+        <v>-0.5463053816436698</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.5222562717953423</v>
+        <v>-0.5233633428997067</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5205239149216538</v>
+        <v>-0.5216361014526356</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 19.36</t>
+          <t>X &lt; 19.32</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0003802306669413724</v>
+        <v>-0.0004310658836743642</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.03832212722392114</v>
+        <v>0.03745575528124334</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1051450474761992</v>
+        <v>-0.1058820330696832</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1770849204260543</v>
+        <v>-0.1777570040508678</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2277923861837152</v>
+        <v>-0.2291235432520651</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2026360365569957</v>
+        <v>-0.2039926952768383</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2732254890780439</v>
+        <v>-0.2745208883748589</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3261270229351112</v>
+        <v>-0.327368173192788</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.357063630258331</v>
+        <v>-0.358267582513669</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3979056827485294</v>
+        <v>-0.399083786967644</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3152125659434688</v>
+        <v>-0.3164822890374595</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3980273457885346</v>
+        <v>-0.3992071045432226</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4601920956929462</v>
+        <v>-0.4613305514929209</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5445137604452981</v>
+        <v>-0.545558732484217</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.409022918544899</v>
+        <v>-0.410249215423903</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4237282224861758</v>
+        <v>-0.4249208502939794</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3308815992581629</v>
+        <v>-0.3321898009115358</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3583104992220996</v>
+        <v>-0.3595898164693381</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4534586924197157</v>
+        <v>-0.4546190017254617</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4881059245960486</v>
+        <v>-0.4892203093821124</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.4749199540443456</v>
+        <v>-0.4760664781522621</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.5630177400896628</v>
+        <v>-0.5640619020884472</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.5399852697068042</v>
+        <v>-0.541049933295632</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5382814936282259</v>
+        <v>-0.5393511915748022</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 19.98</t>
+          <t>X &lt; 19.94</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.01415937949607837</v>
+        <v>0.01334183487462326</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05199436196131302</v>
+        <v>0.05112200203694073</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.09185452733839838</v>
+        <v>-0.09259658744772992</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1639815282787609</v>
+        <v>-0.1646582350875079</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.214778767391735</v>
+        <v>-0.2161054777879201</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1895702813687663</v>
+        <v>-0.1909226055926396</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.260365100672999</v>
+        <v>-0.2616556648814736</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3133300600809577</v>
+        <v>-0.3145662122586259</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3442412501009073</v>
+        <v>-0.345440252743245</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.385298086658544</v>
+        <v>-0.3864707175909672</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3025440289983479</v>
+        <v>-0.3038084117902216</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3854136016177137</v>
+        <v>-0.3865878772842635</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.447891698604046</v>
+        <v>-0.4490239120075614</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5322506087278995</v>
+        <v>-0.5332892370656666</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3969933865793607</v>
+        <v>-0.3982127699215852</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4413904159805924</v>
+        <v>-0.442540896882889</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.348616895714585</v>
+        <v>-0.3498827633908661</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3760742829169743</v>
+        <v>-0.3773111855329461</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4711347047113392</v>
+        <v>-0.4722527963574379</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5057209093628501</v>
+        <v>-0.5067932096839414</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.492706692660434</v>
+        <v>-0.4938107092668531</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5808061680227823</v>
+        <v>-0.5818078057795972</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.5577036514518525</v>
+        <v>-0.5587259455872555</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.5560284358695498</v>
+        <v>-0.5570556833780174</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_12.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/volatility/realized_vol_12.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -618,2379 +618,2297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 2.252</t>
+          <t>X ≈ 2.249</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.085841642695264</v>
+        <v>5.063625499780201</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.75407446081595</v>
+        <v>5.43365175447483</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.46574255451538</v>
+        <v>9.708196094904473</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.331463707848826</v>
+        <v>10.34965137963388</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.14341618671276</v>
+        <v>10.07894283393657</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.76118750612531</v>
+        <v>9.010241996141183</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.57000161651273</v>
+        <v>12.5204266134868</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.5815269360546</v>
+        <v>10.37782956237236</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.77101878730355</v>
+        <v>11.73787998881985</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>11.43324010033248</v>
+        <v>10.33412321597758</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.992492871174584</v>
+        <v>8.764043337497995</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.145728265901127</v>
+        <v>7.261694258768784</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.029777396263647</v>
+        <v>6.76857916052446</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.801782169563211</v>
+        <v>3.446669865736553</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>2.5733578449776</v>
+        <v>2.151747254738581</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>1.447182101394624</v>
+        <v>1.480788050637628</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.4064384501701355</v>
+        <v>0.1455538960245235</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.08484258945488</v>
+        <v>-0.603220467182382</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-2.591160487075861</v>
+        <v>-2.238353116801946</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.257510816145924</v>
+        <v>-1.408393525148227</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-2.374257306843134</v>
+        <v>-2.592627057540419</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.7278982898879036</v>
+        <v>-2.668796877286525</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.6951460326235761</v>
+        <v>-1.192100487664028</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.6193602964871374</v>
+        <v>-1.972122891230157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 2.873</t>
+          <t>X ≈ 2.859</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.7993848306487195</v>
+        <v>-0.6651631948129548</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.878997355694445</v>
+        <v>0.9915328475117988</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.510612951574608</v>
+        <v>-0.2553831201058969</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.09660978990113023</v>
+        <v>-1.224184696305443</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4703013356992614</v>
+        <v>-0.3560523414521555</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.3030931580384788</v>
+        <v>-1.342375153393839</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5965709709638176</v>
+        <v>-1.753170244348027</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.797819413914148</v>
+        <v>0.6107731855787222</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.7163783125930507</v>
+        <v>-0.7859344727590951</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.822845232483282</v>
+        <v>-3.866163245980445</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.384503928471389</v>
+        <v>-5.884714681107198</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.080438042118821</v>
+        <v>-7.305963006825777</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.845987761171642</v>
+        <v>-7.654919845358229</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.067486138255681</v>
+        <v>-8.285760136331625</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-8.790338073863197</v>
+        <v>-9.732554412248355</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-8.200500904906477</v>
+        <v>-8.79388359360086</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-9.046810799279669</v>
+        <v>-10.04719813703354</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-10.93016912075396</v>
+        <v>-11.71264933552655</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-8.231630950279133</v>
+        <v>-8.442576182258144</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-8.403559238019788</v>
+        <v>-9.379307394458358</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-7.526570273503708</v>
+        <v>-8.035760427686881</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.027745574793556</v>
+        <v>-9.262567472928971</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.468233763389073</v>
+        <v>-9.022475059033084</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-8.479915688296138</v>
+        <v>-8.038534130054821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 3.494</t>
+          <t>X ≈ 3.469</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.9632555066238311</v>
+        <v>0.8267889189738327</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.421976262666206</v>
+        <v>-2.210422034897853</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.324458714727697</v>
+        <v>-3.4718343138113</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02232634216992579</v>
+        <v>-0.8765843672012892</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.602235194908388</v>
+        <v>-2.750616749820466</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.41680650945726</v>
+        <v>-3.792376624732441</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.27484175225861</v>
+        <v>-1.571993440314102</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.464151485232449</v>
+        <v>-3.250224688894548</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.952060635173147</v>
+        <v>-4.095448742626495</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.895053541649638</v>
+        <v>-0.8918571619928599</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.8560281447828331</v>
+        <v>-1.019655276806745</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.930620098459656</v>
+        <v>1.904729125290842</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.8140742942169368</v>
+        <v>0.7959419050368339</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.9372359899424509</v>
+        <v>-0.6503131432241673</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.473226729164182</v>
+        <v>1.871917113590882</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.915679397411175</v>
+        <v>1.230530306996876</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.01536162874891289</v>
+        <v>-0.07432639006310637</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.213358493865535</v>
+        <v>1.796648785057457</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.8932382776567493</v>
+        <v>0.006155084557406099</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.463542254450445</v>
+        <v>3.026997044986118</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.305781241948154</v>
+        <v>2.861831827610835</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.4613446271873087</v>
+        <v>1.984601458978617</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-1.956007175113427</v>
+        <v>-0.9834640743161742</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-1.648544212796629</v>
+        <v>-0.744992146026938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 4.114</t>
+          <t>X ≈ 4.079</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.409837487879095</v>
+        <v>-1.970889939704357</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.783121151883876</v>
+        <v>-4.96182577356165</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.442901001766963</v>
+        <v>-0.7140935960057035</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.500421480496193</v>
+        <v>-1.990649271004131</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.447183473568572</v>
+        <v>-2.264323200208146</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.261539147693959</v>
+        <v>-0.3884968138969427</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.074530488773618</v>
+        <v>-2.212465975345005</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.785316949583844</v>
+        <v>-4.922924263509792</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.312415279255006</v>
+        <v>-3.4183446582851</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.999060097267112</v>
+        <v>-2.490859828069503</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.117739051335455</v>
+        <v>-2.563682110135183</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.613678039790472</v>
+        <v>-0.08505910286599061</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.04896211928041794</v>
+        <v>0.5289192558002185</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5245827697326177</v>
+        <v>0.6284885410662255</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4823297950359162</v>
+        <v>-0.396247145143434</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.5855778994721845</v>
+        <v>-0.8718948180157753</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.069418892709784</v>
+        <v>-0.9754418237485538</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.524547956401619</v>
+        <v>-1.79912805497203</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-1.309557515524297</v>
+        <v>-1.241255736397413</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.170931161222043</v>
+        <v>-3.101302935212779</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.319094726159953</v>
+        <v>-1.942018839457603</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-1.746415361004637</v>
+        <v>-2.364175981012693</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.123433204855218</v>
+        <v>-1.084643256977969</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.9842085484608063</v>
+        <v>-1.59406317060953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 4.735</t>
+          <t>X ≈ 4.689</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>298</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.326860290305945</v>
+        <v>3.546581917452407</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.991600971890939</v>
+        <v>5.468610787861323</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.883832813687924</v>
+        <v>2.044850053417619</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.166628622378546</v>
+        <v>1.626840597664042</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.170451203840685</v>
+        <v>-1.139050042236875</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.649817152095579</v>
+        <v>-2.797165384159328</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.427429314749872</v>
+        <v>-3.597304404652512</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.851693950817122</v>
+        <v>-3.573116241863822</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.618970234385408</v>
+        <v>-2.444039024342793</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7247886237874965</v>
+        <v>-2.579693196858962</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.552282986075888</v>
+        <v>-0.3045243408135434</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.61258685097291</v>
+        <v>2.091865395787927</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.489851992197018</v>
+        <v>3.167282002719652</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.939580438986525</v>
+        <v>4.452395544733299</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.949614070557494</v>
+        <v>4.306346725292009</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.208839351406226</v>
+        <v>3.398556437954682</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.408657064420709</v>
+        <v>3.9660407614153</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2.963295422737836</v>
+        <v>3.165877442694367</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.181222120065122</v>
+        <v>3.714948685994173</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.028216852093237</v>
+        <v>1.920245551003454</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.160532052731313</v>
+        <v>2.693699082363374</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>4.632888535215294</v>
+        <v>4.295422784150503</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.766472346053988</v>
+        <v>2.527472676620455</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>3.026210562629295</v>
+        <v>3.372147553711635</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 5.356</t>
+          <t>X ≈ 5.299</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.506412050388874</v>
+        <v>5.255000760194505</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.48434118052505</v>
+        <v>4.165259861629224</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.23527009640943</v>
+        <v>5.842123504711374</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11.31790213204829</v>
+        <v>10.70608493179091</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.30167727576341</v>
+        <v>11.68387002177111</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>15.97875867897015</v>
+        <v>16.4616051002707</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15.22050914227815</v>
+        <v>14.8203256224693</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>15.81756375178695</v>
+        <v>15.35057343199574</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13.68142228622462</v>
+        <v>12.53827878677986</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>13.79073319225967</v>
+        <v>13.66105756795847</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>12.326524704721</v>
+        <v>12.49709293828083</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>11.18017041284151</v>
+        <v>12.46293346949686</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>12.68981767091699</v>
+        <v>13.0344543325404</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>14.22598706995004</v>
+        <v>14.47001753375313</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>16.20070715883563</v>
+        <v>16.31215058237968</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>15.05301109075288</v>
+        <v>16.87224734680784</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>15.36569392903986</v>
+        <v>16.35796236609846</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>15.70724156488623</v>
+        <v>16.23449731217299</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>15.93041463507162</v>
+        <v>16.03476813776709</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>16.56341003588817</v>
+        <v>17.52006480358575</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>15.1517362124306</v>
+        <v>16.54004906527297</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>15.0758902510217</v>
+        <v>16.47282868163943</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>14.47317198104751</v>
+        <v>14.61567855637028</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>13.95874323659626</v>
+        <v>13.61625029208012</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 5.976</t>
+          <t>X ≈ 5.909</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.390473736801347</v>
+        <v>2.265830902394882</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.370701481468714</v>
+        <v>3.955185902280633</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.563625128808866</v>
+        <v>4.154164946862032</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1985579843536698</v>
+        <v>1.629554768163921</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.9618744120219205</v>
+        <v>0.874698330722893</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.77867000785659</v>
+        <v>1.029341544946192</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.517093999041812</v>
+        <v>2.171048296152762</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.680209569543244</v>
+        <v>2.83515845440121</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8505235104446456</v>
+        <v>2.964359803960058</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.707084253933878</v>
+        <v>5.552916995228912</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.546171116194117</v>
+        <v>4.858666287925772</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.268679076076509</v>
+        <v>3.131210554706122</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.593022253429368</v>
+        <v>2.988911870561886</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.692152966776241</v>
+        <v>4.193078515727009</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.160585681566701</v>
+        <v>4.479954735498914</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.0007383474059707851</v>
+        <v>3.590384975570224</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.185552784187372</v>
+        <v>3.491387309670777</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.6429517550422332</v>
+        <v>2.395331717308693</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.4187639696677152</v>
+        <v>1.158098494254261</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.2746587520940906</v>
+        <v>1.372989844179443</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.257955417525245</v>
+        <v>0.3224003149124997</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.333801378934446</v>
+        <v>-0.7221470848235754</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.6187980320910569</v>
+        <v>0.9766284245294585</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.1864269834080829</v>
+        <v>1.300081351848149</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 6.597</t>
+          <t>X ≈ 6.518</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.376463826662999</v>
+        <v>0.160350810681706</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.711549840076422</v>
+        <v>-0.8680412054641664</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.97744527644717</v>
+        <v>-2.906715305993018</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.803090445343763</v>
+        <v>-3.109690050960367</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.316483212285647</v>
+        <v>-1.045693831623566</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1145854991198547</v>
+        <v>-0.496343135393893</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.314401294837197</v>
+        <v>-0.9037060574374962</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1124359309130796</v>
+        <v>-0.03906286658449432</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.167150666959373</v>
+        <v>0.08779831581720288</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6250961488210294</v>
+        <v>-0.7091073612280283</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.200711761623637</v>
+        <v>2.29638037578291</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.682554904418396</v>
+        <v>1.629943876557761</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1492255105294404</v>
+        <v>1.291130575854659</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7593814210028711</v>
+        <v>2.212460148683078</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.7591741371785758</v>
+        <v>0.3568983143198423</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.5251137032661362</v>
+        <v>-1.424128117230914</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.224508885221439</v>
+        <v>1.431609030563756</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.122444013010529</v>
+        <v>1.530327841135936</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.5065433149264038</v>
+        <v>1.354380482862055</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.942937167259053</v>
+        <v>2.35160506904819</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>1.401736212430649</v>
+        <v>1.395537838495464</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.325890251021605</v>
+        <v>1.713336571695947</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>2.017031630170322</v>
+        <v>1.958177434841723</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.6911993769470968</v>
+        <v>1.796940289598012</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 7.217</t>
+          <t>X ≈ 7.128</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.808688320934763</v>
+        <v>-5.115909942473081</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.798821805172153</v>
+        <v>-2.800769071332191</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.489775385444069</v>
+        <v>-1.50377977775814</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.219666132204132</v>
+        <v>-1.586915504487912</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.162466187711786</v>
+        <v>-3.934321260880473</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.724933781459228</v>
+        <v>-2.734775052893561</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.697157401169513</v>
+        <v>-3.031292663195586</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.7089496512577398</v>
+        <v>0.2580828908501971</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.040363783925294</v>
+        <v>1.408558020996452</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.3767979556658076</v>
+        <v>2.151008012159679</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.4558546278926485</v>
+        <v>1.916652072222675</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.158066350456536</v>
+        <v>0.0988931138317426</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1632294658920088</v>
+        <v>-1.558709444908722</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.09951380474692</v>
+        <v>-0.7857350446481846</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.3242773690217646</v>
+        <v>-0.9693250246025045</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.324137933564742</v>
+        <v>0.1025832250639525</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>5.232269721612411</v>
+        <v>1.023924551338055</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>5.43567491434024</v>
+        <v>0.8749873409549949</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.433235310888115</v>
+        <v>1.395264081618208</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>7.037937510937113</v>
+        <v>1.615754380446859</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5.725506704233972</v>
+        <v>1.039421824368389</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.103212655393172</v>
+        <v>0.235682834537819</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>5.377687367875225</v>
+        <v>0.7842891591678196</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>3.116062764925189</v>
+        <v>-0.6166437006991359</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 7.838</t>
+          <t>X ≈ 7.738</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.396158468743302</v>
+        <v>-0.4710034822961475</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.167321103478905</v>
+        <v>0.8260957930829349</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.465702107824896</v>
+        <v>-0.9533727404440313</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.594307352075433</v>
+        <v>-0.5173863353215609</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.918624446314723</v>
+        <v>-1.320258138177188</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.726272044034395</v>
+        <v>-2.184095442747392</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7893212298220362</v>
+        <v>-1.957560134038239</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.066063706525192</v>
+        <v>-3.808025919650483</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-5.596984408072387</v>
+        <v>-3.682636241087224</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.515205507049252</v>
+        <v>-3.964070229154366</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.952983299089809</v>
+        <v>-4.718530997733637</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.232712014571199</v>
+        <v>-5.511423280104232</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.47057600332716</v>
+        <v>-5.09854467319709</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.834512022630832</v>
+        <v>-4.834700458598732</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.635512463068466</v>
+        <v>-3.979773602016145</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-5.183982683982684</v>
+        <v>-2.904698486417978</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-5.889328392388727</v>
+        <v>-2.493961390990904</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-5.422740524781339</v>
+        <v>-1.090610668058432</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-4.063992000999939</v>
+        <v>0.1573186252597836</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.877146191031841</v>
+        <v>1.190984108787113</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.133978073283458</v>
+        <v>2.469806835421871</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.638395463264118</v>
+        <v>2.394644313466586</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-5.363920750782</v>
+        <v>0.06095921111609925</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.725467289719617</v>
+        <v>0.9297480518781214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 8.459</t>
+          <t>X ≈ 8.348</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.325778620281163</v>
+        <v>-6.140029325513126</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.345486925480408</v>
+        <v>-7.035286810567719</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.358848440264829</v>
+        <v>-6.991279613758067</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-4.07180245970757</v>
+        <v>-8.233032461916942</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.352798411706971</v>
+        <v>-4.612486705912339</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7959692119108865</v>
+        <v>-0.5594492038102601</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4868766247467065</v>
+        <v>0.5935207320089759</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2086651799936732</v>
+        <v>-0.3607503607504086</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4347791449409755</v>
+        <v>-0.2328214510662576</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.892626327826783</v>
+        <v>-2.9769248943375</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.121159341732401</v>
+        <v>-0.7566379316813041</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8424099382844048</v>
+        <v>0.2654814125486951</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.404179378277604</v>
+        <v>-1.498761354252608</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1831005018310137</v>
+        <v>-1.746995415685859</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.159974302598982</v>
+        <v>-2.429149797570965</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.935450394354504</v>
+        <v>-4.46524837615371</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-4.124162051879878</v>
+        <v>-6.517180735930658</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.174208235153159</v>
+        <v>-6.000714191741615</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-6.067905895324643</v>
+        <v>-8.383654561998519</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-6.565991592206011</v>
+        <v>-8.81841876629025</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.738674746473485</v>
+        <v>-8.736512618320269</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-6.499452214731825</v>
+        <v>-8.162324490924902</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.485251474852511</v>
+        <v>-6.619988706945222</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-2.876152221226548</v>
+        <v>-6.782127701234685</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 9.079</t>
+          <t>X ≈ 8.958</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.359152886567941</v>
+        <v>5.32834101382489</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.824376088218216</v>
+        <v>2.663079339411347</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.386357039187224</v>
+        <v>4.634191689132706</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1265969802555063</v>
+        <v>6.461144329034113</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3376125471971605</v>
+        <v>6.185586188934828</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-4.275421266705408</v>
+        <v>-0.9155447211961132</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-7.447369950595757</v>
+        <v>-2.517078346332113</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.925581395348878</v>
+        <v>-4.434902015547138</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.884094213434132</v>
+        <v>-5.113424718766304</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.857009889470618</v>
+        <v>-3.490121375276011</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-7.382950247308699</v>
+        <v>-3.217886360671528</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.861699650756691</v>
+        <v>-2.688016702239601</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>1.035800857728887</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2059405940594061</v>
+        <v>-0.01888481660744645</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.535916108360126</v>
+        <v>2.524767253120395</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.530303030303031</v>
+        <v>5.505426110649736</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.396385893325473</v>
+        <v>4.595094086021504</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.691545189504382</v>
+        <v>6.881564819569491</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>8.507436570428645</v>
+        <v>6.289575433812118</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>8.694282380396729</v>
+        <v>6.504161878871201</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>10.55173621243069</v>
+        <v>8.356072216200047</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>8.075890251021598</v>
+        <v>7.474458081341545</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>10.75036496350356</v>
+        <v>8.52454417952314</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>8.274532710280475</v>
+        <v>7.555953572330559</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 9.7</t>
+          <t>X ≈ 9.567</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-12.11542338461836</v>
+        <v>-12.63353581901968</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-6.517996793137712</v>
+        <v>-4.697624472905424</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.023812452338191</v>
+        <v>-1.406864029342465</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.584224098899575</v>
+        <v>-4.726538955423365</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.012188818383699</v>
+        <v>-0.4566425500681532</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.885590758230826</v>
+        <v>-5.754254398615572</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.427206320590685</v>
+        <v>-2.912972774484601</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.240835632636973</v>
+        <v>-5.03607503607504</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.046806077840913</v>
+        <v>-3.089964308209112</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.972264126758759</v>
+        <v>-3.88601580342845</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.393119738834116</v>
+        <v>-5.431962607005993</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-7.21424202363805</v>
+        <v>-3.890362743295469</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.795031209138187</v>
+        <v>-1.368891224382502</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-8.558482966940758</v>
+        <v>-4.344398013088394</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-10.06408389164005</v>
+        <v>-7.753825122246113</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-6.927324088341031</v>
+        <v>-2.647066557971968</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-7.061241225318462</v>
+        <v>-2.750946969696976</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-6.318624302021043</v>
+        <v>-1.065649256676757</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-7.797648175333961</v>
+        <v>-0.8511870295309834</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-8.458259992484628</v>
+        <v>-1.545691493562906</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-8.153348533332014</v>
+        <v>-0.29495417676182</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-4.839363986266541</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.717431646665844</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.098348645651825</v>
+        <v>5.165924246817262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 10.32</t>
+          <t>X ≈ 10.18</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4298379391200342</v>
+        <v>-2.379836030436174</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.269201893433156</v>
+        <v>-8.05209945528734</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.872358557143045</v>
+        <v>-6.981212161830122</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.998156613283037</v>
+        <v>-2.922451569940669</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.251378278490854</v>
+        <v>-1.647622113140784</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.981843285054033</v>
+        <v>-1.490688507142657</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-6.588654354265529</v>
+        <v>-3.836158116274639</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4448474503947608</v>
+        <v>0.51008423101446</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.431502116841102</v>
+        <v>-0.1371806577510881</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.093707137177049</v>
+        <v>-3.258813548319225</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.489372265657323</v>
+        <v>-6.862547525962995</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.35527763240802</v>
+        <v>-11.01509847268226</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-13.31330208458539</v>
+        <v>-13.6803781870323</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-15.36924334635303</v>
+        <v>-14.70380604691503</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-12.35766187329128</v>
+        <v>-12.28518523500163</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-9.010981373366697</v>
+        <v>-10.17349361928275</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-7.31003612502311</v>
+        <v>-8.726986434108532</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.414876828844193</v>
+        <v>-7.309482942370906</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.364123062598871</v>
+        <v>-6.319826916775511</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.424983674649141</v>
+        <v>-4.554852874817271</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.967529842615171</v>
+        <v>-5.122297376198006</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.043375804024272</v>
+        <v>-4.42226609970372</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.68633228420282</v>
+        <v>-5.729019211324569</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.009870959444392</v>
+        <v>-4.340770608714806</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 10.94</t>
+          <t>X ≈ 10.79</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-11.17509368877443</v>
+        <v>-10.25904463855836</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-6.030418432329732</v>
+        <v>-3.042264907098001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-12.94788953615524</v>
+        <v>-10.26710826272089</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-10.92111752820076</v>
+        <v>-9.366973148096278</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-19.47608608293977</v>
+        <v>-17.10521785535979</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-17.91925688314377</v>
+        <v>-15.45574693592896</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-22.80079460812997</v>
+        <v>-19.23590357502726</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-24.44886906658164</v>
+        <v>-19.54082401843596</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-24.40738188466701</v>
+        <v>-20.9054324221846</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-25.1802975607035</v>
+        <v>-20.20894660397119</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-26.2761009322402</v>
+        <v>-21.42924890279953</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-26.55485033568828</v>
+        <v>-24.69090548413675</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-20.82869733405109</v>
+        <v>-15.35803640755775</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-23.78950223789502</v>
+        <v>-21.57641972272204</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-18.96819348068106</v>
+        <v>-14.79588753744292</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-17.00394354503943</v>
+        <v>-14.23458351862325</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-17.13786068201676</v>
+        <v>-14.33846393034826</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-15.87283837213962</v>
+        <v>-14.47134803550986</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-15.65694699121498</v>
+        <v>-15.74942312179693</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-15.47010118124711</v>
+        <v>-15.53483667673802</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-14.64278433551451</v>
+        <v>-14.60974386468592</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-14.71863029692361</v>
+        <v>-16.17744370007397</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-13.07429257074285</v>
+        <v>-14.44127190136275</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-15.88985085136346</v>
+        <v>-16.09594820908505</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 11.56</t>
+          <t>X ≈ 11.39</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.450061977477127</v>
+        <v>0.8051993588459183</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.702896639054543</v>
+        <v>-5.962446607292698</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-7.686370233540046</v>
+        <v>-9.391053752662572</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.262960616619146</v>
+        <v>-9.983455951470795</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3557943653790332</v>
+        <v>-8.085101048091865</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.088215096930959</v>
+        <v>-4.66729787687639</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8.861720958495148</v>
+        <v>-1.114553802152585</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.174418604651201</v>
+        <v>-4.680343810778638</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.079542150202236</v>
+        <v>-4.552414901094494</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.579353746893013</v>
+        <v>-4.261509874574671</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.853413389054936</v>
+        <v>-3.989274859970429</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.574663985606939</v>
+        <v>-4.265856814441655</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.724229191478067</v>
+        <v>-5.380748931892377</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.503150315031533</v>
+        <v>-4.542026471586418</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>5.845007017450975</v>
+        <v>-5.224180853471502</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>4.166666666666664</v>
+        <v>-4.66287683465184</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.760022256961889</v>
+        <v>-6.940670289855042</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.791545189504475</v>
+        <v>-4.899641351538385</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.007436570428602</v>
+        <v>-4.685179124392612</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.351172165057783</v>
+        <v>-7.731462244551075</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.893718333023841</v>
+        <v>-7.21195022419262</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.833200658069309</v>
+        <v>-6.200156224408836</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.55872594558722</v>
+        <v>-4.869565217391269</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.5018054375531378</v>
+        <v>-3.9447476899416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 12.18</t>
+          <t>X ≈ 12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.046652886568076</v>
+        <v>8.752455239102474</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8506239117817387</v>
+        <v>10.14589266569378</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.976142960812815</v>
+        <v>-0.9448670099683412</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.001596980255471</v>
+        <v>1.741419315813637</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.899887452802787</v>
+        <v>6.383893962599508</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-9.400421266705365</v>
+        <v>4.901483306302509</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-13.29736995059567</v>
+        <v>0.8277127694796249</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-15.13808139534888</v>
+        <v>0.5227923260710483</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-13.53409421343413</v>
+        <v>2.290065498050197</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.494509889470663</v>
+        <v>8.051391052011141</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.09545024730874</v>
+        <v>6.684281804320449</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2491996507566938</v>
+        <v>9.686388374439304</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.877638282387231</v>
+        <v>15.12887330616886</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>12.46905940594064</v>
+        <v>19.798672031621</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>13.37341610836</v>
+        <v>20.75586191203107</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>13.96780303030303</v>
+        <v>21.31716593085073</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>13.83388589332552</v>
+        <v>19.57394125683056</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>13.72904518950433</v>
+        <v>17.80171288937387</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>13.94493657042874</v>
+        <v>19.65551937881473</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>15.69428238039669</v>
+        <v>19.8701058238738</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>13.5892362124307</v>
+        <v>16.02397279790281</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>13.5133902510216</v>
+        <v>15.94881027594763</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>13.78786496350361</v>
+        <v>16.19244476122591</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>12.14953271028033</v>
+        <v>14.39096150464135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 12.8</t>
+          <t>X ≈ 12.62</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.803637811106455</v>
+        <v>-11.5426267281106</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.163910971939153</v>
+        <v>-7.788533563814468</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.377054713605901</v>
+        <v>-3.043227665706048</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.638224887232262</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-9.950759545826045</v>
+        <v>-13.91118800461361</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-9.76379335972873</v>
+        <v>-15.75425439861552</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-10.53574204361908</v>
+        <v>-18.54933641084824</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.488372093023258</v>
+        <v>-16.85425685425686</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-8.446884911108484</v>
+        <v>-16.72632794457281</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-11.54538198249381</v>
+        <v>-17.52237943979209</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.620159549634273</v>
+        <v>-5.250144425187756</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.89890895308227</v>
+        <v>-5.526726379659053</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-10.34765241528724</v>
+        <v>-6.641618497109825</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-8.243149896385049</v>
+        <v>-0.8898525585428843</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.401032387429801</v>
+        <v>4.42799305957201</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.655743481324876</v>
+        <v>-1.010702921608335</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.8615021723953191</v>
+        <v>4.885416666666664</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>3.082242863922914</v>
+        <v>6.752532561505063</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.972552849498399</v>
+        <v>4.966994788650837</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.166182735882337</v>
+        <v>3.181581233709821</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.708728903848368</v>
+        <v>2.614136732329086</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.784574865257532</v>
+        <v>4.538974210373802</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.510100152775415</v>
+        <v>4.782608695652179</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-3.911513801347532</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 13.42</t>
+          <t>X ≈ 13.22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>15.58992211733726</v>
+        <v>24.71824283710685</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>15.25514531898745</v>
+        <v>20.12450991444628</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.124818577648824</v>
+        <v>18.86981581255481</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9.258018404359817</v>
+        <v>18.27741361374648</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>8.922227931812657</v>
+        <v>22.34968156060378</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>12.95534796406382</v>
+        <v>13.81096299268882</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.337245434019628</v>
+        <v>17.36370706741251</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.212880143112763</v>
+        <v>12.71096053704748</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>11.94667501733498</v>
+        <v>12.83888944673183</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.327605495144766</v>
+        <v>7.695011864555738</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>15.29397282961448</v>
+        <v>7.967246879160072</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.476761887704846</v>
+        <v>-1.004987249224271</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.338707871459079</v>
+        <v>-2.119879366674915</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.713632901751602</v>
+        <v>-2.368113428108281</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-10.06408389163996</v>
+        <v>-3.050267809993208</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.777389277389325</v>
+        <v>-2.488963791173546</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-5.757460260520546</v>
+        <v>-2.592844202898554</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-5.862300964341671</v>
+        <v>-2.725728308060155</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-5.646409583417345</v>
+        <v>-2.511266080914382</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-5.459563773449482</v>
+        <v>-2.296679635855398</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.155956095261615</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.231802056670602</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.888826501965191</v>
+        <v>-2.695652173913039</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>5.659148094895706</v>
+        <v>1.490034918754027</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 14.04</t>
+          <t>X ≈ 13.84</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.28949576208062</v>
+        <v>2.554934247499197</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>13.59194365578578</v>
+        <v>7.187076192283094</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.15392460675472</v>
+        <v>1.054333309903711</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.072542926201422</v>
+        <v>-9.294166449880123</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2943693039539355</v>
+        <v>-12.00874898022336</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4813354900513929</v>
+        <v>-6.973766593737473</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-8.398721301947106</v>
+        <v>-12.64689738645793</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.271527341294778</v>
+        <v>-12.95181782986665</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.175365246025287</v>
+        <v>-5.506815749450901</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.300253132713863</v>
+        <v>-1.42481846418233</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.02619349055194</v>
+        <v>3.725465330909806</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.00764559670268</v>
+        <v>-3.868189794293194</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2745977418467618</v>
+        <v>-7.422106301987974</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.351886540005346</v>
+        <v>-7.670340363420948</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-3.30732713488316</v>
+        <v>-8.352494745306004</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-10.82104832104832</v>
+        <v>-7.791190726486377</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.846857349917762</v>
+        <v>-5.456046747967477</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.951698053738866</v>
+        <v>-5.588930853129078</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-2.73580667281454</v>
+        <v>-5.374468625983305</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.548960862846471</v>
+        <v>-5.15988218092432</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-5.794209733515245</v>
+        <v>-8.166351072548963</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-8.572758397627091</v>
+        <v>-10.68053798474815</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.1901755770368894</v>
+        <v>-0.6808059384941672</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-2.968710532962824</v>
+        <v>-0.8429449327836309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 14.66</t>
+          <t>X ≈ 14.45</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20.04336341288381</v>
+        <v>0.02880184331802838</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>22.34016556190244</v>
+        <v>17.64003786475696</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>15.63898861813463</v>
+        <v>16.38534376286538</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.66287670395505</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>14.59024412614454</v>
+        <v>15.51738342395777</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.514052417505042</v>
+        <v>12.10288845852734</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11.37368268098319</v>
+        <v>11.30780644629462</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11.09547123623007</v>
+        <v>14.57431457431457</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>11.1369584181449</v>
+        <v>18.2736720554273</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.732463794739914</v>
+        <v>6.763334845922245</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.374944489533405</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.727774033453869</v>
+        <v>10.33041647748381</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.341454071860838</v>
+        <v>9.215524360033079</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.015112037519543</v>
+        <v>8.96729029859987</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.725389792570532</v>
+        <v>1.142278773857619</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.688197767145176</v>
+        <v>1.703582792677338</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>14.08059641964138</v>
+        <v>8.742559523809526</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>8.712597821083321</v>
+        <v>5.038246847219355</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>8.928489202007647</v>
+        <v>5.252709074365129</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.852177117238831</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.6780520019044118</v>
+        <v>1.328422446614852</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.029372906873107</v>
+        <v>4.824688496088037</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-7.018056089127931</v>
+        <v>5.068322981366514</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>4.906183987077007</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 15.29</t>
+          <t>X ≈ 15.05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>29.06606892406325</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.821777757935678</v>
+        <v>28.82016208835948</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.124818577648767</v>
+        <v>23.21764189951134</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.280443134101724</v>
+        <v>18.27741361374653</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-25.6931566835718</v>
+        <v>18.00185547364732</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-17.81388280516684</v>
+        <v>13.81096299268889</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12.18339928017347</v>
+        <v>17.36370706741262</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>11.90518783542028</v>
+        <v>17.05878662400407</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.437940367280284</v>
+        <v>12.83888944673159</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.90316373562436</v>
+        <v>7.695011864555667</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-11.62910409346254</v>
+        <v>-0.7284052947529744</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.90785349691054</v>
+        <v>3.342838837732309</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-13.03101556376666</v>
+        <v>-2.119879366675043</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-28.63670982482863</v>
+        <v>6.327538745804894</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-29.29485312240919</v>
+        <v>9.993210450876425</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-28.7004662004662</v>
+        <v>1.858862295783034</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-28.83438333744367</v>
+        <v>14.79846014492747</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-28.93922404126485</v>
+        <v>10.31774995280941</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-28.72333266034053</v>
+        <v>10.53221217995518</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-20.8441791580648</v>
+        <v>2.051146451101133</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-21.38672532603095</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-21.46257128743994</v>
+        <v>-7.287112746147869</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-21.18809657495788</v>
+        <v>-15.73913043478267</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-28.95623652048875</v>
+        <v>-24.59692160298511</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 15.91</t>
+          <t>X ≈ 15.66</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.897614425029573</v>
+        <v>2.707373271889445</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.821777757935578</v>
+        <v>-10.03853356381451</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-9.25979680696657</v>
+        <v>-5.043227665706091</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.280443134101667</v>
+        <v>-5.635629864514186</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.616233606649054</v>
+        <v>-18.41118800461361</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-10.12157511285925</v>
+        <v>-12.00425439861561</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-18.58583148905729</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-18.86404293381027</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-18.82255575189589</v>
+        <v>-12.97632794457275</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-19.59547142793238</v>
+        <v>-13.77237943979209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-19.32141178577013</v>
+        <v>-13.50014442518776</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-19.60016118921823</v>
+        <v>-13.77672637965914</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-20.72332325607434</v>
+        <v>-14.89161849710974</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-13.25209444021314</v>
+        <v>-27.63985255854293</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-13.91023773779381</v>
+        <v>-28.3220069404279</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-21.0081585081585</v>
+        <v>-27.76070292160824</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-28.83438333744367</v>
+        <v>-27.86458333333325</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-21.24691634895716</v>
+        <v>-27.99746743849494</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-28.72333266034064</v>
+        <v>-27.78300521134916</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-36.2287945426803</v>
+        <v>-21.31841876629018</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-21.38672532603083</v>
+        <v>-21.885863267671</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-13.77026359513225</v>
+        <v>-21.96102578962628</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-13.4957888826502</v>
+        <v>-21.71739130434791</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-13.57162113587347</v>
+        <v>-21.87953029863728</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 16.53</t>
+          <t>X ≈ 16.27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-20.30751378009864</v>
+        <v>-3.542626728110648</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-13.97562391178178</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-8.746976294146201</v>
+        <v>9.242486620008286</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.79326364692227</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.129054119469409</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>-5.754254398615522</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.619296716070856</v>
+        <v>-6.549336410848241</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.382572453232626</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.942990110529479</v>
+        <v>-14.66523658264913</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.217049752691253</v>
+        <v>-7.250144425187806</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.48180494905376</v>
+        <v>-8.641618497109924</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.92739273927384</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>13.26924944169343</v>
+        <v>-2.42914979757095</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>20.53030303030307</v>
+        <v>-9.010702921608427</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>13.72971922665889</v>
+        <v>-23.40029761904762</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>-23.53318172420922</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-6.159230096237962</v>
+        <v>-37.60443378277783</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-12.63905095293651</v>
+        <v>-44.53270448057599</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-19.8482637875693</v>
+        <v>-30.81443469624234</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-19.9241097489784</v>
+        <v>-23.74674007534038</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-12.98296836982968</v>
+        <v>-16.36024844720486</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-6.392133956386381</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 17.15</t>
+          <t>X ≈ 16.88</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>13.02581955323482</v>
+        <v>-11.87596006144393</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.975623911781661</v>
+        <v>-28.78853356381441</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>27.91969037252067</v>
+        <v>-13.37656099903938</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.126596980255393</v>
+        <v>-13.9689631978476</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>43.53761254719709</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>43.72457873329459</v>
+        <v>19.24574560138448</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>42.95263004940436</v>
+        <v>18.45066358915176</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>42.67441860465117</v>
+        <v>18.14574314574308</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>42.71590578656574</v>
+        <v>18.27367205542725</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>41.94299011052938</v>
+        <v>25.81095389354113</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>25.55038308602452</v>
+        <v>9.416522241478901</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>25.27163368257652</v>
+        <v>17.473273620341</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>24.14847161572076</v>
+        <v>16.35838150289012</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>23.92739273927394</v>
+        <v>24.44348077479041</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>23.26924944169325</v>
+        <v>23.76132639290535</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>23.86363636363625</v>
+        <v>32.65596374505833</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>40.39638589332556</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>40.50743657042894</v>
+        <v>32.63366145531762</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>40.69428238039673</v>
+        <v>24.51491456704322</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>40.1517362124307</v>
+        <v>15.61413673232903</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>40.0758902510216</v>
+        <v>15.5389742103738</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>40.35036496350365</v>
+        <v>15.78260869565218</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>15.62046970136272</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 17.77</t>
+          <t>X ≈ 17.5</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>46.35915288656732</v>
+        <v>-53.54262672810989</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>46.02437608821751</v>
+        <v>46.21146643618553</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>44.58635703918723</v>
+        <v>44.95677233429395</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>43.87340301974449</v>
+        <v>-55.63562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>43.53761254719721</v>
+        <v>44.08881199538639</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>43.72457873329459</v>
+        <v>44.24574560138448</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>42.95263004940424</v>
+        <v>43.45066358915176</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>42.67441860465117</v>
+        <v>43.14574314574385</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>42.71590578656658</v>
+        <v>43.27367205542654</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>41.94299011053009</v>
+        <v>42.47762056020791</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>42.2170497526913</v>
+        <v>42.74985557481295</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>41.93830034924402</v>
+        <v>42.47327362033953</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>40.81513828238648</v>
+        <v>41.35838150289089</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>40.59405940593989</v>
+        <v>41.11014744145707</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>39.93591610836075</v>
+        <v>40.42799305957201</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>40.53030303030374</v>
+        <v>40.98929707839167</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>40.39638589332627</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>40.5074365704287</v>
+        <v>40.96699478865084</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>40.69428238039602</v>
+        <v>41.18158123371053</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>40.15173621242999</v>
+        <v>40.6141367323298</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>40.07589025102089</v>
+        <v>40.5389742103738</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>40.35036496350365</v>
+        <v>40.78260869565218</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136272</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 18.39</t>
+          <t>X ≈ 18.11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-33.64084711343182</v>
+        <v>-3.542626728110776</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-33.97562391178164</v>
+        <v>-3.788533563814646</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-15.41364296081277</v>
+        <v>19.95677233429395</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-16.12659698025551</v>
+        <v>19.36437013548573</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>19.08881199538639</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-16.27542126670541</v>
+        <v>19.24574560138448</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.952630049404242</v>
+        <v>18.45066358915176</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>22.67441860465117</v>
+        <v>18.14574314574314</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>22.71590578656587</v>
+        <v>43.27367205542742</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.94299011052923</v>
+        <v>17.47762056020791</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.2170497526913</v>
+        <v>17.74985557481224</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>41.93830034924331</v>
+        <v>42.4732736203413</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>40.81513828238732</v>
+        <v>41.35838150289018</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>40.59405940594073</v>
+        <v>41.11014744145707</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>39.9359161083599</v>
+        <v>40.42799305957201</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>40.53030303030289</v>
+        <v>40.98929707839167</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>40.39638589332542</v>
+        <v>40.88541666666666</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>40.29154518950438</v>
+        <v>40.75253256150506</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>40.50743657042856</v>
+        <v>40.96699478865084</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>40.69428238039686</v>
+        <v>41.18158123370982</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>40.15173621243083</v>
+        <v>40.61413673232909</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>40.07589025102173</v>
+        <v>40.5389742103738</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>40.35036496350365</v>
+        <v>40.78260869565218</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>40.27453271028038</v>
+        <v>40.62046970136272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 19.01</t>
+          <t>X ≈ 18.71</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>46.35915288656803</v>
+        <v>-20.20929339477703</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>46.02437608821822</v>
+        <v>-20.4552002304809</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44.58635703918723</v>
+        <v>-21.70989433237272</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>43.8734030197452</v>
+        <v>-22.3022965311807</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>43.53761254719721</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>43.72457873329459</v>
+        <v>-22.42092106528219</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>42.95263004940424</v>
+        <v>10.11733025581842</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>42.67441860465117</v>
+        <v>43.14574314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>42.71590578656587</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>41.94299011052938</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>42.2170497526913</v>
+        <v>42.74985557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>41.93830034924331</v>
+        <v>42.47327362034072</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>40.81513828238719</v>
+        <v>41.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>40.5940594059406</v>
+        <v>41.11014744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-60.06408389163925</v>
+        <v>7.094659726238923</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-59.46969696969626</v>
+        <v>7.655963745058585</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-59.60361410667444</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-59.70845481049562</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-59.49256342957059</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-59.30571761960327</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-59.8482637875693</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-59.9241097489784</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-59.64963503649635</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-59.72546728971962</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>X ≈ 19.63</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>46.35915288656732</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>46.02437608821751</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>44.58635703918652</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>43.87340301974378</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>43.53761254719721</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>43.72457873329459</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>42.95263004940424</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>42.67441860465117</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>42.71590578656658</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>41.94299011052938</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>42.2170497526913</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>41.93830034924331</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>40.8151382823879</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>40.5940594059406</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>39.93591610835933</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>-59.46969696969697</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>-59.60361410667444</v>
-      </c>
-      <c r="T34" s="4" t="n">
-        <v>-59.70845481049562</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>-59.49256342957201</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>-59.30571761960327</v>
-      </c>
-      <c r="W34" s="4" t="n">
-        <v>-59.8482637875693</v>
-      </c>
-      <c r="X34" s="4" t="n">
-        <v>-59.9241097489784</v>
-      </c>
-      <c r="Y34" s="4" t="n">
-        <v>-59.64963503649635</v>
-      </c>
-      <c r="Z34" s="4" t="n">
-        <v>-59.72546728971962</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
   </sheetData>
@@ -2999,7 +2917,7 @@
     <mergeCell ref="A3:Z3"/>
     <mergeCell ref="A2:Z2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6:Z34">
+  <conditionalFormatting sqref="C6:Z33">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-20"/>
@@ -3180,2461 +3098,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 1.942</t>
+          <t>X &gt; 1.945</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1024683945894296</v>
+        <v>0.08569185596019935</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.06774872604626836</v>
+        <v>0.03265262680223202</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0628700713954089</v>
+        <v>0.03351377467176064</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.04571681373752767</v>
+        <v>0.07739050749635368</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.007896078620753144</v>
+        <v>0.08408665575260699</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01734874222051275</v>
+        <v>0.05076775795759403</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.07004893194135775</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01291220393666492</v>
+        <v>-0.01121813122996684</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1310338389780128</v>
+        <v>0.1335183002528026</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.119933810261287</v>
+        <v>0.09371047443447367</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.08355750000954032</v>
+        <v>0.08713368132111299</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1797310496904032</v>
+        <v>0.2122496487517154</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3261698864420524</v>
+        <v>0.3873927521500988</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.4210799845269406</v>
+        <v>0.5119833905242857</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.3774435546607506</v>
+        <v>0.4990831069653723</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.3930305743197451</v>
+        <v>0.5448526339472224</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>0.5475387769215558</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.45875928326371</v>
+        <v>0.6102260094742249</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.4835417078241662</v>
+        <v>0.6645036854479969</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.5090418665036864</v>
+        <v>0.6891457546235031</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.522327963775588</v>
+        <v>0.732831094346885</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.5542161105133729</v>
+        <v>0.7051956410654014</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.5477333845562811</v>
+        <v>0.7291645151296109</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.5198213731580239</v>
+        <v>0.6442297251227345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 2.563</t>
+          <t>X &gt; 2.554</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3169</v>
+        <v>3205</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2260601460134168</v>
+        <v>-0.1659228867227469</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3874070518632564</v>
+        <v>-0.2403463930676466</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5860567539162247</v>
+        <v>-0.4555029291902386</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5605888272294877</v>
+        <v>-0.4418314149018627</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5652732746346558</v>
+        <v>-0.4211135629262657</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5176553426388892</v>
+        <v>-0.4020980225683672</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6443567679215576</v>
+        <v>-0.559268130277168</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6222846920521334</v>
+        <v>-0.5363431628566673</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5629886857959363</v>
+        <v>-0.4530360191069107</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5012448878997731</v>
+        <v>-0.4239016516591292</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.4605115295211348</v>
+        <v>-0.3514495836712825</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3125641587730428</v>
+        <v>-0.1440717324722414</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09681140314739878</v>
+        <v>0.06484916458171597</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2354560715587155</v>
+        <v>0.3636466638520872</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.2568726848232217</v>
+        <v>0.4155475088563989</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.3351503705611378</v>
+        <v>0.4975448219335377</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.4404664978595605</v>
+        <v>0.5678575134910773</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.5435136934413762</v>
+        <v>0.6715609015860338</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.6523641066605848</v>
+        <v>0.8112315487754529</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6060378168921545</v>
+        <v>0.795168020870932</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.6813705125567964</v>
+        <v>0.9009197747230928</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.6246130514000257</v>
+        <v>0.8757375405889647</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.5396394114531802</v>
+        <v>0.8262768179229241</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.514355998383877</v>
+        <v>0.7764759416123326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 3.184</t>
+          <t>X &gt; 3.164</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2888</v>
+        <v>2944</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.325835090072303</v>
+        <v>-0.1216627914742645</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6079263172800609</v>
+        <v>-0.3495585132412984</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7900609738756899</v>
+        <v>-0.4732445291124563</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6245337065278633</v>
+        <v>-0.3724719697774219</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.6660338236318211</v>
+        <v>-0.4268815584441867</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5975134896923251</v>
+        <v>-0.3187378557390801</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7650980056732095</v>
+        <v>-0.4534228681261894</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9550579793708778</v>
+        <v>-0.6380406380406427</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6874700315533104</v>
+        <v>-0.4235229428829896</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3726542726546356</v>
+        <v>-0.118728324173432</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07871033003878836</v>
+        <v>0.1391014321000412</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2486451768295055</v>
+        <v>0.4908649599891248</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.5598778477545565</v>
+        <v>0.749244447052611</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.9460262796466097</v>
+        <v>1.13045888356946</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1.137158773185725</v>
+        <v>1.315226381617386</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>1.165662146325133</v>
+        <v>1.321275398174869</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.363570694707249</v>
+        <v>1.508934118377951</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>1.659893496346122</v>
+        <v>1.769481714047437</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.516769442879443</v>
+        <v>1.631626867321572</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.482664123135315</v>
+        <v>1.69718503289571</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>1.479996330037061</v>
+        <v>1.693200186689459</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>1.563779524377999</v>
+        <v>1.774547869572721</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>1.513397154573227</v>
+        <v>1.699416845057954</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>1.389491159033838</v>
+        <v>1.557969701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 3.804</t>
+          <t>X &gt; 3.774</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2628</v>
+        <v>2695</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.453370689441023</v>
+        <v>-0.2092933947772622</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4284541004610318</v>
+        <v>-0.1776271526132902</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6382560223454306</v>
+        <v>-0.1961948606931543</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.6885305149987175</v>
+        <v>-0.3258953512399358</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4744766103396216</v>
+        <v>-0.2121839470702653</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4175225516638292</v>
+        <v>0.002203165960125375</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.7146667369851656</v>
+        <v>-0.35007441822831</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.7068219399781839</v>
+        <v>-0.3966922786111056</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2655546750307991</v>
+        <v>-0.08426152390854469</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2220363845501012</v>
+        <v>-0.04729638331368591</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.00180674106106693</v>
+        <v>0.2461628126261246</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08223974318269711</v>
+        <v>0.3602333543638494</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5347290364607034</v>
+        <v>0.7449299138288339</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.132345986683582</v>
+        <v>1.294990325006047</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>1.103910040859091</v>
+        <v>1.263791876140054</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>1.19039407734401</v>
+        <v>1.329659638510059</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>1.496955153287601</v>
+        <v>1.655216814705156</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>1.605136685328212</v>
+        <v>1.766971658135944</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.578458218738611</v>
+        <v>1.781809603465646</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.484555936627729</v>
+        <v>1.574319284839866</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.4972322215527</v>
+        <v>1.585226428400254</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.672848425926546</v>
+        <v>1.755140320866943</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.856641114131264</v>
+        <v>1.947297122951888</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.690057824435634</v>
+        <v>1.770747994498159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 4.425</t>
+          <t>X &gt; 4.384</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2342</v>
+        <v>2406</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2144511743456761</v>
+        <v>0.002303197693201753</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01878937940768566</v>
+        <v>0.3970334464948095</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4178766610667992</v>
+        <v>-0.13398674161364</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3451484415007471</v>
+        <v>-0.1259311439199706</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2335738934807523</v>
+        <v>0.03431158250447908</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1923352132929423</v>
+        <v>0.04913263153730441</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3043674060664969</v>
+        <v>-0.1263706942022296</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03547078963207184</v>
+        <v>0.1469823031161255</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2286392330853957</v>
+        <v>0.3162164585664442</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1170877750729034</v>
+        <v>0.2462156015302241</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5008220551551901</v>
+        <v>0.5836712011040959</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2893415732127096</v>
+        <v>0.4137202704650136</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.5940498470130322</v>
+        <v>0.7708763311897187</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.206564722827032</v>
+        <v>1.375048103708721</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.297618236019616</v>
+        <v>1.463189746942604</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.407271953248973</v>
+        <v>1.594102380794325</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.810355228930327</v>
+        <v>1.971201996132059</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.987327038673527</v>
+        <v>2.195318631156809</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.931136485177213</v>
+        <v>2.144929255676963</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.930956154383935</v>
+        <v>2.135938080182854</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>1.841156007652543</v>
+        <v>2.008906346276781</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.090401561307559</v>
+        <v>2.249937665523305</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.220561376825593</v>
+        <v>2.311482812810461</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.016633478854246</v>
+        <v>2.174916916657807</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 5.045</t>
+          <t>X &gt; 4.994</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2044</v>
+        <v>2108</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8765406148868706</v>
+        <v>-0.4987381013998871</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6034744697633485</v>
+        <v>-0.3199162915162077</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7534487860554933</v>
+        <v>-0.4420006718410221</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7113468588373451</v>
+        <v>-0.3737138664019497</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.09698414862396731</v>
+        <v>0.2001852846737933</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02015481496692928</v>
+        <v>0.4515030341357829</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.005159232283617143</v>
+        <v>0.3643020978822946</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3106053750791773</v>
+        <v>0.6728785869890075</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4980069538810383</v>
+        <v>0.7064233532092175</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2398270934977518</v>
+        <v>0.6457036574694826</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.3475268705101939</v>
+        <v>0.7092320509577306</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1951628753061314</v>
+        <v>0.1764872309269592</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1718634285860148</v>
+        <v>0.4321055104516134</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6623187916061326</v>
+        <v>0.9400151163152941</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.7651844010429656</v>
+        <v>1.061263380933063</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.9988242601712614</v>
+        <v>1.339013524516439</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>1.431542143325558</v>
+        <v>1.689199172576828</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.84503810596749</v>
+        <v>2.058114396888222</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.748883295746396</v>
+        <v>1.922981537349372</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1.91677626792729</v>
+        <v>2.166429718558305</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>1.648800791687052</v>
+        <v>1.912099783015961</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.719725867459957</v>
+        <v>1.960775158241098</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.140971617124002</v>
+        <v>2.280949141361042</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.869444647658071</v>
+        <v>2.005668942349438</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 5.666</t>
+          <t>X &gt; 5.604</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1816</v>
+        <v>1871</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.677924539822371</v>
+        <v>-1.227565525343167</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.493354408235682</v>
+        <v>-0.8880545856345776</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.756437720638097</v>
+        <v>-1.238012125525096</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.221627018485989</v>
+        <v>-1.77719452656855</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.653644283403878</v>
+        <v>-1.25445570019636</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.983458445491628</v>
+        <v>-1.576500274081198</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.905138003112171</v>
+        <v>-1.466845724312847</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.636303496005283</v>
+        <v>-1.186348392309014</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.157179552602628</v>
+        <v>-0.7923204938010713</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.461498121545056</v>
+        <v>-1.00295421360795</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.156444223212304</v>
+        <v>-0.7839389967683843</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.62334348637313</v>
+        <v>-1.379839737828291</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.399773998314565</v>
+        <v>-1.164236911159854</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.040608723516343</v>
+        <v>-0.7738333994157358</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.172755680882553</v>
+        <v>-0.8705700058883394</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.7656881833158593</v>
+        <v>-0.6285847736572947</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.3178998209601573</v>
+        <v>-0.168896432374865</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1046293016539011</v>
+        <v>0.2623887149414017</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.03161733496184382</v>
+        <v>0.1354382854525369</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.07788171996745064</v>
+        <v>0.2215812337098271</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.04650167303185526</v>
+        <v>0.0591740855841536</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.04285060344449931</v>
+        <v>0.1225300032195022</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.5926557124023262</v>
+        <v>0.71850613154961</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.3516252212935953</v>
+        <v>0.5349539343931795</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 6.287</t>
+          <t>X &gt; 6.213</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1589</v>
+        <v>1665</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.116267150768614</v>
+        <v>-1.659781539826078</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.04536239247917</v>
+        <v>-1.487278333688948</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.516446699130526</v>
+        <v>-1.905152351898515</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.51063688050489</v>
+        <v>-2.198690235106021</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.752468550744148</v>
+        <v>-1.517882565283067</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.15557107943949</v>
+        <v>-1.898904727366272</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.394028289134177</v>
+        <v>-1.916939519037122</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.110091076797929</v>
+        <v>-1.683904194364452</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.443994275895093</v>
+        <v>-1.257110969079619</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.057009889470613</v>
+        <v>-1.814071011818392</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.685389271698938</v>
+        <v>-1.482063134093913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.179346709580223</v>
+        <v>-1.937963677925637</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.827316319992278</v>
+        <v>-1.678079943613106</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.573860393558142</v>
+        <v>-1.388358236964926</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.506090161232443</v>
+        <v>-1.532556850768692</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.8749667313029903</v>
+        <v>-1.150571421309465</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5326787645526636</v>
+        <v>-0.6217603668261589</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.02772609402699544</v>
+        <v>-0.001506935801941722</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.09595752133748903</v>
+        <v>0.008910956315503427</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1282446445476708</v>
+        <v>0.07912467289496306</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1265631476100566</v>
+        <v>0.02660675630989573</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.239515172355766</v>
+        <v>0.2270365978963014</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.7657205330442451</v>
+        <v>0.6865702802860341</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.3752249695629502</v>
+        <v>0.4402895211825353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 6.907</t>
+          <t>X &gt; 6.823</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1349</v>
+        <v>1410</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.247885236599124</v>
+        <v>-1.988954411726418</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.104750837680541</v>
+        <v>-1.599268027091306</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.25652108122393</v>
+        <v>-1.724018626158028</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.636516157331187</v>
+        <v>-2.033934949260029</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.830034511626323</v>
+        <v>-1.603278400093828</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.559453643453018</v>
+        <v>-2.15255948336128</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.408194692863802</v>
+        <v>-2.100183868475362</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.465493030105826</v>
+        <v>-1.98137549832466</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.908541930665351</v>
+        <v>-1.500339244007776</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.534182201694477</v>
+        <v>-2.013904863520906</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.554673369547281</v>
+        <v>-2.165398662475894</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.866415936681534</v>
+        <v>-2.583223554800291</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.178962012598063</v>
+        <v>-2.215064824793444</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.988966424317702</v>
+        <v>-2.039570072667232</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.909102341824465</v>
+        <v>-1.874266827433637</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.124054429076587</v>
+        <v>-1.101098401834314</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.8452992507986181</v>
+        <v>-0.9931144067796609</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1670346921524342</v>
+        <v>-0.2785408848226183</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.2031481816068279</v>
+        <v>-0.2344186389110021</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1946065084921571</v>
+        <v>-0.3318558242816891</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1003023346411993</v>
+        <v>-0.2209658862130226</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.04623865724843057</v>
+        <v>-0.04176233353554437</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.543100323029222</v>
+        <v>0.4565987736110699</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3190101009401189</v>
+        <v>0.1949377864690973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 7.528</t>
+          <t>X &gt; 7.433</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1166</v>
+        <v>1216</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.845975318560164</v>
+        <v>-1.490081572117163</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.838871775029638</v>
+        <v>-1.407581182862081</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.376859385107046</v>
+        <v>-1.759155416116563</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.701939446008936</v>
+        <v>-2.105252196205569</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.620913588192671</v>
+        <v>-1.231385048948582</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.37653523414329</v>
+        <v>-2.059673117827344</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.205896085985643</v>
+        <v>-1.95163526142295</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.741176939479082</v>
+        <v>-2.338657511071311</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.528310151737472</v>
+        <v>-1.964423182667986</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.872776813206698</v>
+        <v>-2.678372871647589</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.027166185612039</v>
+        <v>-2.816646888241948</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.134535983233135</v>
+        <v>-3.011127036473503</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.495324839396694</v>
+        <v>-2.319779416650057</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.630640422532814</v>
+        <v>-2.239606253124215</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.259624200387819</v>
+        <v>-2.018640766372158</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.665237278444827</v>
+        <v>-1.29313313507302</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.799154415422301</v>
+        <v>-1.314911740558301</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.04636218613885</v>
+        <v>-0.4625741708430553</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.087760685145909</v>
+        <v>-0.4944173624164847</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.329731341730202</v>
+        <v>-0.6425765312860747</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.014644576591593</v>
+        <v>-0.4220474781972285</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.7474373647588521</v>
+        <v>-0.08602578962619845</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2156727723454068</v>
+        <v>0.4043192219679668</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1199784389477543</v>
+        <v>0.3244170697837632</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 8.148</t>
+          <t>X &gt; 8.043</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>991</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.572229555409763</v>
+        <v>-1.68352692380531</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.604281833073408</v>
+        <v>-1.831586401387852</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.831402799359694</v>
+        <v>-1.912112205823469</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.544356818802434</v>
+        <v>-2.406667046510364</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.568341035042955</v>
+        <v>-1.21451481478973</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.491364758128213</v>
+        <v>-2.036054790004947</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.456048053522096</v>
+        <v>-1.950510579145693</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.330626804026934</v>
+        <v>-2.059736306311656</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.986415101426061</v>
+        <v>-1.638265322263557</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.759330777462552</v>
+        <v>-2.434316817482895</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.687087482424744</v>
+        <v>-2.455623877242552</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.764020538748625</v>
+        <v>-2.536511115471185</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.96992730792563</v>
+        <v>-1.79230342861667</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.888281663686044</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.840067746332195</v>
+        <v>-1.646370932600206</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.043864477265082</v>
+        <v>-0.9872195556592018</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.076873440680494</v>
+        <v>-1.09109996738421</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.2735405824431538</v>
+        <v>-0.3433578494538381</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.5621900693291124</v>
+        <v>-0.6181324129147185</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.8798851271713843</v>
+        <v>-0.9906301165837235</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.8169822537650688</v>
+        <v>-0.9709904692364688</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.5901036944879863</v>
+        <v>-0.5569162005850998</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.6934527536146433</v>
+        <v>0.4694971496639226</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.5167123268293139</v>
+        <v>0.2095107972531309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 8.769</t>
+          <t>X &gt; 8.653</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>845</v>
+        <v>868</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.09646841520712</v>
+        <v>-0.8928571428571388</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9578724324918397</v>
+        <v>-0.9083492320172368</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.567489114658926</v>
+        <v>-1.01096960118992</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.280443134101667</v>
+        <v>-1.372957053454364</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.432801653986218</v>
+        <v>-0.6116488341066884</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.784297006350378</v>
+        <v>-2.298033200458839</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.964529713909364</v>
+        <v>-2.40187097306022</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.76936837759736</v>
+        <v>-2.361169296653166</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.254508414617561</v>
+        <v>-1.8876182671534</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.909080895387781</v>
+        <v>-2.338047642557072</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.345080424823493</v>
+        <v>-2.757056867584062</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.387143437738942</v>
+        <v>-3.033638822055359</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.380127989802162</v>
+        <v>-1.844383474068351</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.246177280449935</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.957575015900311</v>
+        <v>-1.507490811395726</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.8898153128922388</v>
+        <v>-0.3701499262166266</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5503596688046244</v>
+        <v>-0.128408218125962</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.05485879897183565</v>
+        <v>0.6603666628875473</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.3890933751624317</v>
+        <v>0.7596215167614346</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1025664040653638</v>
+        <v>0.398171095460981</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.03339301716442833</v>
+        <v>0.4067634604396844</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.430919836820415</v>
+        <v>0.7924304315719581</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.415453720900096</v>
+        <v>1.727309156481674</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.102935077144288</v>
+        <v>1.449962788920324</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 9.39</t>
+          <t>X &gt; 9.263</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.696402668987517</v>
+        <v>-1.929723502304149</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.614512800670667</v>
+        <v>-1.503587327255332</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.080309627479437</v>
+        <v>-1.951829816243688</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.654374758033292</v>
+        <v>-2.678640617202447</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.740165230580558</v>
+        <v>-1.744521337946942</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.525421266705408</v>
+        <v>-2.528447947002626</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.186258839484644</v>
+        <v>-2.382669744181577</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.047803617571056</v>
+        <v>-2.015547176837508</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.450760880100795</v>
+        <v>-1.349983858551248</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.223676556137285</v>
+        <v>-2.146035353770586</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.644061358419805</v>
+        <v>-2.680251952069483</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.478366317423365</v>
+        <v>-3.091242508691316</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.934861717612812</v>
+        <v>-2.324414196034553</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.600385038503845</v>
+        <v>-2.035013848865511</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.564083891639967</v>
+        <v>-2.179533822148414</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.830808080808083</v>
+        <v>-1.34941259902768</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.409169662229992</v>
+        <v>-0.9156586021505362</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.09734369938451</v>
+        <v>-0.3764996965594491</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.02034120734907</v>
+        <v>-0.1620374694136757</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.3890509529366</v>
+        <v>-0.6194940351073797</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.792708232013744</v>
+        <v>-0.9181213321870416</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.8963319712006239</v>
+        <v>-0.3212408433896385</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.2051905920519062</v>
+        <v>0.5944366526414271</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1421339563862887</v>
+        <v>0.4322976583519633</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 10.01</t>
+          <t>X &gt; 9.872</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3458638500231856</v>
+        <v>-0.07259518236926965</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.653364775569159</v>
+        <v>-0.9494168445715587</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.09138382460015</v>
+        <v>-2.046382239838536</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.472111930421626</v>
+        <v>-2.323327025397553</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.475676489347634</v>
+        <v>-1.96797033899847</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.454823260060891</v>
+        <v>-1.968765439624988</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.894546030329977</v>
+        <v>-2.290661331983891</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.009966777408636</v>
+        <v>-1.491480829020269</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.137914811440773</v>
+        <v>-1.048094506086947</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.076943444287899</v>
+        <v>-1.844146001306285</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.30122267255787</v>
+        <v>-2.20282581320037</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.746085032816495</v>
+        <v>-2.952593887545483</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.374230488376938</v>
+        <v>-2.490198938750211</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.432518667149104</v>
+        <v>-1.634332053811072</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.093984223865867</v>
+        <v>-1.212385489323886</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.8318232155441407</v>
+        <v>-1.124267590378047</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.3012885252790909</v>
+        <v>-0.5972331756046287</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.07390331547901496</v>
+        <v>-0.2569311608924139</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.308101022255947</v>
+        <v>-0.0424689337466404</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.003392038207920223</v>
+        <v>-0.4587973151860751</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5459382061739504</v>
+        <v>-1.026241816566809</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1234452971511573</v>
+        <v>-0.4704895120236756</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.4832553289521613</v>
+        <v>-0.06912632012069508</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.2413101189182498</v>
+        <v>-0.3889940210347618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 10.63</t>
+          <t>X &gt; 10.48</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5173678967100201</v>
+        <v>0.5167792124834634</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5882706115447931</v>
+        <v>0.8649317827201912</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.255427950670786</v>
+        <v>-0.7858019231317854</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.576901239890404</v>
+        <v>-2.170283329860801</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.3041724426608</v>
+        <v>-2.04980186599974</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.117206256563421</v>
+        <v>-2.090888061981858</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.077795914084597</v>
+        <v>-1.895871064313582</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.356007358837672</v>
+        <v>-2.002771705742006</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.706000907146098</v>
+        <v>-1.2807833901173</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.073237069998001</v>
+        <v>-1.482775479396047</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.596337671243788</v>
+        <v>-1.012520662811511</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.063728048322623</v>
+        <v>-0.8930630133224255</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.04434720733648589</v>
+        <v>0.3682824929891808</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.648826140220521</v>
+        <v>1.704206847397657</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.396362355824543</v>
+        <v>1.616111871453199</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.9765504948060766</v>
+        <v>1.187316880371867</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.248312871013191</v>
+        <v>1.479476072607255</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.549151680376582</v>
+        <v>1.544611769425856</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.562203304708625</v>
+        <v>1.561054194591428</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.5320105751228965</v>
+        <v>0.5875218277692227</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.01053559284313366</v>
+        <v>0.02007732638848836</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5221377155246429</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.405131697783574</v>
+        <v>1.37666810159277</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.5179404181911238</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 11.25</t>
+          <t>X &gt; 11.09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.549629077044223</v>
+        <v>2.165135828967024</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.738661802503934</v>
+        <v>1.462607988696952</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7768332296634171</v>
+        <v>0.6645348913715736</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.126596980255506</v>
+        <v>-1.069419818852168</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>0.2531955570302316</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6293406380564974</v>
+        <v>-0.04649184153790031</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.524058620832818</v>
+        <v>0.7565996622111157</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.483942414174976</v>
+        <v>0.6799897210856045</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.239715310375395</v>
+        <v>1.721160639902131</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.942990110529379</v>
+        <v>1.381730149249009</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.693240228881777</v>
+        <v>2.110586168419545</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.366871777814737</v>
+        <v>2.747246223080673</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.672281139530043</v>
+        <v>2.773906617045434</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.07024988213108</v>
+        <v>5.265398583009578</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>4.93591610836004</v>
+        <v>4.126623196558313</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>4.101731601731601</v>
+        <v>3.546374703962449</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.444004940944595</v>
+        <v>3.89911529680365</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>4.577259475218668</v>
+        <v>3.994541693925157</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.555055618047739</v>
+        <v>4.209003921070931</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>3.313329999444349</v>
+        <v>3.053727352431281</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.532688593383078</v>
+        <v>2.257972348767446</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.171128346259692</v>
+        <v>3.096051835944579</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.92179353493222</v>
+        <v>3.796307325789165</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.369770805518471</v>
+        <v>3.177547326933492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 11.87</t>
+          <t>X &gt; 11.7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.780839633555985</v>
+        <v>2.526737433739115</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.650882112314612</v>
+        <v>3.436899962197089</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.020091978946269</v>
+        <v>3.33827522446736</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.49990904384088</v>
+        <v>1.300786320456822</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7665282098478201</v>
+        <v>2.470314885559802</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5525297004403456</v>
+        <v>1.182161786355572</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.420863926499365</v>
+        <v>1.254131797244249</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5057439058559794</v>
+        <v>2.105280717997481</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.752050364879125</v>
+        <v>3.389278991843433</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9791346888426347</v>
+        <v>2.882244837664551</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.855603969558771</v>
+        <v>3.732514534349818</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.78167384321921</v>
+        <v>4.612001944040372</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.863331053471533</v>
+        <v>4.942196531791915</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.955505189073136</v>
+        <v>7.873153221803882</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>4.694952252938343</v>
+        <v>6.612964157837915</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>4.084519897772914</v>
+        <v>5.729181471455263</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>5.155422037903861</v>
+        <v>6.781370423892092</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>5.050581334082679</v>
+        <v>6.359468977690028</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.965267895729916</v>
+        <v>6.573931204835802</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>4.549704067143708</v>
+        <v>5.921465626773411</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.705953079900581</v>
+        <v>4.775986443311737</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>4.232516757045694</v>
+        <v>5.567875944477855</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>5.109401108081954</v>
+        <v>6.100527770796681</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>4.129954397027355</v>
+        <v>5.071336753385829</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 12.49</t>
+          <t>X &gt; 12.31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.956167811941164</v>
+        <v>1.194215377152567</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.487062655382395</v>
+        <v>2.000940120396052</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.407252561575291</v>
+        <v>4.255017948329034</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.336089586908663</v>
+        <v>1.206475398643619</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.119702099436019</v>
+        <v>1.632671644509202</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.560399628816974</v>
+        <v>0.386096478577457</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.654122586717669</v>
+        <v>1.345400431257026</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.241582783755639</v>
+        <v>2.443988759778222</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.402472950744979</v>
+        <v>3.6245492484097</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.763885632917443</v>
+        <v>1.775866174242992</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.037945275079366</v>
+        <v>3.100732767794696</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.50546452834778</v>
+        <v>3.525905199288317</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.382302461491662</v>
+        <v>2.761890274820004</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.40002955519433</v>
+        <v>5.320673757246546</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.622483272539149</v>
+        <v>3.585887796414113</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.7243328810493</v>
+        <v>2.392805850321501</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>3.082953057504668</v>
+        <v>4.043311403508767</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>2.978112353683485</v>
+        <v>3.910427298347166</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.820869406249592</v>
+        <v>3.77401233251048</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.888312231142997</v>
+        <v>2.935967198622102</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.345766063176967</v>
+        <v>2.368522697241367</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.016188758484283</v>
+        <v>3.345991754233445</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.036932127682761</v>
+        <v>3.940503432494282</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.214831217743061</v>
+        <v>3.076610052239914</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 13.11</t>
+          <t>X &gt; 12.92</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.248041775456919</v>
+        <v>3.904181782527708</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.357709421551554</v>
+        <v>4.083806861717441</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.03080148363167</v>
+        <v>5.807836164081188</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.095625241966708</v>
+        <v>2.662242475911256</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4.426501436086106</v>
+        <v>4.93987582517363</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>3.82021368649086</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.174852271626463</v>
+        <v>5.578323163619842</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.674418604651166</v>
+        <v>6.549998464892077</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.049239119899198</v>
+        <v>7.95452311925704</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.498545666084937</v>
+        <v>5.881875879356848</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.883716419357974</v>
+        <v>4.877515149280327</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.493855904798863</v>
+        <v>5.451997024596267</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.815138282387188</v>
+        <v>4.762636822039113</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.816281628162827</v>
+        <v>6.64206233507408</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.047027219471147</v>
+        <v>3.40671646382733</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.752525252525253</v>
+        <v>3.116956652859756</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.507497004436665</v>
+        <v>3.864140070921984</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.958211856171047</v>
+        <v>3.305724050866765</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.174103237095373</v>
+        <v>3.520186278012538</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.472060158174507</v>
+        <v>2.883708893284286</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.929513990208477</v>
+        <v>2.316264391903552</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.742556917688269</v>
+        <v>3.092165699735503</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.905920519059208</v>
+        <v>3.761332099907499</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.385643821391483</v>
+        <v>3.599193105618035</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 13.73</t>
+          <t>X &gt; 13.53</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.63553479611577</v>
+        <v>1.646052517172429</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.803270560580025</v>
+        <v>2.343541907883647</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.887864576875664</v>
+        <v>4.390734598444894</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.159835180548512</v>
+        <v>0.9681437203913887</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.83912008488565</v>
+        <v>3.051076146329791</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.518548582540824</v>
+        <v>2.736311639120323</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.761675275534898</v>
+        <v>4.299720192925349</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.996026644852165</v>
+        <v>5.881592202346916</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.540026389580945</v>
+        <v>7.424615451653658</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.259573025102242</v>
+        <v>5.685167730019231</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.523582416007883</v>
+        <v>4.542308405000924</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.757395826630237</v>
+        <v>6.15251890335982</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.141771448216339</v>
+        <v>5.509324899116585</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.930742823026023</v>
+        <v>7.61958140372122</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.760036711375115</v>
+        <v>4.107238342590882</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.344373382061832</v>
+        <v>3.725146134995448</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.717993933526557</v>
+        <v>4.564661949685537</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.110640666891307</v>
+        <v>3.960079731316384</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.326532047815633</v>
+        <v>4.174541958462157</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.508352732155529</v>
+        <v>3.445732177106045</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.463294001375424</v>
+        <v>2.406589562517766</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.39247316559446</v>
+        <v>3.274823266977577</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.169460440890582</v>
+        <v>4.461853978671051</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.088603062039176</v>
+        <v>3.828016871174036</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 14.35</t>
+          <t>X &gt; 14.14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.531992392740875</v>
+        <v>1.42813350580753</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.8892041586953567</v>
+        <v>1.18222667010366</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.228332347829209</v>
+        <v>5.190690462948922</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.898094377769183</v>
+        <v>3.428697620865847</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.648723658308327</v>
+        <v>6.661911410591074</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.983837992553845</v>
+        <v>5.06445905167687</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.767444864219051</v>
+        <v>8.362944290906142</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>10.39720513404724</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.765288502615263</v>
+        <v>10.52513404373135</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.757804925344189</v>
+        <v>7.389901261962294</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.562728765036979</v>
+        <v>4.738159668379495</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.9876830652927</v>
+        <v>8.555144965370189</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>8.609843491194276</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.96442977631096</v>
+        <v>11.28558603794828</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.579685746352425</v>
+        <v>6.486373101783485</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.445768609374952</v>
+        <v>6.967288011695906</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>5.723643954936477</v>
+        <v>6.249608584896876</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>5.939535335860803</v>
+        <v>6.46407081204265</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>4.89181324459426</v>
+        <v>5.509066613826775</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>4.34926707662823</v>
+        <v>4.941622112446041</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>6.125272967070991</v>
+        <v>6.620845555403044</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.165179778318461</v>
+        <v>5.694889397406563</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.472063574477907</v>
+        <v>4.94795508147967</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 14.98</t>
+          <t>X &gt; 14.75</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.834395500528743</v>
+        <v>1.702128516644642</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.007881976297909</v>
+        <v>-2.040281815562722</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5749332833934204</v>
+        <v>2.998730376251991</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4814356899329368</v>
+        <v>2.406328177443768</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.602128676229476</v>
+        <v>4.927972834547241</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.9826432494236315</v>
+        <v>3.686305041943918</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>6.662307468759082</v>
+        <v>7.786327924816092</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.803450862715678</v>
+        <v>9.57930957930958</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.038486431727151</v>
+        <v>9.007937789692981</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.459119142787443</v>
+        <v>7.512585595172936</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.313823946239687</v>
+        <v>4.288317113273784</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.067332607307819</v>
+        <v>8.207539354606681</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.363525379161381</v>
+        <v>8.491248635757309</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.56180134142447</v>
+        <v>11.73951807082769</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.871399979327784</v>
+        <v>8.260160891739851</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.465786901270775</v>
+        <v>7.422863511958113</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.106063312680398</v>
+        <v>6.619682400932398</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.80767422176244</v>
+        <v>6.486798295770797</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.023565602686766</v>
+        <v>6.70126052291657</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.210411412654793</v>
+        <v>5.517245569374154</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.47431685759198</v>
+        <v>5.649101767294113</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.62427734779579</v>
+        <v>6.972540643940242</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>8.898752060277843</v>
+        <v>5.817573730617205</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>8.822919807054568</v>
+        <v>4.956134037027049</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 15.6</t>
+          <t>X &gt; 15.36</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.19039666298152</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-8.02967796583583</v>
+        <v>-7.95520023048114</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.359588906758717</v>
+        <v>-0.8765609990393841</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2707411243996631</v>
+        <v>-0.6356298645142644</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.798873808458467</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.184038192754052</v>
+        <v>1.745745601384471</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.015693112467304</v>
+        <v>5.950663589151759</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.440184370416944</v>
+        <v>8.14574314574314</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>8.273672055427248</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>7.47762056020791</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.181013716655265</v>
+        <v>5.249855574812244</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.40676881771178</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.98630945355836</v>
+        <v>10.52504816955685</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>16.26973508161628</v>
+        <v>12.77681410812374</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>11.10708727953121</v>
+        <v>7.92799305957201</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>11.7014742014742</v>
+        <v>8.489297078391672</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.963953460893123</v>
+        <v>5.052083333333336</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>8.760013657972848</v>
+        <v>5.752532561505063</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>8.975905038897174</v>
+        <v>5.966994788650837</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.261849947964294</v>
+        <v>6.181581233709821</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.620204680899171</v>
+        <v>6.447470065662415</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>12.14796232309367</v>
+        <v>9.705640877040473</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>12.42243703557573</v>
+        <v>9.949275362318851</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>13.24750568325334</v>
+        <v>10.62046970136272</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 16.22</t>
+          <t>X &gt; 15.97</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.661255276697275</v>
+        <v>-4.504165189649065</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-8.057256564843001</v>
+        <v>-7.634687409968315</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3116021444862511</v>
+        <v>-0.2355353580137347</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.004148000663683149</v>
+        <v>0.1336009047165021</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.782510506380888</v>
+        <v>5.627273533847934</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.949068529212958</v>
+        <v>3.861130216769091</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.279160661649136</v>
+        <v>6.912202050690219</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.06217370669198</v>
+        <v>10.45343545343545</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>13.124069051872</v>
+        <v>11.54290282465802</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.35115337583551</v>
+        <v>10.74685132943868</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.563988528201499</v>
+        <v>8.134470959427631</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.38727994108004</v>
+        <v>12.66558131264864</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>16.32534236401984</v>
+        <v>14.43530457981324</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>20.18589614063447</v>
+        <v>18.99476282607245</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>14.42571202672739</v>
+        <v>13.50491613649508</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>16.04050711193568</v>
+        <v>14.06622015531474</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>12.84536548516229</v>
+        <v>10.11618589743589</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>12.74052478134111</v>
+        <v>10.94484025381276</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>13.97682432553075</v>
+        <v>11.15930248095853</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>14.16367013549878</v>
+        <v>10.41235046447905</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>12.60071580426743</v>
+        <v>10.80644442463678</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>15.58609433265425</v>
+        <v>14.57743574883535</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>15.8605690451363</v>
+        <v>14.82107023411373</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>16.80514495517833</v>
+        <v>15.62046970136272</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 16.84</t>
+          <t>X &gt; 16.58</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.833618197769319</v>
+        <v>-4.653737839221712</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-6.987672104552864</v>
+        <v>-9.344089119370025</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.212863063283621</v>
+        <v>-1.709894332372713</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.49990904384088</v>
+        <v>-1.191185420069829</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.393034233944192</v>
+        <v>6.311034217608615</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.170361865824709</v>
+        <v>5.356856712495592</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9.217690290368104</v>
+        <v>9.006219144707316</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>12.55393667694032</v>
+        <v>12.03463203463203</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13.80024313596346</v>
+        <v>13.27367205542725</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>14.23214673703541</v>
+        <v>14.69984278243012</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>10.89174854787202</v>
+        <v>10.52763335259003</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>15.43227625285776</v>
+        <v>15.80660695367428</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>17.92357201732695</v>
+        <v>18.02504816955685</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>21.31695097220566</v>
+        <v>22.22125855256818</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>14.63471128908292</v>
+        <v>15.98354861512757</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>15.22909821102591</v>
+        <v>17.65596374505834</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>12.68554251983159</v>
+        <v>15.32986111111111</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>13.78552109311883</v>
+        <v>16.30808811706062</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>17.61587030536847</v>
+        <v>18.74477256642862</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>19.00753539244492</v>
+        <v>18.95935901148761</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>18.46498922447889</v>
+        <v>17.28080339899576</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>22.00360109439509</v>
+        <v>20.5389742103738</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>21.07325652976871</v>
+        <v>19.67149758454106</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>20.99742427654544</v>
+        <v>19.5093585902516</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 17.46</t>
+          <t>X &gt; 17.19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.991496464081322</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-7.222377158535032</v>
+        <v>-6.352636127917037</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8681884153582331</v>
+        <v>0.08497746249908289</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.016260162601625</v>
+        <v>0.7746265457421373</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.576573586158247</v>
+        <v>5.627273533847934</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.166137174853034</v>
+        <v>3.220104575743456</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.588993685767875</v>
+        <v>7.553227691715861</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.2068861371187</v>
+        <v>11.0944610944611</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.54707461773471</v>
+        <v>12.50444128619647</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.07286024039951</v>
+        <v>12.99044107302842</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.749517285158838</v>
+        <v>10.6985735235302</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.66557307651604</v>
+        <v>15.55019669726401</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.43851490576382</v>
+        <v>18.28145842596711</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>21.11353992542112</v>
+        <v>21.87937821068784</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>13.96189013433406</v>
+        <v>14.78696741854638</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>14.55627705627705</v>
+        <v>15.34827143736604</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.52625602319569</v>
+        <v>11.39823717948718</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>11.72011661807581</v>
+        <v>12.54740435637686</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>15.83211189510403</v>
+        <v>16.60802042967647</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>17.31765900377336</v>
+        <v>18.10465815678675</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>16.77511283580733</v>
+        <v>17.53721365540602</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>20.59537077050212</v>
+        <v>21.30820497960458</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>19.57114418428287</v>
+        <v>20.26978818283167</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>19.4953119310596</v>
+        <v>20.1076491885422</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 18.08</t>
+          <t>X &gt; 17.8</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-2.893276078759953</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-7.922992332834411</v>
+        <v>-7.035286810567719</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.466274539760143</v>
+        <v>-0.4977731202515088</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4523503881655344</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>4.063928336670898</v>
+        <v>5.127773034347427</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.61931557539986</v>
+        <v>2.68730404294292</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.110524786246344</v>
+        <v>7.087027225515392</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.779681762545906</v>
+        <v>10.67821067821068</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.13695841814481</v>
+        <v>12.10484088659609</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.67983221579253</v>
+        <v>12.60749069007804</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>9.322312910586042</v>
+        <v>10.28232310727978</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.30672140187488</v>
+        <v>15.20054634761368</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>17.13092775607141</v>
+        <v>17.9817581262668</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>20.85721730067745</v>
+        <v>21.62962796093759</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>13.62012663467582</v>
+        <v>14.45396708554603</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>14.21451355661881</v>
+        <v>15.0152711043657</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>10.13322799858871</v>
+        <v>11.01528679653679</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>11.34417676845175</v>
+        <v>12.18110399007649</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>15.5074365704287</v>
+        <v>16.29167011332616</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>17.01007185408095</v>
+        <v>17.80495785708645</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>16.46752568611492</v>
+        <v>17.23751335570572</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>20.33904814575845</v>
+        <v>21.05845472985433</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>19.29773338455628</v>
+        <v>20.0033879164314</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>19.22190113133301</v>
+        <v>19.84124892214194</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 18.7</t>
+          <t>X &gt; 18.41</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.528171057093942</v>
+        <v>-2.857695221261281</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.088299968119813</v>
+        <v>-7.213191098061046</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4840654960240371</v>
+        <v>-1.618570131459471</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.619881892983926</v>
+        <v>0.5287536971295665</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.10099282888735</v>
+        <v>4.362784598126119</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.879508310759377</v>
+        <v>1.779992176726942</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.332911739545089</v>
+        <v>6.464362219288745</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.871601703242717</v>
+        <v>10.26903081697601</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.32153958938277</v>
+        <v>10.39695972666012</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.36552532179698</v>
+        <v>12.34063425883805</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.414232851282854</v>
+        <v>9.873143246045117</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.36083556051091</v>
+        <v>13.70615033266971</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.46302560633085</v>
+        <v>16.70084725631484</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>19.46729884256031</v>
+        <v>20.56220223597762</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>11.766902023853</v>
+        <v>13.0307327855994</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>12.36128894579599</v>
+        <v>13.59203680441907</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.002019696142455</v>
+        <v>9.378567351598171</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.305629696546632</v>
+        <v>10.6155462601352</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13.74687319014702</v>
+        <v>14.93959752837686</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>15.34216970434039</v>
+        <v>16.52404698713448</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>14.79962353637436</v>
+        <v>15.95660248575375</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>18.94912968764131</v>
+        <v>19.99102900489435</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.81515369589802</v>
+        <v>18.86480047647409</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>17.73932144267474</v>
+        <v>18.70266148218463</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 19.32</t>
+          <t>X &gt; 19.02</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>70</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.212275684860543</v>
+        <v>-2.114055299539174</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.832766768924643</v>
+        <v>-6.645676420957329</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.127928675098488</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.016260162601625</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.296007304723169</v>
+        <v>2.817174172813054</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.809772906547096</v>
+        <v>6.307806446294613</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.388704318936874</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.858762929423008</v>
+        <v>10.41652919828439</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.94299011052938</v>
+        <v>12.47762056020791</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.931335466977011</v>
+        <v>8.464141289097952</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.93830034924331</v>
+        <v>12.47327362034095</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.10085256810148</v>
+        <v>15.64409578860447</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.16548797736917</v>
+        <v>19.68157601288564</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>12.79305896550289</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.38744588744588</v>
+        <v>13.84643993553452</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.967814464754127</v>
+        <v>9.456845238095234</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10.29154518950438</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.79315085614299</v>
+        <v>15.25270907436513</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.40856809468244</v>
+        <v>16.89586694799553</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.86602192671641</v>
+        <v>16.32842244661479</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>20.0758902510216</v>
+        <v>20.5389742103738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>18.92179353493222</v>
+        <v>19.35403726708075</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>18.84596128170895</v>
+        <v>19.19189827279128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 19.94</t>
+          <t>X &gt; 19.63</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.916209432272545</v>
+        <v>-2.114055299539174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-7.598812317578883</v>
+        <v>-6.645676420957329</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-1.790454555015664</v>
+        <v>-0.7575133799917637</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.395142150179268</v>
+        <v>1.507227278342867</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.957902402269674</v>
+        <v>4.088811995386394</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.695593226048217</v>
+        <v>2.817174172813054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.271470629114383</v>
+        <v>6.307806446294613</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>7.891809908998994</v>
+        <v>8.860028860028848</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>10.41652919828439</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>11.50820750183372</v>
+        <v>12.47762056020791</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>7.43444105703913</v>
+        <v>8.464141289097952</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.50351774054765</v>
+        <v>12.47327362034095</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>14.72818176064805</v>
+        <v>15.64409578860447</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.85492897115799</v>
+        <v>19.68157601288564</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.39968422430207</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>14.44334650856389</v>
+        <v>13.84643993553452</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>9.961603284629902</v>
+        <v>9.456845238095234</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>11.30603794312756</v>
+        <v>10.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>15.86975541100842</v>
+        <v>15.25270907436513</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>17.50587658329528</v>
+        <v>16.89586694799553</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>16.96333041532925</v>
+        <v>16.32842244661479</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>21.23531054087668</v>
+        <v>20.5389742103738</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>20.06050989103989</v>
+        <v>19.35403726708075</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>19.98467763781661</v>
+        <v>19.19189827279128</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5742,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 1.942</t>
+          <t>X &lt; 1.945</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.264035519229068</v>
+        <v>-6.399769585253459</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-0.9313907066716069</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.239729917334515</v>
+        <v>-2.186084808563187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.401959299096092</v>
+        <v>-4.207058435942848</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-8.449334310183666</v>
+        <v>-7.182825827186953</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.1198337187117</v>
+        <v>-10.83505069656253</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.050219076508249</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.80583334386891</v>
+        <v>-12.44061365885847</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.12947365758657</v>
+        <v>-11.80809372550637</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.4061386531058</v>
+        <v>-10.10728728233062</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-16.03271414351032</v>
+        <v>-14.6695835225162</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-22.9529776596418</v>
+        <v>-21.49876135425268</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-27.52188262304491</v>
+        <v>-26.03270970140008</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-25.28147519598779</v>
+        <v>-23.85772122614227</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-26.13636363636364</v>
+        <v>-24.72498863589404</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-26.27028077334111</v>
+        <v>-24.82886904761905</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-29.27367220179997</v>
+        <v>-27.81889600992351</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-30.50705618319449</v>
+        <v>-29.03300521134916</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-31.7694857355453</v>
+        <v>-30.24699019486161</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-32.31203190351133</v>
+        <v>-30.81443469624234</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-33.83715322723927</v>
+        <v>-32.31816864676905</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-33.56267851475722</v>
+        <v>-32.07453416149067</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-32.18923540566165</v>
+        <v>-30.80810172720872</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 2.563</t>
+          <t>X &lt; 2.554</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.326231075868442</v>
+        <v>1.629787064992847</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.637544812498057</v>
+        <v>3.539052643082087</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.903229467170767</v>
+        <v>6.163668886018087</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.190275447728027</v>
+        <v>6.00230116996849</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.266007608925605</v>
+        <v>5.295708547110529</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.629928527533274</v>
+        <v>4.159538704832755</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.327115646112063</v>
+        <v>5.51962910639314</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.048904201358987</v>
+        <v>5.214708662984521</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.26734611578398</v>
+        <v>4.480568607151383</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.494430439747489</v>
+        <v>3.684517111932045</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.945444814419695</v>
+        <v>3.094683161019141</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.020604875992284</v>
+        <v>0.6629287927547409</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.7486477258432629</v>
+        <v>-1.745066772971889</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.084952939738415</v>
+        <v>-5.441576696473973</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.331573603574121</v>
+        <v>-5.692696595600395</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.383277216610544</v>
+        <v>-6.424496025056605</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-7.751762254822594</v>
+        <v>-7.390445402298852</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.091170859878339</v>
+        <v>-8.816432955736317</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-10.52137001393344</v>
+        <v>-10.32610865962503</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.923001570220556</v>
+        <v>-10.11152221456604</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-10.87707037193145</v>
+        <v>-11.1100011987054</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-10.12987106585083</v>
+        <v>-11.6161982034193</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.032351085879064</v>
+        <v>-10.51049475262369</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-8.69666070535748</v>
+        <v>-10.67263374691315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 3.184</t>
+          <t>X &lt; 3.164</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>524</v>
+        <v>493</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.511824642293227</v>
+        <v>0.412748525439099</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.703765401195319</v>
+        <v>2.195239255658151</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.555822688042184</v>
+        <v>2.766102963097197</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.461189279286472</v>
+        <v>2.173700764288974</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.697917890708666</v>
+        <v>2.303822137374226</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.312364992836578</v>
+        <v>1.243717203818548</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.257973560854623</v>
+        <v>1.665673731139591</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.315639978696971</v>
+        <v>2.78063158387701</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.830409603359769</v>
+        <v>1.691521954007371</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.103295454040833</v>
+        <v>-0.3215680807657151</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5310418503621364</v>
+        <v>-1.672051118899724</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.336508811062032</v>
+        <v>-3.571351126109356</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.032189961887617</v>
+        <v>-4.889083000152425</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.161665784899093</v>
+        <v>-6.96287487091616</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-7.201488471792636</v>
+        <v>-7.847869009393506</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-7.370460328475602</v>
+        <v>-7.692244503758431</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-8.458575938735514</v>
+        <v>-8.810323698444897</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-10.0901341998086</v>
+        <v>-10.36308609975254</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.301723734914809</v>
+        <v>-9.337264846237602</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.114877924946782</v>
+        <v>-9.731197670955488</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-9.084905008943345</v>
+        <v>-9.487283145967055</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-9.542430359665431</v>
+        <v>-10.37380469429151</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-9.267955647183378</v>
+        <v>-9.72449069582855</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-8.580429121780696</v>
+        <v>-9.278110420341136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 3.804</t>
+          <t>X &lt; 3.774</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>784</v>
+        <v>742</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.333642682486399</v>
+        <v>0.5513330034330295</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9988658841365847</v>
+        <v>0.7081107314875439</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.60166316163621</v>
+        <v>0.6614703208711319</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.654015264642439</v>
+        <v>1.142893625418615</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.9355717308706915</v>
+        <v>0.5988791094803574</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7398848557435755</v>
+        <v>-0.4522409757967267</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.753650457567502</v>
+        <v>0.5743195031302548</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.730541053630752</v>
+        <v>0.7500500098077438</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2414159906475035</v>
+        <v>-0.2573252491549596</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1062554166518268</v>
+        <v>-0.5142931864228188</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>-1.454996177209324</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-1.731578131680621</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.424657635980161</v>
+        <v>-2.981241138619261</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.431450798141036</v>
+        <v>-4.846725873906813</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.324287973272611</v>
+        <v>-4.585484029376772</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-4.622758194186765</v>
+        <v>-4.698034457996471</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.649532474021377</v>
+        <v>-5.880081985624443</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.009475218658885</v>
+        <v>-6.282507869761787</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-5.921134858142729</v>
+        <v>-6.202816532103881</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.606738027766532</v>
+        <v>-5.449146529093419</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-5.639080114099919</v>
+        <v>-5.342736583034792</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-6.225130157141663</v>
+        <v>-6.226524441917306</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-6.843512587516763</v>
+        <v>-6.79151529356615</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-6.281589738699211</v>
+        <v>-6.414570729904135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 4.425</t>
+          <t>X &lt; 4.384</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3274068548220015</v>
+        <v>-0.1577137687295505</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2874819883457391</v>
+        <v>-0.8871795986307163</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.515395321166686</v>
+        <v>0.2759212704641669</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2692947097538223</v>
+        <v>0.2637898646926971</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02687491881252413</v>
+        <v>-0.2051918730855604</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0662709399080228</v>
+        <v>-0.435105462445307</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1888578738673559</v>
+        <v>-0.208581328563632</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.556206978915597</v>
+        <v>-0.8465049162723659</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9815732050307702</v>
+        <v>-1.149218342244914</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.727411383401531</v>
+        <v>-1.072330943186849</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.573799920511313</v>
+        <v>-1.77002803333518</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.105583871111506</v>
+        <v>-1.270664304004356</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.761892529937747</v>
+        <v>-1.997583579554053</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.103419585656042</v>
+        <v>-3.312742956215097</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.294709475206723</v>
+        <v>-3.412938075248547</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.54065868771751</v>
+        <v>-3.627579740231027</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.421541277542786</v>
+        <v>-4.507405835758171</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.806494026181895</v>
+        <v>-5.028262782820832</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.683973326863544</v>
+        <v>-4.813800555675058</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-4.683868880107475</v>
+        <v>-4.793200531566612</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-4.479449595225695</v>
+        <v>-4.390712928194674</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-5.022148964664673</v>
+        <v>-5.144827923476825</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.307898341818479</v>
+        <v>-5.192173069624253</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-4.86565420560747</v>
+        <v>-5.063332432487911</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 5.045</t>
+          <t>X &lt; 4.994</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1368</v>
+        <v>1329</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.202561480887042</v>
+        <v>0.6706469482503294</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6492850467032909</v>
+        <v>0.5398246451407474</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8135966604545288</v>
+        <v>0.6699911543088817</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6833083365689561</v>
+        <v>0.567658625769738</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2351478315354854</v>
+        <v>-0.4138058056607221</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4123477051613449</v>
+        <v>-0.9638352369388699</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.3831310576605773</v>
+        <v>-0.9688120662789501</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.8387009288765341</v>
+        <v>-1.456955504931528</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.120709822478624</v>
+        <v>-1.437505739021361</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.7265941345472058</v>
+        <v>-1.408350932665314</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8901712538732554</v>
+        <v>-1.436190936815663</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.07482875360133079</v>
+        <v>-0.5124728162682004</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6144751384735017</v>
+        <v>-0.8338106893020125</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.346130236656052</v>
+        <v>-1.564533249752557</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.49369731250065</v>
+        <v>-1.677270098322722</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.847523373781577</v>
+        <v>-2.050582530336698</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.49201673249501</v>
+        <v>-2.605930210684726</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.107433658052145</v>
+        <v>-3.190281584469354</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.96448173737582</v>
+        <v>-2.900574812553081</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.215272688895752</v>
+        <v>-3.287944725658129</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.809605873637871</v>
+        <v>-2.801965600251798</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-2.916810478905404</v>
+        <v>-3.027617211748087</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.550292450667278</v>
+        <v>-3.461183629404253</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.146519921298577</v>
+        <v>-3.171855355070697</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 5.666</t>
+          <t>X &lt; 5.604</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1596</v>
+        <v>1566</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.824487052714197</v>
+        <v>1.359334056203132</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.489710254364383</v>
+        <v>1.084884157704522</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.738137176601349</v>
+        <v>1.448222619284451</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.211941433236056</v>
+        <v>2.095675585422363</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.563846151194717</v>
+        <v>1.412844969387663</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.938195222988533</v>
+        <v>1.669603469404777</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.853317119985121</v>
+        <v>1.418917557405727</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.549418604651166</v>
+        <v>1.087293336340345</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.002334804702201</v>
+        <v>0.6799021889301073</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.355122693393668</v>
+        <v>0.8745671250934066</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.003791466262278</v>
+        <v>0.6747441807956918</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.538050192895589</v>
+        <v>1.45416534008617</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.290435343050099</v>
+        <v>1.269152694732114</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8817392058155278</v>
+        <v>0.8678005026815541</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.036604038316263</v>
+        <v>1.053391910880244</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.5678264824606316</v>
+        <v>0.8232689813290932</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.05867482390716816</v>
+        <v>0.2723898467432946</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.421400401489997</v>
+        <v>-0.2436360208704187</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.2680481074949981</v>
+        <v>-0.02917379372464524</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.3938977321736346</v>
+        <v>-0.133872150709081</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.2485139439170183</v>
+        <v>0.1288238332230804</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.3496416638720206</v>
+        <v>-0.07405260954956816</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.9771240784500037</v>
+        <v>-0.7244155699927717</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.7029108987421822</v>
+        <v>-0.631126722647501</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 6.287</t>
+          <t>X &lt; 6.213</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1823</v>
+        <v>1772</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.774907809981599</v>
+        <v>1.465767228240836</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.604244797189779</v>
+        <v>1.418633289489001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.971477389296638</v>
+        <v>1.763495023369579</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.914978512085845</v>
+        <v>2.043742332795148</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.250960468422591</v>
+        <v>1.351851815913598</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.602040440077964</v>
+        <v>1.597036286008503</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.814774469535529</v>
+        <v>1.507934785109086</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.568780947289369</v>
+        <v>1.291810561473483</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.9853471885373892</v>
+        <v>0.9465219711102151</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.52677981480101</v>
+        <v>1.420252731186537</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.198429818408719</v>
+        <v>1.162911286686182</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.631619078706613</v>
+        <v>1.65120154826888</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.329924700788069</v>
+        <v>1.471057559228207</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.108845824341479</v>
+        <v>1.256708884523583</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.053112165315135</v>
+        <v>1.454501801816789</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.4974443227455225</v>
+        <v>1.147310622409734</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1992336479805417</v>
+        <v>0.6483963506395796</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2889586440115011</v>
+        <v>0.06404497685495159</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1825962882788588</v>
+        <v>0.109206978267089</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.3791020664816926</v>
+        <v>0.0416263804366821</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.3740031084893403</v>
+        <v>0.1513827819904847</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.4720549544578532</v>
+        <v>-0.1495133742763102</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.9325297733384517</v>
+        <v>-0.5266463833545885</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.5921705261431001</v>
+        <v>-0.4066183347546612</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 6.907</t>
+          <t>X &lt; 6.823</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2063</v>
+        <v>2027</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.405024446201061</v>
+        <v>1.30081749889527</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.215105204587125</v>
+        <v>1.130702853219312</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.273947575160193</v>
+        <v>1.176165086497676</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.478424748377996</v>
+        <v>1.395237357435747</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.9494908668495583</v>
+        <v>1.049596309111884</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.426172166418688</v>
+        <v>1.332552859844505</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.330225413962431</v>
+        <v>1.20336231339121</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.370070778564212</v>
+        <v>1.123160916975351</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.00493430275727</v>
+        <v>0.8375227430500374</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.420746396796304</v>
+        <v>1.150839233426588</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.433305195361839</v>
+        <v>1.304427846198671</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.638348728536961</v>
+        <v>1.646908642475722</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.192496772953227</v>
+        <v>1.446964180055531</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.068176483831266</v>
+        <v>1.376026318857356</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.020136824720154</v>
+        <v>1.314692566961178</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.5012614039719594</v>
+        <v>0.8217268467504724</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.3189415564426952</v>
+        <v>0.7473496055226718</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1247181212410311</v>
+        <v>0.2493258520822721</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1024375825238621</v>
+        <v>0.2664521147485175</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.1092026147630065</v>
+        <v>0.3330365864478537</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1677216772111194</v>
+        <v>0.3082659873858233</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2630927998258556</v>
+        <v>0.08510149207089057</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5895575171164964</v>
+        <v>-0.2139379249694287</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4428691316973286</v>
+        <v>-0.1294069636594841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 7.528</t>
+          <t>X &lt; 7.433</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2246</v>
+        <v>2221</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8845392000338208</v>
+        <v>0.73926444048886</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7946941094196305</v>
+        <v>0.7853173955786659</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.035120290070623</v>
+        <v>0.9389151914368128</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.161388885468867</v>
+        <v>1.130783712975678</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6047503563844856</v>
+        <v>0.6124938541888909</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.9936905317921685</v>
+        <v>0.9735059947684732</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9101897311018519</v>
+        <v>0.8299122474701832</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.188350493196054</v>
+        <v>1.042834868338211</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.078737644972954</v>
+        <v>0.8833408110225918</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.261272536381519</v>
+        <v>1.232658625590801</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.340167556057111</v>
+        <v>1.352006112446659</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.397759808702766</v>
+        <v>1.505097914379498</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.07211657215236</v>
+        <v>1.179009305580763</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.143704796011527</v>
+        <v>1.181928509200446</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.9558717624620385</v>
+        <v>1.110219271421201</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6456535183243233</v>
+        <v>0.7557990990472589</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.7159597947902796</v>
+        <v>0.7686152291105017</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3270691681899862</v>
+        <v>0.3030943592578765</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.3475076499489234</v>
+        <v>0.3644768030393308</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.4720601581745001</v>
+        <v>0.4441711617673718</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.3118073551607949</v>
+        <v>0.3713309769334003</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.1737550197048705</v>
+        <v>0.09812850637020176</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1035736212760554</v>
+        <v>-0.1264822134387273</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1528938257837424</v>
+        <v>-0.17196613834912</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 8.148</t>
+          <t>X &lt; 8.043</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2421</v>
+        <v>2415</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5735555052259755</v>
+        <v>0.6411304499041677</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.506570111959519</v>
+        <v>0.7867639331079772</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5650630178932019</v>
+        <v>0.7860005773152992</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8172784806211766</v>
+        <v>0.9968136673132406</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4228584488365641</v>
+        <v>0.4569303191333134</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7971494590018509</v>
+        <v>0.719235120496684</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7869204513730637</v>
+        <v>0.6052688523096563</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.7376110543844447</v>
+        <v>0.6529418294124127</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5976791855806525</v>
+        <v>0.5164704093367121</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9162960653548424</v>
+        <v>0.8143846606607781</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8859075998564592</v>
+        <v>0.86352938041356</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.9189826344878611</v>
+        <v>0.9405171308477449</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6013224929135035</v>
+        <v>0.6741275869792105</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.569378204788805</v>
+        <v>0.6977763074364489</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5532000589773247</v>
+        <v>0.7002702872947779</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2256509100889517</v>
+        <v>0.4610263396380603</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2398784798165039</v>
+        <v>0.5055653041563417</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.08752361972512546</v>
+        <v>0.1907812190845846</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.02928323159935076</v>
+        <v>0.3471600779070414</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1581999061699193</v>
+        <v>0.5036151320149003</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.135234562265687</v>
+        <v>0.5396950449841782</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.04287332984949188</v>
+        <v>0.2824578678003675</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.4836565063559632</v>
+        <v>-0.1114310394471616</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4111343694387486</v>
+        <v>-0.08346404604930058</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 8.769</t>
+          <t>X &lt; 8.653</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.297376824791975</v>
+        <v>0.2382374694202696</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.176558397990334</v>
+        <v>0.3218485280419543</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.343698615694187</v>
+        <v>0.323567701089317</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5413581801619571</v>
+        <v>0.4478000311983621</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2661508302598605</v>
+        <v>0.155272582712513</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.7071706095034926</v>
+        <v>0.6431170741328387</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7699675107045536</v>
+        <v>0.6045692349367542</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7077132233116359</v>
+        <v>0.5925516563814455</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5392985053884871</v>
+        <v>0.4718144702879314</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7574031287393765</v>
+        <v>0.5883445245904113</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.8992202953269626</v>
+        <v>0.7668966282591825</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.9146477707244998</v>
+        <v>0.9002399124757758</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5901576772669372</v>
+        <v>0.5444280145180826</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5474936317846044</v>
+        <v>0.5517914895377203</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.4561024437637613</v>
+        <v>0.513330530479692</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.1031185642836121</v>
+        <v>0.1666350683024191</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.00765451071485046</v>
+        <v>0.08572722567287627</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2059285765274907</v>
+        <v>-0.1795062734463926</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3168247048434623</v>
+        <v>-0.1751963535403078</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2236483858420897</v>
+        <v>-0.05433015377560224</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1984583400984832</v>
+        <v>-0.01572329877511436</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3289365298269828</v>
+        <v>-0.2233750700618273</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.654307933692607</v>
+        <v>-0.5014379969548202</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.551334060268907</v>
+        <v>-0.4850188155699371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 9.39</t>
+          <t>X &lt; 9.263</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.392302057838755</v>
+        <v>0.4706280583400613</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2985102075992074</v>
+        <v>0.428777670071355</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3917385356855689</v>
+        <v>0.5205158862467911</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5105711613374098</v>
+        <v>0.7226451078410534</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2694458190526134</v>
+        <v>0.430994886241848</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4773462609698669</v>
+        <v>0.5718245390458634</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3907991154802843</v>
+        <v>0.4617336998528714</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.355363951770812</v>
+        <v>0.3624282694050081</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1965116232854811</v>
+        <v>0.2160649653238451</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4056656463756454</v>
+        <v>0.4015215576220257</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5164952240406535</v>
+        <v>0.5842975555956897</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7400754971722989</v>
+        <v>0.7357505149805093</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6005618857908104</v>
+        <v>0.5669613845469854</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5126382364365227</v>
+        <v>0.5256117403841856</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5060753086562286</v>
+        <v>0.6056392475808892</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.3080808080808026</v>
+        <v>0.4117332131565732</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.1963117918064796</v>
+        <v>0.2928240740740762</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1136356268653813</v>
+        <v>0.144900105039703</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.09216033757738273</v>
+        <v>0.1219243661156213</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1898313418210549</v>
+        <v>0.2472097097943617</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3001592179965655</v>
+        <v>0.3693296106673642</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.06104244107356749</v>
+        <v>0.1308109450676866</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.1249413862921216</v>
+        <v>-0.08598818630773053</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1415148380108562</v>
+        <v>-0.114769808477611</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 10.01</t>
+          <t>X &lt; 9.872</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2810</v>
+        <v>2803</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1286692101492264</v>
+        <v>-0.03944201473480291</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.01448908256850245</v>
+        <v>0.2291655512297837</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2910550257644076</v>
+        <v>0.4454408895347441</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3398341151508433</v>
+        <v>0.5103141666582403</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.342137114182016</v>
+        <v>0.396395269659962</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3370256922761996</v>
+        <v>0.3251500678857155</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4340591261640583</v>
+        <v>0.3300962132652359</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2469592982109674</v>
+        <v>0.1517736530152263</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.06103852992870884</v>
+        <v>0.08701485173668999</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2645198555718693</v>
+        <v>0.2340990834595971</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3112757533997765</v>
+        <v>0.3492873929940643</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4074711500937624</v>
+        <v>0.5549787713178631</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3330397357725161</v>
+        <v>0.4912883969910951</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.1330664981391791</v>
+        <v>0.3351741033838351</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.06362096823943375</v>
+        <v>0.2786331733700109</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.005107856420842438</v>
+        <v>0.2920363170967519</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.1076964637919389</v>
+        <v>0.1736728944246693</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.155897992313804</v>
+        <v>0.09749518165458682</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.2385669819691643</v>
+        <v>0.08380390545995908</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1728107255023517</v>
+        <v>0.1769499547643321</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.05444935457961009</v>
+        <v>0.3432885498629403</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.1445933905146788</v>
+        <v>0.1468173476287049</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2757467405162686</v>
+        <v>0.09073993673634106</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2236879302890173</v>
+        <v>0.09246399319289367</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 10.63</t>
+          <t>X &lt; 10.48</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2919</v>
+        <v>2932</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.139827398952022</v>
+        <v>-0.1416114996842026</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2183984782557715</v>
+        <v>-0.1324739835842692</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.06254751537770886</v>
+        <v>0.1210120904741103</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.2531240132797095</v>
+        <v>0.3603050948353186</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2088174484906062</v>
+        <v>0.3070431034853414</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1767408034341926</v>
+        <v>0.2457456013844848</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1733384962707305</v>
+        <v>0.1478490757573852</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2212669862525303</v>
+        <v>0.1674527793930736</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1119521396674372</v>
+        <v>0.07720106798239357</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1768803253265148</v>
+        <v>0.08115077066276655</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.09563092595187328</v>
+        <v>0.03338698398032847</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.007218807107513214</v>
+        <v>0.04800188121051718</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1746228097629796</v>
+        <v>-0.1298957652036137</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4438374871969941</v>
+        <v>-0.324250926999774</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3987833451918732</v>
+        <v>-0.2724489669495753</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.330646747626588</v>
+        <v>-0.1671655066423412</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.3759996159020602</v>
+        <v>-0.2169991210162223</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.4264035284443395</v>
+        <v>-0.2277261178686629</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.4296359329912676</v>
+        <v>-0.1974587353532513</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.2567952795416915</v>
+        <v>-0.03095282623568352</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.1631166280894902</v>
+        <v>0.1030634784960327</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.2527643193310212</v>
+        <v>-0.05407282439102801</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4030596940305884</v>
+        <v>-0.1652262855956863</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.2530452273695047</v>
+        <v>-0.1025862331529694</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 11.25</t>
+          <t>X &lt; 11.09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2992</v>
+        <v>2999</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.407016267660822</v>
+        <v>-0.3659225586863712</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.3591673756172113</v>
+        <v>-0.1970075790412125</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2526738270590414</v>
+        <v>-0.1094528312689604</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.01769923789164096</v>
+        <v>0.1444297578772478</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2684319562900015</v>
+        <v>-0.0795113975890871</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2621322301605531</v>
+        <v>-0.1029451510185737</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3840266471726963</v>
+        <v>-0.2827581615113672</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.377443097476494</v>
+        <v>-0.2705089272253502</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4832960757553764</v>
+        <v>-0.3892343812018169</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4389127504153976</v>
+        <v>-0.3700395791880382</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.5450134752621025</v>
+        <v>-0.4440355274453864</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6382642313159437</v>
+        <v>-0.5024819425949545</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6767032094543097</v>
+        <v>-0.4688610220267648</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.011536863213301</v>
+        <v>-0.797463060370788</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.8504884234626857</v>
+        <v>-0.5959431106407607</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.7363636363636346</v>
+        <v>-0.4806064799721455</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.7840075711626042</v>
+        <v>-0.5317490019960047</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.8025175189679388</v>
+        <v>-0.5453043769308721</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.8005380708792771</v>
+        <v>-0.5443234536927051</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.627479969402998</v>
+        <v>-0.3768603247317373</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.5160434202905009</v>
+        <v>-0.2253036407555271</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.6054724744292983</v>
+        <v>-0.4140414510723787</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7121141544382112</v>
+        <v>-0.4840579710144866</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>-0.459890418677297</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 11.87</t>
+          <t>X &lt; 11.7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3080</v>
+        <v>3091</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2409115671863944</v>
+        <v>-0.331322938772125</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3972873547218256</v>
+        <v>-0.367396397094268</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4636268369817458</v>
+        <v>-0.3838446322870297</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2233711738038977</v>
+        <v>-0.1550769876258187</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2507062653229539</v>
+        <v>-0.3163326991473667</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1101533519216744</v>
+        <v>-0.2380112336107061</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1213124756199804</v>
+        <v>-0.3073801688920028</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2196382428940495</v>
+        <v>-0.4010865935552133</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3535610955019806</v>
+        <v>-0.5125481635038582</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.2677403354951906</v>
+        <v>-0.4853424027550517</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3629696459507983</v>
+        <v>-0.5491134973527068</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4614409185445325</v>
+        <v>-0.6140612169133206</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4660005076483955</v>
+        <v>-0.6145391934347799</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.7975263545772009</v>
+        <v>-0.908556202528743</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6597459181857701</v>
+        <v>-0.7332972630086374</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.5966399748783147</v>
+        <v>-0.6047655224473019</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.711485826791062</v>
+        <v>-0.7220720357219719</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.700029664675796</v>
+        <v>-0.6746550393990418</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.691915131354115</v>
+        <v>-0.6673721364137677</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.6481300709651379</v>
+        <v>-0.5954785401189326</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.5553672582147797</v>
+        <v>-0.4330513736825452</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.6119747716909245</v>
+        <v>-0.5861470311392978</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.7077330566196807</v>
+        <v>-0.6145452500140536</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6020906663430026</v>
+        <v>-0.5636131197307748</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 12.49</t>
+          <t>X &lt; 12.31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3144</v>
+        <v>3152</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2148919508175098</v>
+        <v>-0.156799956457057</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4064514544223314</v>
+        <v>-0.1653451580173595</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5953175263735986</v>
+        <v>-0.3946301239474579</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.279567903137945</v>
+        <v>-0.1186059048673656</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3447775887496647</v>
+        <v>-0.1874415523903323</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2981916651873746</v>
+        <v>-0.139112442779556</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3880849142148648</v>
+        <v>-0.2855307939343845</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5217839269944022</v>
+        <v>-0.3832972582972687</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6205931054885738</v>
+        <v>-0.4585666562873101</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3939319920671949</v>
+        <v>-0.3208633311376445</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4183636144293885</v>
+        <v>-0.409702087115086</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4571369131141125</v>
+        <v>-0.4154747993809167</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3576033974860238</v>
+        <v>-0.3109197933475727</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.528324867997263</v>
+        <v>-0.5090808950388208</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.374898988373225</v>
+        <v>-0.3186061179034709</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.300915243808646</v>
+        <v>-0.1815889975576894</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.4160546017553699</v>
+        <v>-0.3301578822412239</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.4068675089083271</v>
+        <v>-0.3177650952397073</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.3944370402413568</v>
+        <v>-0.2746903554733393</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.3158828038472308</v>
+        <v>-0.1999143302952433</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2677108800383223</v>
+        <v>-0.1148648524569609</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3246183313051674</v>
+        <v>-0.2663523590618411</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4127510937300514</v>
+        <v>-0.2893862298156265</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3425156357756052</v>
+        <v>-0.2742003493987042</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 13.11</t>
+          <t>X &lt; 12.92</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3187</v>
+        <v>3202</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2763611321235615</v>
+        <v>-0.3333244025292004</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3452094524486498</v>
+        <v>-0.2835707846581386</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4884559283938188</v>
+        <v>-0.4357191332828378</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3111931760771469</v>
+        <v>-0.2042208018202913</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4736163985295505</v>
+        <v>-0.4004770452842052</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4251872573450299</v>
+        <v>-0.3815835911621051</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.5242738207580544</v>
+        <v>-0.5692183617646691</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6287346891359107</v>
+        <v>-0.6392164564942746</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7256932140587367</v>
+        <v>-0.711407210970016</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5437327885646539</v>
+        <v>-0.5882998378020403</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5017002473087047</v>
+        <v>-0.4849811281426568</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.543725283767003</v>
+        <v>-0.4949902253342202</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4919286344358227</v>
+        <v>-0.4094367355163016</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6320901092298783</v>
+        <v>-0.5150082247944923</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.3644593609766318</v>
+        <v>-0.2446945766783841</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.3460662967705161</v>
+        <v>-0.1945035446612877</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.398855183693847</v>
+        <v>-0.2488930871507264</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.3598798026659935</v>
+        <v>-0.2075671891183859</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.3760220761878443</v>
+        <v>-0.1929677932013547</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.3273409351783201</v>
+        <v>-0.1471773439570612</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2871352609235345</v>
+        <v>-0.0722907247691964</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.3443041672913481</v>
+        <v>-0.1913628682778921</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4275522259568234</v>
+        <v>-0.2102105363178453</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.3906696744074196</v>
+        <v>-0.2602298614105578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 13.73</t>
+          <t>X &lt; 13.53</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3213</v>
+        <v>3225</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1488817240623774</v>
+        <v>-0.1559272207214377</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2198279303289254</v>
+        <v>-0.1390109275348266</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.435287982457794</v>
+        <v>-0.2989269879488106</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2342369431382849</v>
+        <v>-0.07322616651735103</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3980310171592194</v>
+        <v>-0.2391781402486259</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3175134982126764</v>
+        <v>-0.2809272324113863</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4529427060137152</v>
+        <v>-0.4419952634083941</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5897498685603537</v>
+        <v>-0.5444759224456917</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6236233336323949</v>
+        <v>-0.6152168334616377</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4803132672208505</v>
+        <v>-0.5294803968776094</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3743947606378981</v>
+        <v>-0.4249436839894898</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5113120538574734</v>
+        <v>-0.4986139298598573</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5310155637666583</v>
+        <v>-0.4215937752309671</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6408149347357863</v>
+        <v>-0.5281833158845117</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.4427306948677767</v>
+        <v>-0.2646476330686838</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.3576199749748312</v>
+        <v>-0.2108266457035981</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4421234234446274</v>
+        <v>-0.2655734323432313</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4043230925707988</v>
+        <v>-0.2254928176345175</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.4186044488379181</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3688198887981784</v>
+        <v>-0.16248813761257</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.3022438870717892</v>
+        <v>-0.06120403594847801</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.3595685359146401</v>
+        <v>-0.1799597840482647</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.408813630149119</v>
+        <v>-0.2279306719857672</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.341713788319062</v>
+        <v>-0.247747352900852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 14.35</t>
+          <t>X &lt; 14.14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3250</v>
+        <v>3266</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1730805384243297</v>
+        <v>-0.1221341771832627</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.06364347168398865</v>
+        <v>-0.04765765140570721</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2928847828855297</v>
+        <v>-0.2820472580394835</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2550373472279901</v>
+        <v>-0.1882774603755024</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3901941215088129</v>
+        <v>-0.3860738493624609</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3084690023235197</v>
+        <v>-0.3644858237068718</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5429316279756122</v>
+        <v>-0.5944171297029399</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.620131303493352</v>
+        <v>-0.699473185762038</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5919043206316843</v>
+        <v>-0.6763431838290757</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4896079286863042</v>
+        <v>-0.5406721227189166</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.3817856748293877</v>
+        <v>-0.3730477493719562</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5509700370227932</v>
+        <v>-0.5407593265779127</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5218749037520354</v>
+        <v>-0.509180291433907</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6942841523416021</v>
+        <v>-0.6175692862596591</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.4752529619069108</v>
+        <v>-0.3659000701989896</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.4764495786595191</v>
+        <v>-0.3057548458600081</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4694415552467461</v>
+        <v>-0.3305931102963697</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.433270535311344</v>
+        <v>-0.2926997123335653</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.4449443819522472</v>
+        <v>-0.2742158502974945</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.393609445048881</v>
+        <v>-0.2251465950363638</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.3647101447780372</v>
+        <v>-0.1628592909196129</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.453015038031289</v>
+        <v>-0.3116989842406355</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.4063252856504533</v>
+        <v>-0.2336141387524648</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.3716211358734682</v>
+        <v>-0.2552192147426098</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 14.98</t>
+          <t>X &lt; 14.75</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3288</v>
+        <v>3294</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.05894147007754214</v>
+        <v>-0.1208600714931762</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.193560378248435</v>
+        <v>0.1016956279828776</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1099258257266413</v>
+        <v>-0.141266881392319</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1411072583691748</v>
+        <v>-0.1136021035003907</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2180572441544655</v>
+        <v>-0.2516649137593916</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1955664572680149</v>
+        <v>-0.2590853164899158</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4059176056638378</v>
+        <v>-0.4937640762061406</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4853876907483539</v>
+        <v>-0.5702689388490114</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4569673590593197</v>
+        <v>-0.5159924957966879</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.394986873116892</v>
+        <v>-0.4788486054510983</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3155161364332031</v>
+        <v>-0.3103198107335601</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4556390446960918</v>
+        <v>-0.4486864522543286</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5004118843299992</v>
+        <v>-0.4267924759297941</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5824111822946918</v>
+        <v>-0.5363416626591615</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.4037866517248858</v>
+        <v>-0.3531150239883942</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.4284348337746309</v>
+        <v>-0.2887162468657536</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.3016414207867371</v>
+        <v>-0.2536321064323985</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.3277626429182163</v>
+        <v>-0.2474674384949367</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.3367784310896695</v>
+        <v>-0.2273065147744475</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.3445997581208928</v>
+        <v>-0.1768177960051531</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.3526697432058796</v>
+        <v>-0.1501944778620015</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.4712222109844788</v>
+        <v>-0.2680646245776543</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.4827150000110976</v>
+        <v>-0.1885597413736164</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.479725197262205</v>
+        <v>-0.2113457206166416</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 15.6</t>
+          <t>X &lt; 15.36</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3301</v>
+        <v>3317</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.05951389739835378</v>
+        <v>0.08012776290736667</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1622033527382314</v>
+        <v>0.2995167506509375</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.08552736779651582</v>
+        <v>0.01968425760131964</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1494816535466867</v>
+        <v>0.01315647051719537</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3178091395497731</v>
+        <v>-0.1258163019757177</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2645746261510311</v>
+        <v>-0.162050500564547</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3565923737422381</v>
+        <v>-0.3705721636976733</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4368264963437127</v>
+        <v>-0.4486162902004551</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4686539239287058</v>
+        <v>-0.4238069361693917</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4401169784600683</v>
+        <v>-0.4224094608068043</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.35989653578185</v>
+        <v>-0.3132074882508249</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.5005768013754661</v>
+        <v>-0.4224908735010473</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.5495960171297156</v>
+        <v>-0.4384934971098247</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.692560950447195</v>
+        <v>-0.4888907310707395</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.5172560970780324</v>
+        <v>-0.2815679747033997</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.5395065798510998</v>
+        <v>-0.2738608163451772</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4137713013540036</v>
+        <v>-0.1494810469314061</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4402358809522298</v>
+        <v>-0.174340745747422</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.4484013001097154</v>
+        <v>-0.1528125563220684</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.4252335046259645</v>
+        <v>-0.1613877515355853</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.4354308577872246</v>
+        <v>-0.138875315863686</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.5538402969650775</v>
+        <v>-0.3167052111387036</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.5642322503061621</v>
+        <v>-0.2963545352097867</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.5918714096832716</v>
+        <v>-0.3804347303526825</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 16.22</t>
+          <t>X &lt; 15.97</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3314</v>
+        <v>3333</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.09004890095221185</v>
+        <v>0.09265336724101303</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1310907165155797</v>
+        <v>0.2502145732943291</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.121289137724311</v>
+        <v>-0.0044679757835695</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.1577907415032698</v>
+        <v>-0.01379866857034528</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3267738914466491</v>
+        <v>-0.2130973124895021</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3030323111231752</v>
+        <v>-0.2185934018981257</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4277362069752257</v>
+        <v>-0.3702319332362976</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5087645785320163</v>
+        <v>-0.4792195296823678</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5403273164680797</v>
+        <v>-0.4837950891366702</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5149425817783069</v>
+        <v>-0.4862276620807009</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.4339872175521577</v>
+        <v>-0.3762651663712617</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5752294162407665</v>
+        <v>-0.4863676352644362</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.628470740169206</v>
+        <v>-0.5076472052437992</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7416806662615656</v>
+        <v>-0.6188384993146911</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.5696511501413113</v>
+        <v>-0.4158130445572539</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6196066626530268</v>
+        <v>-0.4054949000578887</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.5250233207665858</v>
+        <v>-0.2822480039920237</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5217078225438172</v>
+        <v>-0.3076651024661885</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5591497507523755</v>
+        <v>-0.2852520657530064</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5655126768666889</v>
+        <v>-0.2628299140276695</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5175432569693541</v>
+        <v>-0.2431774163519691</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6056537779289499</v>
+        <v>-0.4205460295062622</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6149442370996638</v>
+        <v>-0.3991549516183639</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.6427877483798596</v>
+        <v>-0.4836407096783901</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 16.84</t>
+          <t>X &lt; 16.58</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3329</v>
+        <v>3347</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.001228975007151689</v>
+        <v>0.07755131343243704</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.06794517207379158</v>
+        <v>0.2631138092932801</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1599116175291897</v>
+        <v>0.03396948393766053</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1695948900793454</v>
+        <v>0.02222579334139141</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3393289103894048</v>
+        <v>-0.2070881828667268</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2849820674224688</v>
+        <v>-0.2416243837566796</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3826957126997641</v>
+        <v>-0.3959475880182737</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.46459484826363</v>
+        <v>-0.4760231343639063</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4958167014724069</v>
+        <v>-0.4800459695578851</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.503913867933079</v>
+        <v>-0.5452892880515421</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.422088487883201</v>
+        <v>-0.4049063299496609</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5340133292960587</v>
+        <v>-0.5157111965688443</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5920473463553293</v>
+        <v>-0.5415589378483645</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6757818639006672</v>
+        <v>-0.6235433538959327</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.5074631606633346</v>
+        <v>-0.4242119463874658</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.5245366460529723</v>
+        <v>-0.4414033687022183</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4609282553554976</v>
+        <v>-0.3787455277280856</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4880650053981697</v>
+        <v>-0.4046401196759675</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5843450732425666</v>
+        <v>-0.441119769821718</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.6198490327445896</v>
+        <v>-0.4477831351353032</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.6045663085777022</v>
+        <v>-0.3709378945365813</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.6926477255620114</v>
+        <v>-0.5180577394619732</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.6706560575173697</v>
+        <v>-0.46589787543504</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6686934837718965</v>
+        <v>-0.5208508842363244</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 17.46</t>
+          <t>X &lt; 17.19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3335</v>
+        <v>3359</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.0220474666752466</v>
+        <v>0.03513790819928175</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06071806021703452</v>
+        <v>0.160002372299104</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.109709706939114</v>
+        <v>-0.0136418668894791</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1802482470215381</v>
+        <v>-0.0274617674441302</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2608370652058909</v>
+        <v>-0.1681447837728669</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.2062294981399475</v>
+        <v>-0.1723769926338861</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3051265138415786</v>
+        <v>-0.3289572639288139</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3873540005413147</v>
+        <v>-0.4098124098124174</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4184225716430845</v>
+        <v>-0.4133463203878094</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4278668617011405</v>
+        <v>-0.451522635760071</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.3755428399012928</v>
+        <v>-0.3699546268484895</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4877528327106901</v>
+        <v>-0.4516744662802381</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.5476829967520871</v>
+        <v>-0.48138110838579</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6316506090070817</v>
+        <v>-0.5342574264562643</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.4648015949892468</v>
+        <v>-0.3380401945847638</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4807648727780389</v>
+        <v>-0.3234442343496369</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.3875758062555263</v>
+        <v>-0.2316362150921023</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4148301472211529</v>
+        <v>-0.2578686272022139</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5105275014275819</v>
+        <v>-0.3231360080197945</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.5456098028916756</v>
+        <v>-0.35871017277249</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5313075263350271</v>
+        <v>-0.3138823039588345</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6193449902130439</v>
+        <v>-0.4607282591293185</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.5968772427313596</v>
+        <v>-0.4078674948240106</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.595032507110929</v>
+        <v>-0.4631861485926336</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 18.08</t>
+          <t>X &lt; 17.8</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.0358423774879455</v>
+        <v>0.01930055536561071</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.07440586784895231</v>
+        <v>0.173619008627881</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.09639541836416043</v>
+        <v>-0.00034094580070132</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1671214141053383</v>
+        <v>-0.04391388818291375</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2477823857387023</v>
+        <v>-0.155047134533703</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.1931314634853791</v>
+        <v>-0.1592277556315125</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2922253040106142</v>
+        <v>-0.3159932068209983</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3745074096686452</v>
+        <v>-0.396910882692886</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4055504951410782</v>
+        <v>-0.4004020186468296</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4152188446945075</v>
+        <v>-0.4387991196972507</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3628248367383762</v>
+        <v>-0.3571708111942726</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4750807738152432</v>
+        <v>-0.4389446477492029</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5353248188975428</v>
+        <v>-0.4689694315506472</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6193297153983224</v>
+        <v>-0.5219000362877395</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4527236524770331</v>
+        <v>-0.3259398582077466</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.468500797448165</v>
+        <v>-0.3111779809907489</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3753759971919379</v>
+        <v>-0.2194244381744426</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4026499032544493</v>
+        <v>-0.2456849073006424</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4982503496551018</v>
+        <v>-0.3108655382436609</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5332625297829097</v>
+        <v>-0.3463616913793572</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5191233263533661</v>
+        <v>-0.3017122120657945</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.607153487744128</v>
+        <v>-0.4485332256761723</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.5846065678119032</v>
+        <v>-0.3956120719765011</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.58278143840068</v>
+        <v>-0.450958870065854</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 18.7</t>
+          <t>X &lt; 18.41</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3341</v>
+        <v>3364</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01421215504908702</v>
+        <v>0.01509396867120927</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.02378138111147621</v>
+        <v>0.1689383794814532</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1191753819906438</v>
+        <v>0.02324205364402587</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1908635675807062</v>
+        <v>-0.02097265411237714</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.242149357564692</v>
+        <v>-0.1322935322518006</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2170705670924278</v>
+        <v>-0.1362768705256343</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2873937743003481</v>
+        <v>-0.2937907143087557</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.3401777611516366</v>
+        <v>-0.3749669134284588</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3711025566999311</v>
+        <v>-0.3487014278518288</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4117043753126453</v>
+        <v>-0.4175837026695319</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.329163723754732</v>
+        <v>-0.3357233413855667</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4118338589284818</v>
+        <v>-0.3881007872419957</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4736445338419273</v>
+        <v>-0.4193962748876032</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5578355507887309</v>
+        <v>-0.4725437262963368</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.3924421005951899</v>
+        <v>-0.2776102609142086</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4072902811332142</v>
+        <v>-0.2621857211338323</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.3144862691595094</v>
+        <v>-0.17064978245822</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.34185785800085</v>
+        <v>-0.1970223346373743</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.4369746668695598</v>
+        <v>-0.2618565025334973</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4716369021144828</v>
+        <v>-0.2970410940811519</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4583116344592568</v>
+        <v>-0.2531041349117871</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5463053816436698</v>
+        <v>-0.3998255519553666</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.5233633428997067</v>
+        <v>-0.3466632211383072</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5216361014526356</v>
+        <v>-0.402122450837048</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 19.32</t>
+          <t>X &lt; 19.02</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3342</v>
+        <v>3367</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0004310658836743642</v>
+        <v>-0.00280371926103129</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.03745575528124334</v>
+        <v>0.1506815438869182</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1058820330696832</v>
+        <v>0.003997836064911553</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1777570040508678</v>
+        <v>-0.04070810484494558</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2291235432520651</v>
+        <v>-0.1226469532255408</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2039926952768383</v>
+        <v>-0.1560269244648609</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2745208883748589</v>
+        <v>-0.2845609971366514</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.327368173192788</v>
+        <v>-0.3363733189331839</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.358267582513669</v>
+        <v>-0.3395745442179319</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.399083786967644</v>
+        <v>-0.4090993451455347</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3164822890374595</v>
+        <v>-0.2974817032942667</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3992071045432226</v>
+        <v>-0.3500468886853909</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.4613305514929209</v>
+        <v>-0.3822934527048503</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.545558732484217</v>
+        <v>-0.435603224814777</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.410249215423903</v>
+        <v>-0.2710590731294076</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4249208502939794</v>
+        <v>-0.2551473660527677</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3321898009115358</v>
+        <v>-0.1637830962260409</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.3595898164693381</v>
+        <v>-0.190248345699203</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4546190017254617</v>
+        <v>-0.2548320203645815</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4892203093821124</v>
+        <v>-0.2897922459697995</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.4760664781522621</v>
+        <v>-0.2463973922999898</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.5640619020884472</v>
+        <v>-0.39305309743267</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.541049933295632</v>
+        <v>-0.3397190953216906</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5393511915748022</v>
+        <v>-0.3952713143782987</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 19.94</t>
+          <t>X &lt; 19.63</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.01334183487462326</v>
+        <v>-0.00280371926103129</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05112200203694073</v>
+        <v>0.1506815438869182</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.09259658744772992</v>
+        <v>0.003997836064911553</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1646582350875079</v>
+        <v>-0.04070810484494558</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2161054777879201</v>
+        <v>-0.1226469532255408</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1909226055926396</v>
+        <v>-0.1560269244648609</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2616556648814736</v>
+        <v>-0.2845609971366514</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3145662122586259</v>
+        <v>-0.3363733189331839</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.345440252743245</v>
+        <v>-0.3395745442179319</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3864707175909672</v>
+        <v>-0.4090993451455347</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3038084117902216</v>
+        <v>-0.2974817032942667</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3865878772842635</v>
+        <v>-0.3500468886853909</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4490239120075614</v>
+        <v>-0.3822934527048503</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5332892370656666</v>
+        <v>-0.435603224814777</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.3982127699215852</v>
+        <v>-0.2710590731294076</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.442540896882889</v>
+        <v>-0.2551473660527677</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.3498827633908661</v>
+        <v>-0.1637830962260409</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3773111855329461</v>
+        <v>-0.190248345699203</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4722527963574379</v>
+        <v>-0.2548320203645815</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.5067932096839414</v>
+        <v>-0.2897922459697995</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4938107092668531</v>
+        <v>-0.2463973922999898</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5818078057795972</v>
+        <v>-0.39305309743267</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.5587259455872555</v>
+        <v>-0.3397190953216906</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.5570556833780174</v>
+        <v>-0.3952713143782987</v>
       </c>
     </row>
   </sheetData>
